--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,12 +42,60 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00836221</x:t>
   </x:si>
   <x:si>
     <x:t>DEFEND AMERICAN JOBS</x:t>
   </x:si>
   <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
     <x:t>PATRONIS, JIMMY JR.</x:t>
   </x:si>
   <x:si>
@@ -57,21 +105,60 @@
     <x:t>FL</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
     <x:t>FINE, RANDY</x:t>
   </x:si>
   <x:si>
     <x:t>06</x:t>
   </x:si>
   <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00848440</x:t>
   </x:si>
   <x:si>
     <x:t>PROTECT PROGRESS</x:t>
   </x:si>
   <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALKINSHAW, JAMES</x:t>
   </x:si>
   <x:si>
@@ -82,93 +169,6 @@
   </x:si>
   <x:si>
     <x:t>PEKARSKY, STELLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
   </x:si>
   <x:si>
     <x:t>KELLY, ROBIN</x:t>
@@ -248,8 +248,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G20" totalsRowShown="0">
-  <x:autoFilter ref="A1:G20"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G32" totalsRowShown="0">
+  <x:autoFilter ref="A1:G32"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -613,7 +613,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G20"/>
+  <x:dimension ref="A1:G32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -666,7 +666,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>558813</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -689,7 +689,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>1673736</x:v>
+        <x:v>1803694</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -697,22 +697,22 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>1012792</x:v>
+        <x:v>5168736</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -720,22 +720,22 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="F5" s="1">
-        <x:v>20483</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>21</x:v>
@@ -743,10 +743,10 @@
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>22</x:v>
@@ -758,18 +758,18 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>83860</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>25</x:v>
@@ -781,18 +781,18 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>418060</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>28</x:v>
@@ -801,33 +801,33 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>80948</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="E9" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="F9" s="1">
-        <x:v>817065</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>21</x:v>
@@ -835,22 +835,22 @@
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="F10" s="1">
-        <x:v>2475788</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>21</x:v>
@@ -858,102 +858,102 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>557012</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="F12" s="1">
-        <x:v>771658</x:v>
+        <x:v>5017853</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>91656</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>1564215</x:v>
+        <x:v>515519</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>44</x:v>
@@ -962,21 +962,21 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>141263</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>46</x:v>
@@ -988,18 +988,18 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>5031161</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>49</x:v>
@@ -1008,33 +1008,33 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>9866096</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>119644</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>21</x:v>
@@ -1042,48 +1042,324 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>285008</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="F20" s="1">
+        <x:v>80948</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:7">
+      <x:c r="A21" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F21" s="1">
+        <x:v>817065</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:7">
+      <x:c r="A22" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F22" s="1">
+        <x:v>2475788</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:7">
+      <x:c r="A23" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F23" s="1">
+        <x:v>557012</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:7">
+      <x:c r="A24" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F24" s="1">
+        <x:v>771658</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:7">
+      <x:c r="A25" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F25" s="1">
+        <x:v>91656</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:7">
+      <x:c r="A26" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F26" s="1">
+        <x:v>1564215</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:7">
+      <x:c r="A27" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F27" s="1">
+        <x:v>141263</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:7">
+      <x:c r="A28" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F28" s="1">
+        <x:v>5031161</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:7">
+      <x:c r="A29" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F29" s="1">
+        <x:v>9866096</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:7">
+      <x:c r="A30" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F30" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:7">
+      <x:c r="A31" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F31" s="1">
+        <x:v>285008</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:7">
+      <x:c r="A32" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F32" s="1">
         <x:v>30183</x:v>
       </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>12</x:v>
+      <x:c r="G32" s="1" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1132,70 +1408,70 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>5031161</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="1">
-        <x:v>418060</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
@@ -1206,13 +1482,13 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>285008</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
@@ -1223,217 +1499,217 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>30183</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>9985740</x:v>
+        <x:v>15154476</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>817065</x:v>
+        <x:v>1634131</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>2475788</x:v>
+        <x:v>4279482</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>557012</x:v>
+        <x:v>1072531</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>83860</x:v>
+        <x:v>167720</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>80948</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>771658</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>91656</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>1564215</x:v>
+        <x:v>3128430</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>141263</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1478,58 +1754,58 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>5031161</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>418060</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
@@ -1537,181 +1813,181 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>315191</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>9985740</x:v>
+        <x:v>15154476</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>817065</x:v>
+        <x:v>1634131</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>2475788</x:v>
+        <x:v>4279482</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>557012</x:v>
+        <x:v>1072531</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>83860</x:v>
+        <x:v>167720</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>80948</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>771658</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>91656</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>1564215</x:v>
+        <x:v>3128430</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>141263</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1752,101 +2028,101 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>5031161</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>418060</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2232549</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>13278593</x:v>
+        <x:v>21068089</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>956063</x:v>
+        <x:v>1555442</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>80948</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>2568792</x:v>
+        <x:v>5137584</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1883,23 +2159,23 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>5031161</x:v>
+        <x:v>10049014</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>418060</x:v>
+        <x:v>836118</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2232549</x:v>
@@ -1907,31 +2183,31 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>14234656</x:v>
+        <x:v>22623531</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>80948</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>2568792</x:v>
+        <x:v>5137584</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>1033275</x:v>
@@ -1974,32 +2250,32 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>5031161</x:v>
+        <x:v>10049014</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>418060</x:v>
+        <x:v>836118</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2232549</x:v>
@@ -2007,65 +2283,65 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>13158949</x:v>
+        <x:v>20948445</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>1075707</x:v>
+        <x:v>1675086</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>80948</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>1004577</x:v>
+        <x:v>2009154</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>1564215</x:v>
+        <x:v>3128430</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>1033275</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -169,6 +169,18 @@
   </x:si>
   <x:si>
     <x:t>PEKARSKY, STELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
   </x:si>
   <x:si>
     <x:t>KELLY, ROBIN</x:t>
@@ -248,8 +260,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G32" totalsRowShown="0">
-  <x:autoFilter ref="A1:G32"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G33" totalsRowShown="0">
+  <x:autoFilter ref="A1:G33"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -264,8 +276,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E19" totalsRowShown="0">
-  <x:autoFilter ref="A1:E19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E20" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -278,8 +290,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D18" totalsRowShown="0">
-  <x:autoFilter ref="A1:D18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D19" totalsRowShown="0">
+  <x:autoFilter ref="A1:D19"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -291,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C10" totalsRowShown="0">
-  <x:autoFilter ref="A1:C10"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C11" totalsRowShown="0">
+  <x:autoFilter ref="A1:C11"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -303,8 +315,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B8" totalsRowShown="0">
-  <x:autoFilter ref="A1:B8"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B9" totalsRowShown="0">
+  <x:autoFilter ref="A1:B9"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -314,8 +326,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C10" totalsRowShown="0">
-  <x:autoFilter ref="A1:C10"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C11" totalsRowShown="0">
+  <x:autoFilter ref="A1:C11"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -613,12 +625,12 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G32"/>
+  <x:dimension ref="A1:G33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
     <x:col min="1" max="1" width="15.710625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="23.424911" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="24.282054" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="25.139196" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="25.282054" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="23.424911" style="1" customWidth="1"/>
@@ -1019,22 +1031,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>83860</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>21</x:v>
@@ -1042,22 +1054,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>418060</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>21</x:v>
@@ -1071,16 +1083,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>80948</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>21</x:v>
@@ -1088,25 +1100,25 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>817065</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
@@ -1117,16 +1129,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>2475788</x:v>
+        <x:v>817065</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>12</x:v>
@@ -1134,45 +1146,45 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>557012</x:v>
+        <x:v>2475788</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>771658</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>21</x:v>
@@ -1186,16 +1198,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>91656</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>21</x:v>
@@ -1203,22 +1215,22 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>1564215</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>21</x:v>
@@ -1226,22 +1238,22 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>141263</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>21</x:v>
@@ -1255,16 +1267,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>5031161</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>21</x:v>
@@ -1272,33 +1284,33 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>9866096</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>15</x:v>
@@ -1310,7 +1322,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>119644</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1324,19 +1336,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>285008</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
@@ -1347,18 +1359,41 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F32" s="1">
+        <x:v>285008</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:7">
+      <x:c r="A33" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F33" s="1">
         <x:v>30183</x:v>
       </x:c>
-      <x:c r="G32" s="1" t="s">
+      <x:c r="G33" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1378,7 +1413,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E19"/>
+  <x:dimension ref="A1:E20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1476,10 +1511,10 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>11</x:v>
@@ -1493,10 +1528,10 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>11</x:v>
@@ -1595,16 +1630,16 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>21</x:v>
@@ -1612,16 +1647,16 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>1543316</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>21</x:v>
@@ -1629,16 +1664,16 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>21</x:v>
@@ -1646,16 +1681,16 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>3128430</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>21</x:v>
@@ -1663,16 +1698,16 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>282526</x:v>
+        <x:v>3128430</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>21</x:v>
@@ -1680,24 +1715,24 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>20483</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>47</x:v>
@@ -1706,9 +1741,26 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D19" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:5">
+      <x:c r="A20" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D20" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
+      <x:c r="E20" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1728,7 +1780,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D18"/>
+  <x:dimension ref="A1:D19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1810,7 +1862,7 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>11</x:v>
@@ -1894,13 +1946,13 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
         <x:v>21</x:v>
@@ -1908,13 +1960,13 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>1543316</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>21</x:v>
@@ -1922,13 +1974,13 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>21</x:v>
@@ -1936,13 +1988,13 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>3128430</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>21</x:v>
@@ -1950,13 +2002,13 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>282526</x:v>
+        <x:v>3128430</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>21</x:v>
@@ -1964,16 +2016,16 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>20483</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
@@ -1984,9 +2036,23 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:4">
+      <x:c r="A19" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C19" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="D19" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2006,7 +2072,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C10"/>
+  <x:dimension ref="A1:C11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2083,10 +2149,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>21</x:v>
@@ -2094,10 +2160,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>5137584</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>21</x:v>
@@ -2105,13 +2171,13 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>20483</x:v>
+        <x:v>5137584</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -2119,9 +2185,20 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B10" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:3">
+      <x:c r="A11" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B11" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
+      <x:c r="C11" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2141,7 +2218,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B8"/>
+  <x:dimension ref="A1:B9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2191,25 +2268,33 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>5137584</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B8" s="1">
+        <x:v>5137584</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:2">
+      <x:c r="A9" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B8" s="1">
+      <x:c r="B9" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>
@@ -2229,11 +2314,12 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C10"/>
+  <x:dimension ref="A1:C11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
-    <x:col min="1" max="2" width="23.424911" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="24.282054" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="23.424911" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="13.853482" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -2305,13 +2391,13 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -2319,21 +2405,21 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>2009154</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>3128430</x:v>
+        <x:v>2009154</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -2341,9 +2427,20 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C10" s="1">
+        <x:v>3128430</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:3">
+      <x:c r="A11" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C10" s="1">
+      <x:c r="C11" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -260,8 +260,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G33" totalsRowShown="0">
-  <x:autoFilter ref="A1:G33"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G30" totalsRowShown="0">
+  <x:autoFilter ref="A1:G30"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -625,7 +625,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G33"/>
+  <x:dimension ref="A1:G30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1054,22 +1054,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>83860</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>21</x:v>
@@ -1083,16 +1083,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>418060</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>21</x:v>
@@ -1100,91 +1100,91 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>80948</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>817065</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>2475788</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>557012</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>21</x:v>
@@ -1198,16 +1198,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>771658</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>21</x:v>
@@ -1221,16 +1221,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>91656</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>21</x:v>
@@ -1238,68 +1238,68 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>1564215</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>141263</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>5031161</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>21</x:v>
@@ -1307,93 +1307,24 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>9866096</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:7">
-      <x:c r="A31" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B31" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C31" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F31" s="1">
-        <x:v>119644</x:v>
-      </x:c>
-      <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:7">
-      <x:c r="A32" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B32" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C32" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F32" s="1">
-        <x:v>285008</x:v>
-      </x:c>
-      <x:c r="G32" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:7">
-      <x:c r="A33" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B33" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C33" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D33" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F33" s="1">
-        <x:v>30183</x:v>
-      </x:c>
-      <x:c r="G33" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1554,7 +1485,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>15154476</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>12</x:v>
@@ -1571,7 +1502,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>1634131</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>12</x:v>
@@ -1588,7 +1519,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>4279482</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>12</x:v>
@@ -1605,7 +1536,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>1072531</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>21</x:v>
@@ -1622,7 +1553,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>167720</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>21</x:v>
@@ -1707,7 +1638,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>3128430</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>21</x:v>
@@ -1882,7 +1813,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>15154476</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>12</x:v>
@@ -1896,7 +1827,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>1634131</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>12</x:v>
@@ -1910,7 +1841,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>4279482</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>12</x:v>
@@ -1924,7 +1855,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>1072531</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>21</x:v>
@@ -1938,7 +1869,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>167720</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
         <x:v>21</x:v>
@@ -2008,7 +1939,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>3128430</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>21</x:v>
@@ -2130,7 +2061,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>21068089</x:v>
+        <x:v>13278592</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>12</x:v>
@@ -2141,7 +2072,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>1555442</x:v>
+        <x:v>956063</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>21</x:v>
@@ -2174,7 +2105,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>5137584</x:v>
+        <x:v>3573369</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>21</x:v>
@@ -2263,7 +2194,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>22623531</x:v>
+        <x:v>14234655</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -2287,7 +2218,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>5137584</x:v>
+        <x:v>3573369</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -2375,7 +2306,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>20948445</x:v>
+        <x:v>13158948</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -2386,7 +2317,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>1675086</x:v>
+        <x:v>1075707</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -2430,7 +2361,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>3128430</x:v>
+        <x:v>1564215</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -181,6 +181,18 @@
   </x:si>
   <x:si>
     <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
   </x:si>
   <x:si>
     <x:t>KELLY, ROBIN</x:t>
@@ -260,8 +272,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G30" totalsRowShown="0">
-  <x:autoFilter ref="A1:G30"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G31" totalsRowShown="0">
+  <x:autoFilter ref="A1:G31"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -276,8 +288,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E20" totalsRowShown="0">
-  <x:autoFilter ref="A1:E20"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E21" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -290,8 +302,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D19" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D20" totalsRowShown="0">
+  <x:autoFilter ref="A1:D20"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -303,8 +315,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C11" totalsRowShown="0">
-  <x:autoFilter ref="A1:C11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C12" totalsRowShown="0">
+  <x:autoFilter ref="A1:C12"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -315,8 +327,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B9" totalsRowShown="0">
-  <x:autoFilter ref="A1:B9"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B10" totalsRowShown="0">
+  <x:autoFilter ref="A1:B10"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -326,8 +338,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C11" totalsRowShown="0">
-  <x:autoFilter ref="A1:C11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C12" totalsRowShown="0">
+  <x:autoFilter ref="A1:C12"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -625,7 +637,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G30"/>
+  <x:dimension ref="A1:G31"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1054,22 +1066,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>21</x:v>
@@ -1083,16 +1095,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>80948</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>21</x:v>
@@ -1100,68 +1112,68 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>672092</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>41493</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>771658</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>21</x:v>
@@ -1175,16 +1187,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>91656</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>21</x:v>
@@ -1198,16 +1210,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>141263</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>21</x:v>
@@ -1221,16 +1233,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>5031161</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>21</x:v>
@@ -1238,33 +1250,33 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>4697360</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>15</x:v>
@@ -1276,7 +1288,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>119644</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>12</x:v>
@@ -1290,19 +1302,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>285008</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
@@ -1313,18 +1325,41 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="1">
+        <x:v>285008</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:7">
+      <x:c r="A31" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F31" s="1">
         <x:v>30183</x:v>
       </x:c>
-      <x:c r="G30" s="1" t="s">
+      <x:c r="G31" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1344,7 +1379,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E20"/>
+  <x:dimension ref="A1:E21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1442,16 +1477,16 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>285008</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>21</x:v>
@@ -1459,16 +1494,16 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>21</x:v>
@@ -1476,33 +1511,33 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>9985740</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>817066</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>12</x:v>
@@ -1510,16 +1545,16 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>2475786</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>12</x:v>
@@ -1527,33 +1562,33 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>557012</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>83860</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>21</x:v>
@@ -1561,16 +1596,16 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>91847</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>21</x:v>
@@ -1578,16 +1613,16 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>21</x:v>
@@ -1595,16 +1630,16 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>1543316</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>21</x:v>
@@ -1612,16 +1647,16 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>21</x:v>
@@ -1629,16 +1664,16 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>1564215</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>21</x:v>
@@ -1646,16 +1681,16 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>282526</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>21</x:v>
@@ -1663,24 +1698,24 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>20483</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>47</x:v>
@@ -1689,9 +1724,26 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D20" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:5">
+      <x:c r="A21" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D21" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
+      <x:c r="E21" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1711,7 +1763,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D19"/>
+  <x:dimension ref="A1:D20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1793,13 +1845,13 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>315191</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>21</x:v>
@@ -1807,27 +1859,27 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>9985740</x:v>
+        <x:v>315191</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>817066</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>12</x:v>
@@ -1835,13 +1887,13 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>2475786</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>12</x:v>
@@ -1849,27 +1901,27 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>557012</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>83860</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
         <x:v>21</x:v>
@@ -1877,13 +1929,13 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>91847</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
         <x:v>21</x:v>
@@ -1891,13 +1943,13 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>21</x:v>
@@ -1905,13 +1957,13 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>1543316</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>21</x:v>
@@ -1919,13 +1971,13 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>21</x:v>
@@ -1933,13 +1985,13 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>1564215</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>21</x:v>
@@ -1947,13 +1999,13 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>282526</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>21</x:v>
@@ -1961,16 +2013,16 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>20483</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
@@ -1981,9 +2033,23 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C19" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:4">
+      <x:c r="A20" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C20" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="D20" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2003,7 +2069,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C11"/>
+  <x:dimension ref="A1:C12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2058,13 +2124,13 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>13278592</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -2072,18 +2138,18 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>956063</x:v>
+        <x:v>13278592</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>91847</x:v>
+        <x:v>956063</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>21</x:v>
@@ -2091,10 +2157,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>21</x:v>
@@ -2102,10 +2168,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>3573369</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>21</x:v>
@@ -2113,13 +2179,13 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>20483</x:v>
+        <x:v>3573369</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -2127,9 +2193,20 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B11" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:3">
+      <x:c r="A12" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B12" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
+      <x:c r="C12" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2149,7 +2226,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B9"/>
+  <x:dimension ref="A1:B10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2191,41 +2268,49 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>14234655</x:v>
+        <x:v>300000</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>91847</x:v>
+        <x:v>14234655</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>3573369</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B9" s="1">
+        <x:v>3573369</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:2">
+      <x:c r="A10" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B9" s="1">
+      <x:c r="B10" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>
@@ -2245,7 +2330,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C11"/>
+  <x:dimension ref="A1:C12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2300,46 +2385,46 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>13158948</x:v>
+        <x:v>300000</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>1075707</x:v>
+        <x:v>13158948</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>91847</x:v>
+        <x:v>1075707</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -2347,21 +2432,21 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>2009154</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>1564215</x:v>
+        <x:v>2009154</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -2369,9 +2454,20 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C11" s="1">
+        <x:v>1564215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:3">
+      <x:c r="A12" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C11" s="1">
+      <x:c r="C12" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -195,6 +195,9 @@
     <x:t>GA</x:t>
   </x:si>
   <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
     <x:t>KELLY, ROBIN</x:t>
   </x:si>
   <x:si>
@@ -202,6 +205,18 @@
   </x:si>
   <x:si>
     <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -272,8 +287,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G31" totalsRowShown="0">
-  <x:autoFilter ref="A1:G31"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G34" totalsRowShown="0">
+  <x:autoFilter ref="A1:G34"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -288,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E21" totalsRowShown="0">
-  <x:autoFilter ref="A1:E21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E24" totalsRowShown="0">
+  <x:autoFilter ref="A1:E24"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -302,8 +317,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D20" totalsRowShown="0">
-  <x:autoFilter ref="A1:D20"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D23" totalsRowShown="0">
+  <x:autoFilter ref="A1:D23"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -315,8 +330,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C12" totalsRowShown="0">
-  <x:autoFilter ref="A1:C12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C14" totalsRowShown="0">
+  <x:autoFilter ref="A1:C14"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -327,8 +342,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B10" totalsRowShown="0">
-  <x:autoFilter ref="A1:B10"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B12" totalsRowShown="0">
+  <x:autoFilter ref="A1:B12"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -338,8 +353,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C12" totalsRowShown="0">
-  <x:autoFilter ref="A1:C12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C15" totalsRowShown="0">
+  <x:autoFilter ref="A1:C15"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -637,7 +652,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G31"/>
+  <x:dimension ref="A1:G34"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1135,68 +1150,68 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>672092</x:v>
+        <x:v>102144</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>41493</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>771658</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>21</x:v>
@@ -1210,16 +1225,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>91656</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>21</x:v>
@@ -1233,16 +1248,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>141263</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>21</x:v>
@@ -1256,16 +1271,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>5031161</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>21</x:v>
@@ -1273,33 +1288,33 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>4697360</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>15</x:v>
@@ -1311,7 +1326,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>119644</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1325,19 +1340,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>285008</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
@@ -1348,18 +1363,87 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="1">
+        <x:v>285008</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:7">
+      <x:c r="A32" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F32" s="1">
         <x:v>30183</x:v>
       </x:c>
-      <x:c r="G31" s="1" t="s">
+      <x:c r="G32" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:7">
+      <x:c r="A33" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F33" s="1">
+        <x:v>850000</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:7">
+      <x:c r="A34" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F34" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G34" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1379,7 +1463,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E21"/>
+  <x:dimension ref="A1:E24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1477,16 +1561,16 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>300000</x:v>
+        <x:v>102144</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>21</x:v>
@@ -1494,16 +1578,16 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>285008</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>21</x:v>
@@ -1511,16 +1595,16 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B8" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>21</x:v>
@@ -1528,33 +1612,33 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>9985740</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>817066</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>12</x:v>
@@ -1562,16 +1646,16 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>2475786</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>12</x:v>
@@ -1579,33 +1663,33 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>557012</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>83860</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>21</x:v>
@@ -1613,16 +1697,16 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>91847</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>21</x:v>
@@ -1630,16 +1714,16 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>161896</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>21</x:v>
@@ -1647,16 +1731,16 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>1543316</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>21</x:v>
@@ -1664,16 +1748,16 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>183312</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>21</x:v>
@@ -1681,16 +1765,16 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>1564215</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>21</x:v>
@@ -1698,16 +1782,16 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>282526</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>21</x:v>
@@ -1715,35 +1799,86 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>20483</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D21" s="1">
+        <x:v>1564215</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:5">
+      <x:c r="A22" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D22" s="1">
+        <x:v>282526</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:5">
+      <x:c r="A23" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D23" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:5">
+      <x:c r="A24" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B21" s="1" t="s">
+      <x:c r="B24" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C21" s="1" t="s">
+      <x:c r="C24" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D21" s="1">
+      <x:c r="D24" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
+      <x:c r="E24" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1763,7 +1898,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D20"/>
+  <x:dimension ref="A1:D23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1845,13 +1980,13 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>300000</x:v>
+        <x:v>102144</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>21</x:v>
@@ -1859,13 +1994,13 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>315191</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>21</x:v>
@@ -1873,27 +2008,27 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>9985740</x:v>
+        <x:v>315191</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>817066</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>12</x:v>
@@ -1901,13 +2036,13 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>2475786</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>12</x:v>
@@ -1915,27 +2050,27 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>557012</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>83860</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
         <x:v>21</x:v>
@@ -1943,13 +2078,13 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>91847</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>21</x:v>
@@ -1957,13 +2092,13 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>161896</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>21</x:v>
@@ -1971,13 +2106,13 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>1543316</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>21</x:v>
@@ -1985,13 +2120,13 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>183312</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>21</x:v>
@@ -1999,13 +2134,13 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>1564215</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>21</x:v>
@@ -2013,13 +2148,13 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>282526</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
         <x:v>21</x:v>
@@ -2027,29 +2162,71 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>20483</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C20" s="1">
+        <x:v>1564215</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:4">
+      <x:c r="A21" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C21" s="1">
+        <x:v>282526</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:4">
+      <x:c r="A22" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
+      <x:c r="B22" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C20" s="1">
+      <x:c r="C22" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:4">
+      <x:c r="A23" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C23" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
+      <x:c r="D23" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2069,7 +2246,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C12"/>
+  <x:dimension ref="A1:C14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2127,7 +2304,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>300000</x:v>
+        <x:v>402144</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>21</x:v>
@@ -2157,10 +2334,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>91847</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>21</x:v>
@@ -2168,10 +2345,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>21</x:v>
@@ -2179,10 +2356,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>3573369</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>21</x:v>
@@ -2190,23 +2367,45 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>20483</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B12" s="1">
+        <x:v>3573369</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3">
+      <x:c r="A13" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B12" s="1">
+      <x:c r="B13" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B14" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
+      <x:c r="C14" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2226,7 +2425,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B10"/>
+  <x:dimension ref="A1:B12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2271,7 +2470,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>300000</x:v>
+        <x:v>402144</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -2284,33 +2483,49 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>91847</x:v>
+        <x:v>850000</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>3573369</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B10" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:2">
+      <x:c r="A11" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B11" s="1">
+        <x:v>3573369</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:2">
+      <x:c r="A12" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B10" s="1">
+      <x:c r="B12" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>
@@ -2330,7 +2545,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C12"/>
+  <x:dimension ref="A1:C15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2396,78 +2611,111 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>13158948</x:v>
+        <x:v>102144</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>1075707</x:v>
+        <x:v>13158948</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>91847</x:v>
+        <x:v>1075707</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>161896</x:v>
+        <x:v>850000</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>2009154</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>1564215</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C12" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3">
+      <x:c r="A13" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="1">
+        <x:v>2009154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
+      <x:c r="B14" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="1">
+        <x:v>1564215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3">
+      <x:c r="A15" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C12" s="1">
+      <x:c r="C15" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -183,6 +183,21 @@
     <x:t>MI</x:t>
   </x:si>
   <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00915181</x:t>
   </x:si>
   <x:si>
@@ -190,21 +205,6 @@
   </x:si>
   <x:si>
     <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
   </x:si>
   <x:si>
     <x:t>MORRIS, NATE</x:t>
@@ -1081,48 +1081,48 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>300000</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>418060</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
@@ -1133,16 +1133,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>80948</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>21</x:v>
@@ -1150,22 +1150,22 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>102144</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>21</x:v>
@@ -1173,45 +1173,45 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>672092</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>41493</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>21</x:v>
@@ -1225,16 +1225,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>771658</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>21</x:v>
@@ -1248,16 +1248,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>91656</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>21</x:v>
@@ -1265,22 +1265,22 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>141263</x:v>
+        <x:v>161489</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>21</x:v>
@@ -1288,22 +1288,22 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>5031161</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>21</x:v>
@@ -1311,10 +1311,10 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>15</x:v>
@@ -1326,7 +1326,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>4697360</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1340,19 +1340,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>119644</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
@@ -1363,16 +1363,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>285008</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>21</x:v>
@@ -1380,22 +1380,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>30183</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>21</x:v>
@@ -1403,10 +1403,10 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>62</x:v>
@@ -1426,10 +1426,10 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>64</x:v>
@@ -1561,16 +1561,16 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>102144</x:v>
+        <x:v>161489</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>21</x:v>
@@ -1578,13 +1578,13 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>300000</x:v>
@@ -1595,10 +1595,10 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>11</x:v>
@@ -1612,10 +1612,10 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>11</x:v>
@@ -1983,10 +1983,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>102144</x:v>
+        <x:v>161489</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>21</x:v>
@@ -1997,7 +1997,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>300000</x:v>
@@ -2008,7 +2008,7 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>11</x:v>
@@ -2301,10 +2301,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>402144</x:v>
+        <x:v>461489</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>21</x:v>
@@ -2467,10 +2467,10 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>402144</x:v>
+        <x:v>461489</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -2600,10 +2600,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="B5" s="1" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>300000</x:v>
@@ -2614,10 +2614,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>102144</x:v>
+        <x:v>161489</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -2644,7 +2644,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>63</x:v>
@@ -2677,7 +2677,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>65</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -1280,7 +1280,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>161489</x:v>
+        <x:v>882245</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>21</x:v>
@@ -1570,7 +1570,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>161489</x:v>
+        <x:v>882245</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>21</x:v>
@@ -1986,7 +1986,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>161489</x:v>
+        <x:v>882245</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>21</x:v>
@@ -2304,7 +2304,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>461489</x:v>
+        <x:v>1182245</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>21</x:v>
@@ -2470,7 +2470,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>461489</x:v>
+        <x:v>1182245</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -2617,7 +2617,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>161489</x:v>
+        <x:v>882245</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -1280,7 +1280,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>882245</x:v>
+        <x:v>996447</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>21</x:v>
@@ -1570,7 +1570,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>882245</x:v>
+        <x:v>996447</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>21</x:v>
@@ -1986,7 +1986,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>882245</x:v>
+        <x:v>996447</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>21</x:v>
@@ -2304,7 +2304,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>1182245</x:v>
+        <x:v>1296447</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>21</x:v>
@@ -2470,7 +2470,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>1182245</x:v>
+        <x:v>1296447</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -2617,7 +2617,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>882245</x:v>
+        <x:v>996447</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -1280,7 +1280,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>996447</x:v>
+        <x:v>1052492</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>21</x:v>
@@ -1570,7 +1570,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>996447</x:v>
+        <x:v>1052492</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>21</x:v>
@@ -1986,7 +1986,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>996447</x:v>
+        <x:v>1052492</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>21</x:v>
@@ -2304,7 +2304,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>1296447</x:v>
+        <x:v>1352492</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>21</x:v>
@@ -2470,7 +2470,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>1296447</x:v>
+        <x:v>1352492</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -2617,7 +2617,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>996447</x:v>
+        <x:v>1052492</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -207,16 +207,31 @@
     <x:t>FULLER, CLAY</x:t>
   </x:si>
   <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
     <x:t>MORRIS, NATE</x:t>
   </x:si>
   <x:si>
     <x:t>KY</x:t>
   </x:si>
   <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
     <x:t>RICKETTS, PETE</x:t>
   </x:si>
   <x:si>
     <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -287,8 +302,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G34" totalsRowShown="0">
-  <x:autoFilter ref="A1:G34"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G39" totalsRowShown="0">
+  <x:autoFilter ref="A1:G39"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -303,8 +318,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E24" totalsRowShown="0">
-  <x:autoFilter ref="A1:E24"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E28" totalsRowShown="0">
+  <x:autoFilter ref="A1:E28"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -317,8 +332,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D23" totalsRowShown="0">
-  <x:autoFilter ref="A1:D23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D26" totalsRowShown="0">
+  <x:autoFilter ref="A1:D26"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -330,8 +345,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C14" totalsRowShown="0">
-  <x:autoFilter ref="A1:C14"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C15" totalsRowShown="0">
+  <x:autoFilter ref="A1:C15"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -342,8 +357,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B12" totalsRowShown="0">
-  <x:autoFilter ref="A1:B12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B13" totalsRowShown="0">
+  <x:autoFilter ref="A1:B13"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -353,8 +368,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C15" totalsRowShown="0">
-  <x:autoFilter ref="A1:C15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C18" totalsRowShown="0">
+  <x:autoFilter ref="A1:C18"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -652,13 +667,13 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G34"/>
+  <x:dimension ref="A1:G39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
     <x:col min="1" max="1" width="15.710625" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="24.282054" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="25.139196" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="29.424911" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="25.282054" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="23.424911" style="1" customWidth="1"/>
     <x:col min="6" max="6" width="13.853482" style="1" customWidth="1"/>
@@ -1409,16 +1424,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>850000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>21</x:v>
@@ -1432,18 +1447,133 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F34" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:7">
+      <x:c r="A35" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F35" s="1">
+        <x:v>850000</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:7">
+      <x:c r="A36" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F36" s="1">
+        <x:v>250000</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:7">
+      <x:c r="A37" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F37" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:7">
+      <x:c r="A38" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F38" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:7">
+      <x:c r="A39" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F39" s="1">
+        <x:v>1750000</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1463,11 +1593,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E24"/>
+  <x:dimension ref="A1:E28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
-    <x:col min="1" max="1" width="25.139196" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="29.424911" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="25.282054" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="23.424911" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="13.853482" style="1" customWidth="1"/>
@@ -1502,7 +1632,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>10049014</x:v>
+        <x:v>10399014</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
         <x:v>21</x:v>
@@ -1561,16 +1691,16 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>1052492</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>21</x:v>
@@ -1578,16 +1708,16 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>300000</x:v>
+        <x:v>1052492</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>21</x:v>
@@ -1595,16 +1725,16 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>285008</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>21</x:v>
@@ -1612,7 +1742,7 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>57</x:v>
@@ -1621,7 +1751,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>21</x:v>
@@ -1629,33 +1759,33 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>9985740</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>817066</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>12</x:v>
@@ -1663,16 +1793,16 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>2475786</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>12</x:v>
@@ -1680,33 +1810,33 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>557012</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>83860</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>21</x:v>
@@ -1714,16 +1844,16 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>850000</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>21</x:v>
@@ -1731,16 +1861,16 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>91847</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>21</x:v>
@@ -1748,16 +1878,16 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>161896</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>21</x:v>
@@ -1765,16 +1895,16 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>21</x:v>
@@ -1782,16 +1912,16 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>1543316</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>21</x:v>
@@ -1799,16 +1929,16 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>183312</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>21</x:v>
@@ -1816,16 +1946,16 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>1564215</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>21</x:v>
@@ -1833,16 +1963,16 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>282526</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>21</x:v>
@@ -1850,35 +1980,103 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>20483</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D24" s="1">
+        <x:v>183312</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:5">
+      <x:c r="A25" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D25" s="1">
+        <x:v>1564215</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:5">
+      <x:c r="A26" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D26" s="1">
+        <x:v>282526</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:5">
+      <x:c r="A27" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D27" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:5">
+      <x:c r="A28" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B24" s="1" t="s">
+      <x:c r="B28" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
+      <x:c r="C28" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D24" s="1">
+      <x:c r="D28" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E24" s="1" t="s">
+      <x:c r="E28" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1898,7 +2096,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D23"/>
+  <x:dimension ref="A1:D26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1930,7 +2128,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>10049014</x:v>
+        <x:v>10399014</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>21</x:v>
@@ -1980,13 +2178,13 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>1052492</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>21</x:v>
@@ -1994,13 +2192,13 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>300000</x:v>
+        <x:v>1052492</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>21</x:v>
@@ -2008,13 +2206,13 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>315191</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>21</x:v>
@@ -2022,27 +2220,27 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>9985740</x:v>
+        <x:v>315191</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>817066</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>12</x:v>
@@ -2050,13 +2248,13 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>2475786</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
         <x:v>12</x:v>
@@ -2064,27 +2262,27 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>557012</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>83860</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>21</x:v>
@@ -2092,13 +2290,13 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>850000</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>21</x:v>
@@ -2109,10 +2307,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>91847</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>21</x:v>
@@ -2120,13 +2318,13 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>161896</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>21</x:v>
@@ -2137,10 +2335,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>350000</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>21</x:v>
@@ -2148,13 +2346,13 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>1543316</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
         <x:v>21</x:v>
@@ -2162,13 +2360,13 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>183312</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>21</x:v>
@@ -2176,13 +2374,13 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>1564215</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>21</x:v>
@@ -2190,13 +2388,13 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>282526</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>21</x:v>
@@ -2204,29 +2402,71 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>20483</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C23" s="1">
+        <x:v>1564215</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:4">
+      <x:c r="A24" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C24" s="1">
+        <x:v>282526</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:4">
+      <x:c r="A25" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B23" s="1" t="s">
+      <x:c r="B25" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C23" s="1">
+      <x:c r="C25" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:4">
+      <x:c r="A26" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C26" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
+      <x:c r="D26" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2246,7 +2486,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C14"/>
+  <x:dimension ref="A1:C15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2271,7 +2511,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>10049014</x:v>
+        <x:v>10399014</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>21</x:v>
@@ -2304,7 +2544,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>1352492</x:v>
+        <x:v>1702492</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>21</x:v>
@@ -2334,7 +2574,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>850000</x:v>
@@ -2345,10 +2585,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>91847</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>21</x:v>
@@ -2356,10 +2596,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>21</x:v>
@@ -2367,10 +2607,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>21</x:v>
@@ -2378,10 +2618,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>3573369</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>21</x:v>
@@ -2389,13 +2629,13 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>20483</x:v>
+        <x:v>5323369</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -2403,9 +2643,20 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3">
+      <x:c r="A15" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B15" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
+      <x:c r="C15" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2425,7 +2676,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B12"/>
+  <x:dimension ref="A1:B13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2446,7 +2697,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>10049014</x:v>
+        <x:v>10399014</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -2470,7 +2721,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>1352492</x:v>
+        <x:v>1702492</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -2483,7 +2734,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>850000</x:v>
@@ -2491,41 +2742,49 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>91847</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>3573369</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B12" s="1">
+        <x:v>5323369</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:2">
+      <x:c r="A13" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B12" s="1">
+      <x:c r="B13" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>
@@ -2545,7 +2804,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C15"/>
+  <x:dimension ref="A1:C18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2578,13 +2837,13 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>836118</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
@@ -2592,98 +2851,98 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>2232549</x:v>
+        <x:v>836118</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>300000</x:v>
+        <x:v>2232549</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>1052492</x:v>
+        <x:v>650000</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>13158948</x:v>
+        <x:v>1052492</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>1075707</x:v>
+        <x:v>13158948</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>850000</x:v>
+        <x:v>1075707</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>91847</x:v>
+        <x:v>850000</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>161896</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>350000</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -2691,31 +2950,64 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>2009154</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>1564215</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" s="1">
+        <x:v>2009154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="1">
+        <x:v>1750000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
+      <x:c r="B17" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C17" s="1">
+        <x:v>1564215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C15" s="1">
+      <x:c r="C18" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -183,10 +183,13 @@
     <x:t>MI</x:t>
   </x:si>
   <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
     <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
   </x:si>
   <x:si>
     <x:t>KELLY, ROBIN</x:t>
@@ -302,8 +305,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G39" totalsRowShown="0">
-  <x:autoFilter ref="A1:G39"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G40" totalsRowShown="0">
+  <x:autoFilter ref="A1:G40"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -318,8 +321,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E28" totalsRowShown="0">
-  <x:autoFilter ref="A1:E28"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E29" totalsRowShown="0">
+  <x:autoFilter ref="A1:E29"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -332,8 +335,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D26" totalsRowShown="0">
-  <x:autoFilter ref="A1:D26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D27" totalsRowShown="0">
+  <x:autoFilter ref="A1:D27"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -345,8 +348,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C15" totalsRowShown="0">
-  <x:autoFilter ref="A1:C15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C16" totalsRowShown="0">
+  <x:autoFilter ref="A1:C16"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -667,7 +670,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G39"/>
+  <x:dimension ref="A1:G40"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1295,10 +1298,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>1052492</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
@@ -1309,16 +1312,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>41493</x:v>
+        <x:v>1052492</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>21</x:v>
@@ -1332,19 +1335,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>119644</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
@@ -1355,19 +1358,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>285008</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
@@ -1378,16 +1381,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>21</x:v>
@@ -1395,22 +1398,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B32" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C32" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>300000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>21</x:v>
@@ -1418,22 +1421,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>350000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>21</x:v>
@@ -1441,19 +1444,19 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="1">
         <x:v>350000</x:v>
@@ -1464,10 +1467,10 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>63</x:v>
@@ -1476,10 +1479,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>850000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>21</x:v>
@@ -1487,22 +1490,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>250000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>21</x:v>
@@ -1510,22 +1513,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>21</x:v>
@@ -1533,10 +1536,10 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>68</x:v>
@@ -1545,7 +1548,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F38" s="1">
         <x:v>350000</x:v>
@@ -1556,24 +1559,47 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F39" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:7">
+      <x:c r="A40" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F39" s="1">
+      <x:c r="F40" s="1">
         <x:v>1750000</x:v>
       </x:c>
-      <x:c r="G39" s="1" t="s">
+      <x:c r="G40" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1593,7 +1619,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E28"/>
+  <x:dimension ref="A1:E29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1691,7 +1717,7 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>16</x:v>
@@ -1717,24 +1743,24 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>1052492</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>300000</x:v>
+        <x:v>1052492</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>21</x:v>
@@ -1742,16 +1768,16 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>285008</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>21</x:v>
@@ -1759,16 +1785,16 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>21</x:v>
@@ -1776,33 +1802,33 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>9985740</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>817066</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>12</x:v>
@@ -1810,16 +1836,16 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>2475786</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>12</x:v>
@@ -1827,33 +1853,33 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>557012</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>83860</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>21</x:v>
@@ -1861,16 +1887,16 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>850000</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>21</x:v>
@@ -1878,16 +1904,16 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>350000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>21</x:v>
@@ -1895,16 +1921,16 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>21</x:v>
@@ -1912,16 +1938,16 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>91847</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>21</x:v>
@@ -1929,16 +1955,16 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>21</x:v>
@@ -1946,16 +1972,16 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>21</x:v>
@@ -1963,16 +1989,16 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>1750000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>21</x:v>
@@ -1980,16 +2006,16 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>21</x:v>
@@ -1997,16 +2023,16 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>21</x:v>
@@ -2014,16 +2040,16 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>1564215</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>21</x:v>
@@ -2031,16 +2057,16 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>282526</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>21</x:v>
@@ -2048,24 +2074,24 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>20483</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>47</x:v>
@@ -2074,9 +2100,26 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D28" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:5">
+      <x:c r="A29" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D29" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E28" s="1" t="s">
+      <x:c r="E29" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2096,7 +2139,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D26"/>
+  <x:dimension ref="A1:D27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2198,21 +2241,21 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>1052492</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>300000</x:v>
+        <x:v>1052492</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>21</x:v>
@@ -2220,13 +2263,13 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>315191</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>21</x:v>
@@ -2234,27 +2277,27 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>9985740</x:v>
+        <x:v>315191</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>817066</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
         <x:v>12</x:v>
@@ -2262,13 +2305,13 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>2475786</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
         <x:v>12</x:v>
@@ -2276,27 +2319,27 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>557012</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>83860</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>21</x:v>
@@ -2304,13 +2347,13 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>850000</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>21</x:v>
@@ -2321,10 +2364,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>600000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>21</x:v>
@@ -2335,10 +2378,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>91847</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>21</x:v>
@@ -2346,13 +2389,13 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
         <x:v>21</x:v>
@@ -2360,13 +2403,13 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>21</x:v>
@@ -2377,10 +2420,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>1750000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>21</x:v>
@@ -2388,13 +2431,13 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>21</x:v>
@@ -2402,13 +2445,13 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>21</x:v>
@@ -2416,13 +2459,13 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>1564215</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>21</x:v>
@@ -2430,13 +2473,13 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>282526</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>21</x:v>
@@ -2444,16 +2487,16 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>20483</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
@@ -2464,9 +2507,23 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C26" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:4">
+      <x:c r="A27" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C27" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
+      <x:c r="D27" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2486,7 +2543,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C15"/>
+  <x:dimension ref="A1:C16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2544,21 +2601,21 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>1702492</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>13278592</x:v>
+        <x:v>1702492</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -2566,18 +2623,18 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>956063</x:v>
+        <x:v>13278592</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>850000</x:v>
+        <x:v>956063</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>21</x:v>
@@ -2585,10 +2642,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>600000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>21</x:v>
@@ -2596,10 +2653,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>91847</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>21</x:v>
@@ -2607,10 +2664,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>21</x:v>
@@ -2618,10 +2675,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>21</x:v>
@@ -2629,10 +2686,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>5323369</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>21</x:v>
@@ -2640,13 +2697,13 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>20483</x:v>
+        <x:v>5323369</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -2654,9 +2711,20 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B15" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B16" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="C16" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2721,7 +2789,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>1702492</x:v>
+        <x:v>1758537</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -2734,7 +2802,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>850000</x:v>
@@ -2742,7 +2810,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>600000</x:v>
@@ -2766,7 +2834,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>350000</x:v>
@@ -2837,7 +2905,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>38</x:v>
@@ -2870,7 +2938,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>55</x:v>
@@ -2887,7 +2955,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>1052492</x:v>
+        <x:v>1108537</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -2914,10 +2982,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>850000</x:v>
@@ -2925,10 +2993,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>600000</x:v>
@@ -2958,10 +3026,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>350000</x:v>
@@ -2980,7 +3048,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>32</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,6 +42,51 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
@@ -69,9 +114,6 @@
     <x:t>STRATTON, JULIANA</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00836221</x:t>
   </x:si>
   <x:si>
@@ -84,9 +126,6 @@
     <x:t>AR</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
     <x:t>MOORE, TIM</x:t>
   </x:si>
   <x:si>
@@ -117,9 +156,6 @@
     <x:t>08</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
     <x:t>GOBER, CHRIS</x:t>
   </x:si>
   <x:si>
@@ -186,9 +222,6 @@
     <x:t>SCOTT, DAVID ALBERT</x:t>
   </x:si>
   <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLARK, JASMINE</x:t>
   </x:si>
   <x:si>
@@ -201,40 +234,7 @@
     <x:t>KRISHNAMOORTHI, S</x:t>
   </x:si>
   <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -723,7 +723,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>817066</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -740,13 +740,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F3" s="1">
-        <x:v>1803694</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -763,13 +763,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F4" s="1">
-        <x:v>5168736</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -777,298 +777,298 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="B5" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>418058</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>558813</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F8" s="1">
+        <x:v>817066</x:v>
+      </x:c>
+      <x:c r="G8" s="1" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="F8" s="1">
-        <x:v>1673736</x:v>
-      </x:c>
-      <x:c r="G8" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>771658</x:v>
+        <x:v>1803694</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>91656</x:v>
+        <x:v>5168736</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>141263</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="F12" s="1">
-        <x:v>5017853</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F13" s="1">
-        <x:v>83860</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F14" s="1">
-        <x:v>515519</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>1564215</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>1012792</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>20483</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1076,45 +1076,45 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B18" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C18" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="F18" s="1">
-        <x:v>91847</x:v>
+        <x:v>5017853</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>672092</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1122,22 +1122,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>4697360</x:v>
+        <x:v>515519</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1145,160 +1145,160 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>418060</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>80948</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>771658</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>91656</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>141263</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>5031161</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>56045</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>12</x:v>
@@ -1306,68 +1306,68 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>1052492</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>41493</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>119644</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1375,232 +1375,232 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>285008</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>30183</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>300000</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>350000</x:v>
+        <x:v>2010471</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>350000</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>850000</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>250000</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>350000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>1750000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1649,478 +1649,478 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>10399014</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>1052492</x:v>
+        <x:v>2010471</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>285008</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>30183</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="C18" s="1" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>250000</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>1750000</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>1564215</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2165,366 +2165,366 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>10399014</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>1052492</x:v>
+        <x:v>2010471</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>315191</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="B17" s="1" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1750000</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1564215</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2565,167 +2565,167 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>10399014</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2232549</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>1702492</x:v>
+        <x:v>2660471</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>13278592</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>956063</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>5323369</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2762,7 +2762,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>10399014</x:v>
@@ -2770,7 +2770,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
@@ -2778,7 +2778,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2232549</x:v>
@@ -2786,15 +2786,15 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>1758537</x:v>
+        <x:v>2716516</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>14234655</x:v>
@@ -2802,7 +2802,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>850000</x:v>
@@ -2810,7 +2810,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>600000</x:v>
@@ -2818,7 +2818,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>91847</x:v>
@@ -2826,7 +2826,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>161896</x:v>
@@ -2834,7 +2834,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>350000</x:v>
@@ -2842,7 +2842,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>5323369</x:v>
@@ -2850,7 +2850,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>1033275</x:v>
@@ -2894,10 +2894,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>10049014</x:v>
@@ -2905,10 +2905,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>350000</x:v>
@@ -2916,10 +2916,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>836118</x:v>
@@ -2927,10 +2927,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>2232549</x:v>
@@ -2938,10 +2938,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>650000</x:v>
@@ -2949,21 +2949,21 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>1108537</x:v>
+        <x:v>2066516</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>13158948</x:v>
@@ -2971,10 +2971,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>1075707</x:v>
@@ -2982,10 +2982,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>850000</x:v>
@@ -2993,10 +2993,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>600000</x:v>
@@ -3004,10 +3004,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>91847</x:v>
@@ -3015,10 +3015,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>161896</x:v>
@@ -3026,10 +3026,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>350000</x:v>
@@ -3037,10 +3037,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>2009154</x:v>
@@ -3048,10 +3048,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>1750000</x:v>
@@ -3059,10 +3059,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1564215</x:v>
@@ -3070,10 +3070,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1033275</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,24 +42,177 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATRONIS, JIMMY JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALKINSHAW, JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKARSKY, STELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00915181</x:t>
   </x:si>
   <x:si>
     <x:t>FELLOWSHIP PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
     <x:t>COLLINS, MICHAEL A JR</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
     <x:t>MORRIS, NATE</x:t>
   </x:si>
   <x:si>
@@ -82,159 +235,6 @@
   </x:si>
   <x:si>
     <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATRONIS, JIMMY JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALKINSHAW, JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKARSKY, STELLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00894428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROGERS, MICHAEL J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -723,7 +723,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>350000</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -740,13 +740,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>850000</x:v>
+        <x:v>1803694</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -763,13 +763,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>250000</x:v>
+        <x:v>5168736</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -777,298 +777,298 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>350000</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>350000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>1750000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>817066</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>1803694</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>5168736</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="F11" s="1">
-        <x:v>418058</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>80948</x:v>
+        <x:v>5017853</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>558813</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>1673736</x:v>
+        <x:v>515519</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="F15" s="1">
-        <x:v>771658</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>91656</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="F17" s="1">
-        <x:v>141263</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1076,45 +1076,45 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>5017853</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>83860</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1122,22 +1122,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>515519</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1145,160 +1145,160 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>1564215</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>1012792</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>20483</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>91847</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>672092</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>4697360</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>418060</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>12</x:v>
@@ -1306,68 +1306,68 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>80948</x:v>
+        <x:v>2067216</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>771658</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>91656</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1375,232 +1375,232 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>141263</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>5031161</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>56045</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>2010471</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="F35" s="1">
-        <x:v>41493</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>119644</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>285008</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>30183</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>300000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1649,478 +1649,478 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>10399014</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>2010471</x:v>
+        <x:v>2067216</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>285008</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>30183</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>250000</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>1750000</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>1564215</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2165,366 +2165,366 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>10399014</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>2010471</x:v>
+        <x:v>2067216</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>315191</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1750000</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1564215</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2565,167 +2565,167 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>10399014</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2232549</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>2660471</x:v>
+        <x:v>2717216</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>13278592</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>956063</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>5323369</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2762,7 +2762,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>10399014</x:v>
@@ -2770,7 +2770,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
@@ -2778,7 +2778,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2232549</x:v>
@@ -2786,15 +2786,15 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>2716516</x:v>
+        <x:v>2773261</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>14234655</x:v>
@@ -2802,7 +2802,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>850000</x:v>
@@ -2810,7 +2810,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>600000</x:v>
@@ -2818,7 +2818,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>91847</x:v>
@@ -2826,7 +2826,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>161896</x:v>
@@ -2834,7 +2834,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>350000</x:v>
@@ -2842,7 +2842,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>5323369</x:v>
@@ -2850,7 +2850,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>1033275</x:v>
@@ -2894,10 +2894,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>10049014</x:v>
@@ -2905,10 +2905,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>350000</x:v>
@@ -2916,10 +2916,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>836118</x:v>
@@ -2927,10 +2927,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>2232549</x:v>
@@ -2938,10 +2938,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>650000</x:v>
@@ -2949,21 +2949,21 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>2066516</x:v>
+        <x:v>2123261</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>13158948</x:v>
@@ -2971,10 +2971,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>1075707</x:v>
@@ -2982,10 +2982,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>850000</x:v>
@@ -2993,10 +2993,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>600000</x:v>
@@ -3004,10 +3004,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>91847</x:v>
@@ -3015,10 +3015,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>161896</x:v>
@@ -3026,10 +3026,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>350000</x:v>
@@ -3037,10 +3037,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>2009154</x:v>
@@ -3048,10 +3048,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>1750000</x:v>
@@ -3059,10 +3059,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1564215</x:v>
@@ -3070,10 +3070,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1033275</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,6 +42,63 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
@@ -69,9 +126,6 @@
     <x:t>STRATTON, JULIANA</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00836221</x:t>
   </x:si>
   <x:si>
@@ -84,15 +138,9 @@
     <x:t>AR</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
     <x:t>MOORE, TIM</x:t>
   </x:si>
   <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
     <x:t>NC</x:t>
   </x:si>
   <x:si>
@@ -117,9 +165,6 @@
     <x:t>08</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
     <x:t>GOBER, CHRIS</x:t>
   </x:si>
   <x:si>
@@ -132,12 +177,6 @@
     <x:t>22</x:t>
   </x:si>
   <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00848440</x:t>
   </x:si>
   <x:si>
@@ -186,9 +225,6 @@
     <x:t>SCOTT, DAVID ALBERT</x:t>
   </x:si>
   <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLARK, JASMINE</x:t>
   </x:si>
   <x:si>
@@ -199,42 +235,6 @@
   </x:si>
   <x:si>
     <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -723,7 +723,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>817066</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -743,10 +743,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>1803694</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -760,16 +760,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>5168736</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -777,298 +777,298 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="F5" s="1">
-        <x:v>418058</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>80948</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>558813</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>1673736</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>771658</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>91656</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>141263</x:v>
+        <x:v>1803694</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>5017853</x:v>
+        <x:v>5168736</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>83860</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
+      <x:c r="D14" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F14" s="1">
-        <x:v>515519</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>1564215</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>1012792</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>20483</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1076,45 +1076,45 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>91847</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>672092</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1122,22 +1122,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F20" s="1">
-        <x:v>4697360</x:v>
+        <x:v>5017853</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1145,229 +1145,229 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>418060</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>80948</x:v>
+        <x:v>515519</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>771658</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>91656</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>141263</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>5031161</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>56045</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>2067216</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>41493</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B30" s="1" t="s">
+      <x:c r="D30" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F30" s="1">
-        <x:v>119644</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1375,232 +1375,232 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>285008</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>30183</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>300000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>350000</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>350000</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>850000</x:v>
+        <x:v>2067216</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>250000</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>350000</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>350000</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>1750000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1649,478 +1649,478 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>10399014</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>2067216</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>285008</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>30183</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>250000</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>1750000</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>1564215</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2165,366 +2165,366 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>10399014</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2067216</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>315191</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1750000</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1564215</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2565,167 +2565,167 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>10399014</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2232549</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2717216</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>13278592</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>956063</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>5323369</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2762,7 +2762,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>10399014</x:v>
@@ -2770,7 +2770,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
@@ -2778,7 +2778,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2232549</x:v>
@@ -2786,7 +2786,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>2773261</x:v>
@@ -2794,7 +2794,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>14234655</x:v>
@@ -2802,7 +2802,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>850000</x:v>
@@ -2810,7 +2810,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>600000</x:v>
@@ -2818,7 +2818,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>91847</x:v>
@@ -2826,7 +2826,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>161896</x:v>
@@ -2834,7 +2834,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>350000</x:v>
@@ -2842,7 +2842,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>5323369</x:v>
@@ -2850,7 +2850,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>1033275</x:v>
@@ -2894,10 +2894,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>10049014</x:v>
@@ -2905,10 +2905,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>350000</x:v>
@@ -2916,10 +2916,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>836118</x:v>
@@ -2927,10 +2927,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>2232549</x:v>
@@ -2938,10 +2938,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>650000</x:v>
@@ -2949,10 +2949,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2123261</x:v>
@@ -2960,10 +2960,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>13158948</x:v>
@@ -2971,10 +2971,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>1075707</x:v>
@@ -2982,10 +2982,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>850000</x:v>
@@ -2993,10 +2993,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>600000</x:v>
@@ -3004,10 +3004,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>91847</x:v>
@@ -3015,10 +3015,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>161896</x:v>
@@ -3026,10 +3026,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>350000</x:v>
@@ -3037,10 +3037,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>2009154</x:v>
@@ -3048,10 +3048,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>1750000</x:v>
@@ -3059,10 +3059,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1564215</x:v>
@@ -3070,10 +3070,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1033275</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,6 +42,165 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATRONIS, JIMMY JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALKINSHAW, JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKARSKY, STELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00915181</x:t>
   </x:si>
   <x:si>
@@ -51,24 +210,6 @@
     <x:t>FULLER, CLAY</x:t>
   </x:si>
   <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
     <x:t>COLLINS, MICHAEL A JR</x:t>
   </x:si>
   <x:si>
@@ -94,147 +235,6 @@
   </x:si>
   <x:si>
     <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATRONIS, JIMMY JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALKINSHAW, JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKARSKY, STELLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00894428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROGERS, MICHAEL J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -723,7 +723,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>300000</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -743,10 +743,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>350000</x:v>
+        <x:v>1803694</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -760,16 +760,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>350000</x:v>
+        <x:v>5168736</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -777,298 +777,298 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>850000</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>250000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>350000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>350000</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>1750000</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>817066</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="F11" s="1">
-        <x:v>1803694</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>5168736</x:v>
+        <x:v>5017853</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>418058</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>80948</x:v>
+        <x:v>515519</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>558813</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>1673736</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>771658</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1076,45 +1076,45 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>91656</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>141263</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1122,22 +1122,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>5017853</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1145,229 +1145,229 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>83860</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>515519</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>1564215</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>1012792</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>20483</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>91847</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>672092</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>4697360</x:v>
+        <x:v>2067216</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>418060</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>80948</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1375,232 +1375,232 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>771658</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>91656</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>141263</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>5031161</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F35" s="1">
-        <x:v>56045</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>2067216</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>41493</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>119644</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="E39" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="F39" s="1">
-        <x:v>285008</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>30183</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1649,478 +1649,478 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>10399014</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>2067216</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>285008</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>30183</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>250000</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>1750000</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>1564215</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2165,366 +2165,366 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>10399014</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2067216</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>315191</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1750000</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1564215</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2565,167 +2565,167 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>10399014</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2232549</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2717216</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>13278592</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>956063</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>5323369</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2762,7 +2762,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>10399014</x:v>
@@ -2770,7 +2770,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
@@ -2778,7 +2778,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2232549</x:v>
@@ -2786,7 +2786,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>2773261</x:v>
@@ -2794,7 +2794,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>14234655</x:v>
@@ -2802,7 +2802,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>850000</x:v>
@@ -2810,7 +2810,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>600000</x:v>
@@ -2818,7 +2818,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>91847</x:v>
@@ -2826,7 +2826,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>161896</x:v>
@@ -2834,7 +2834,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>350000</x:v>
@@ -2842,7 +2842,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>5323369</x:v>
@@ -2850,7 +2850,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>1033275</x:v>
@@ -2894,10 +2894,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>10049014</x:v>
@@ -2905,10 +2905,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>350000</x:v>
@@ -2916,10 +2916,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>836118</x:v>
@@ -2927,10 +2927,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>2232549</x:v>
@@ -2938,10 +2938,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>650000</x:v>
@@ -2949,10 +2949,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2123261</x:v>
@@ -2960,10 +2960,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>13158948</x:v>
@@ -2971,10 +2971,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>1075707</x:v>
@@ -2982,10 +2982,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>850000</x:v>
@@ -2993,10 +2993,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>600000</x:v>
@@ -3004,10 +3004,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>91847</x:v>
@@ -3015,10 +3015,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>161896</x:v>
@@ -3026,10 +3026,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>350000</x:v>
@@ -3037,10 +3037,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>2009154</x:v>
@@ -3048,10 +3048,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>1750000</x:v>
@@ -3059,10 +3059,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1564215</x:v>
@@ -3070,10 +3070,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1033275</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -305,8 +305,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G40" totalsRowShown="0">
-  <x:autoFilter ref="A1:G40"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G41" totalsRowShown="0">
+  <x:autoFilter ref="A1:G41"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -670,7 +670,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G40"/>
+  <x:dimension ref="A1:G41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1358,19 +1358,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>119644</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
@@ -1381,19 +1381,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>285008</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
@@ -1404,7 +1404,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>58</x:v>
@@ -1413,7 +1413,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>21</x:v>
@@ -1421,22 +1421,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>300000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>21</x:v>
@@ -1450,16 +1450,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>350000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>21</x:v>
@@ -1473,13 +1473,13 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="1">
         <x:v>350000</x:v>
@@ -1496,16 +1496,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>850000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>21</x:v>
@@ -1519,16 +1519,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>250000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>21</x:v>
@@ -1542,7 +1542,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
         <x:v>16</x:v>
@@ -1551,7 +1551,7 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>21</x:v>
@@ -1565,13 +1565,13 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F39" s="1">
         <x:v>350000</x:v>
@@ -1588,18 +1588,41 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F40" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:7">
+      <x:c r="A41" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F40" s="1">
+      <x:c r="F41" s="1">
         <x:v>1750000</x:v>
       </x:c>
-      <x:c r="G40" s="1" t="s">
+      <x:c r="G41" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2066,7 +2089,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>1564215</x:v>
+        <x:v>1611377</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>21</x:v>
@@ -2479,7 +2502,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>1564215</x:v>
+        <x:v>1611377</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>21</x:v>
@@ -2700,7 +2723,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>5323369</x:v>
+        <x:v>5370531</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>21</x:v>
@@ -2845,7 +2868,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>5323369</x:v>
+        <x:v>5370531</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
@@ -3065,7 +3088,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>1564215</x:v>
+        <x:v>1611377</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -1321,7 +1321,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>2067216</x:v>
+        <x:v>2123261</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>21</x:v>
@@ -1367,7 +1367,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>47162</x:v>
+        <x:v>94324</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>21</x:v>
@@ -1783,7 +1783,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>2067216</x:v>
+        <x:v>2123261</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>21</x:v>
@@ -2089,7 +2089,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>1611377</x:v>
+        <x:v>1658539</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>21</x:v>
@@ -2278,7 +2278,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>2067216</x:v>
+        <x:v>2123261</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>21</x:v>
@@ -2502,7 +2502,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>1611377</x:v>
+        <x:v>1658539</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>21</x:v>
@@ -2635,7 +2635,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>2717216</x:v>
+        <x:v>2773261</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>21</x:v>
@@ -2723,7 +2723,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>5370531</x:v>
+        <x:v>5417693</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>21</x:v>
@@ -2812,7 +2812,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>2773261</x:v>
+        <x:v>2829306</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -2868,7 +2868,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>5370531</x:v>
+        <x:v>5417693</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
@@ -2978,7 +2978,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>2123261</x:v>
+        <x:v>2179306</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -3088,7 +3088,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>1611377</x:v>
+        <x:v>1658539</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -183,15 +183,27 @@
     <x:t>MI</x:t>
   </x:si>
   <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
     <x:t>SCOTT, DAVID ALBERT</x:t>
   </x:si>
   <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLARK, JASMINE</x:t>
   </x:si>
   <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
     <x:t>KELLY, ROBIN</x:t>
   </x:si>
   <x:si>
@@ -199,18 +211,6 @@
   </x:si>
   <x:si>
     <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
   </x:si>
   <x:si>
     <x:t>MORRIS, NATE</x:t>
@@ -1099,45 +1099,45 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>672092</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>4697360</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1191,22 +1191,22 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>771658</x:v>
+        <x:v>2648216</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>21</x:v>
@@ -1214,45 +1214,45 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>91656</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>141263</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>21</x:v>
@@ -1266,16 +1266,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>5031161</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>21</x:v>
@@ -1283,25 +1283,25 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>56045</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
@@ -1312,16 +1312,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>2123261</x:v>
+        <x:v>94324</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>21</x:v>
@@ -1329,22 +1329,22 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>41493</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>21</x:v>
@@ -1352,22 +1352,22 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>94324</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>21</x:v>
@@ -1375,45 +1375,45 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>119644</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F32" s="1">
-        <x:v>285008</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>21</x:v>
@@ -1421,68 +1421,68 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>30183</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>300000</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C35" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>350000</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>21</x:v>
@@ -1490,22 +1490,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>21</x:v>
@@ -1513,10 +1513,10 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>64</x:v>
@@ -1536,10 +1536,10 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>66</x:v>
@@ -1559,10 +1559,10 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>68</x:v>
@@ -1582,10 +1582,10 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>69</x:v>
@@ -1605,10 +1605,10 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>71</x:v>
@@ -1740,13 +1740,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>350000</x:v>
@@ -1757,13 +1757,13 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>56045</x:v>
@@ -1774,16 +1774,16 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>2123261</x:v>
+        <x:v>2648216</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>21</x:v>
@@ -1791,13 +1791,13 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>300000</x:v>
@@ -1808,10 +1808,10 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>11</x:v>
@@ -1825,10 +1825,10 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>11</x:v>
@@ -2247,7 +2247,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>350000</x:v>
@@ -2261,7 +2261,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>56045</x:v>
@@ -2275,10 +2275,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>2123261</x:v>
+        <x:v>2648216</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>21</x:v>
@@ -2289,7 +2289,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>300000</x:v>
@@ -2300,7 +2300,7 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>11</x:v>
@@ -2621,7 +2621,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>56045</x:v>
@@ -2632,10 +2632,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>2773261</x:v>
+        <x:v>3298216</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>21</x:v>
@@ -2809,10 +2809,10 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>2829306</x:v>
+        <x:v>3354261</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -2928,7 +2928,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>38</x:v>
@@ -2961,10 +2961,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>650000</x:v>
@@ -2975,10 +2975,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>2179306</x:v>
+        <x:v>2704261</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -3005,7 +3005,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>65</x:v>
@@ -3016,7 +3016,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>67</x:v>
@@ -3049,7 +3049,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>70</x:v>
@@ -3071,7 +3071,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>32</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -183,6 +183,33 @@
     <x:t>MI</x:t>
   </x:si>
   <x:si>
+    <x:t>TORRES, RITCHIE JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00915181</x:t>
   </x:si>
   <x:si>
@@ -192,25 +219,7 @@
     <x:t>FULLER, CLAY</x:t>
   </x:si>
   <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
     <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
   </x:si>
   <x:si>
     <x:t>MORRIS, NATE</x:t>
@@ -305,8 +314,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G41" totalsRowShown="0">
-  <x:autoFilter ref="A1:G41"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G42" totalsRowShown="0">
+  <x:autoFilter ref="A1:G42"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -321,8 +330,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E29" totalsRowShown="0">
-  <x:autoFilter ref="A1:E29"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E30" totalsRowShown="0">
+  <x:autoFilter ref="A1:E30"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -335,8 +344,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D27" totalsRowShown="0">
-  <x:autoFilter ref="A1:D27"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D28" totalsRowShown="0">
+  <x:autoFilter ref="A1:D28"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -348,8 +357,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C16" totalsRowShown="0">
-  <x:autoFilter ref="A1:C16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C17" totalsRowShown="0">
+  <x:autoFilter ref="A1:C17"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -360,8 +369,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B13" totalsRowShown="0">
-  <x:autoFilter ref="A1:B13"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B14" totalsRowShown="0">
+  <x:autoFilter ref="A1:B14"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -371,8 +380,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C18" totalsRowShown="0">
-  <x:autoFilter ref="A1:C18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C19" totalsRowShown="0">
+  <x:autoFilter ref="A1:C19"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -670,7 +679,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G41"/>
+  <x:dimension ref="A1:G42"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1099,45 +1108,45 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>300000</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>56045</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1191,22 +1200,22 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>2648216</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>21</x:v>
@@ -1214,45 +1223,45 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>672092</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>41493</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>21</x:v>
@@ -1266,16 +1275,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>771658</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>21</x:v>
@@ -1283,22 +1292,22 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>91656</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>21</x:v>
@@ -1312,39 +1321,39 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>94324</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>141263</x:v>
+        <x:v>2704261</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>21</x:v>
@@ -1352,22 +1361,22 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>5031161</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>21</x:v>
@@ -1375,22 +1384,22 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>350000</x:v>
+        <x:v>141486</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>21</x:v>
@@ -1398,48 +1407,48 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>350000</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>4697360</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
@@ -1450,39 +1459,39 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>119644</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>285008</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>21</x:v>
@@ -1490,22 +1499,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>30183</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>21</x:v>
@@ -1513,22 +1522,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>850000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>21</x:v>
@@ -1536,22 +1545,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>250000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>21</x:v>
@@ -1559,22 +1568,22 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>21</x:v>
@@ -1582,13 +1591,13 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
         <x:v>16</x:v>
@@ -1605,24 +1614,47 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F41" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:7">
+      <x:c r="A42" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F41" s="1">
+      <x:c r="F42" s="1">
         <x:v>1750000</x:v>
       </x:c>
-      <x:c r="G41" s="1" t="s">
+      <x:c r="G42" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1642,7 +1674,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E29"/>
+  <x:dimension ref="A1:E30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1740,13 +1772,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>350000</x:v>
@@ -1757,13 +1789,13 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>56045</x:v>
@@ -1780,10 +1812,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>2648216</x:v>
+        <x:v>2704261</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>21</x:v>
@@ -1791,13 +1823,13 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>300000</x:v>
@@ -1808,10 +1840,10 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>11</x:v>
@@ -1825,10 +1857,10 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>11</x:v>
@@ -1927,13 +1959,13 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>850000</x:v>
@@ -1944,13 +1976,13 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>350000</x:v>
@@ -1961,13 +1993,13 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>250000</x:v>
@@ -2012,13 +2044,13 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>350000</x:v>
@@ -2029,16 +2061,16 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>1750000</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>21</x:v>
@@ -2046,16 +2078,16 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>21</x:v>
@@ -2063,16 +2095,16 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>21</x:v>
@@ -2080,16 +2112,16 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>1658539</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>21</x:v>
@@ -2097,16 +2129,16 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>282526</x:v>
+        <x:v>1705701</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>21</x:v>
@@ -2114,24 +2146,24 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>20483</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>47</x:v>
@@ -2140,9 +2172,26 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D29" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:5">
+      <x:c r="A30" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D30" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E29" s="1" t="s">
+      <x:c r="E30" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2162,7 +2211,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D27"/>
+  <x:dimension ref="A1:D28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2247,7 +2296,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>350000</x:v>
@@ -2261,7 +2310,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>56045</x:v>
@@ -2275,10 +2324,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>2648216</x:v>
+        <x:v>2704261</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>21</x:v>
@@ -2289,7 +2338,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>300000</x:v>
@@ -2300,7 +2349,7 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>11</x:v>
@@ -2387,7 +2436,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>850000</x:v>
@@ -2401,7 +2450,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>600000</x:v>
@@ -2443,7 +2492,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>350000</x:v>
@@ -2454,13 +2503,13 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>1750000</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>21</x:v>
@@ -2468,13 +2517,13 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>21</x:v>
@@ -2482,13 +2531,13 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>21</x:v>
@@ -2496,13 +2545,13 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>1658539</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>21</x:v>
@@ -2510,13 +2559,13 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>282526</x:v>
+        <x:v>1705701</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>21</x:v>
@@ -2524,16 +2573,16 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>20483</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
@@ -2544,9 +2593,23 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C27" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:4">
+      <x:c r="A28" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C28" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
+      <x:c r="D28" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2566,7 +2629,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C16"/>
+  <x:dimension ref="A1:C17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2621,7 +2684,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>56045</x:v>
@@ -2632,10 +2695,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>3298216</x:v>
+        <x:v>3354261</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>21</x:v>
@@ -2665,7 +2728,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>850000</x:v>
@@ -2676,7 +2739,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>600000</x:v>
@@ -2709,7 +2772,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>350000</x:v>
@@ -2720,10 +2783,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>5417693</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>21</x:v>
@@ -2731,13 +2794,13 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>20483</x:v>
+        <x:v>5464855</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -2745,9 +2808,20 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B16" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B17" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
+      <x:c r="C17" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2767,7 +2841,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B13"/>
+  <x:dimension ref="A1:B14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2809,10 +2883,10 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>3354261</x:v>
+        <x:v>3410306</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -2825,7 +2899,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>850000</x:v>
@@ -2833,7 +2907,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>600000</x:v>
@@ -2857,7 +2931,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>350000</x:v>
@@ -2865,17 +2939,25 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>5417693</x:v>
+        <x:v>50875</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B13" s="1">
+        <x:v>5464855</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:2">
+      <x:c r="A14" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B13" s="1">
+      <x:c r="B14" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>
@@ -2895,7 +2977,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C18"/>
+  <x:dimension ref="A1:C19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2928,7 +3010,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>38</x:v>
@@ -2961,10 +3043,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>650000</x:v>
@@ -2975,10 +3057,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>2704261</x:v>
+        <x:v>2760306</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -3005,10 +3087,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>850000</x:v>
@@ -3016,10 +3098,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>600000</x:v>
@@ -3049,10 +3131,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>350000</x:v>
@@ -3060,35 +3142,35 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>2009154</x:v>
+        <x:v>50875</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2009154</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>1658539</x:v>
+        <x:v>1750000</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -3096,9 +3178,20 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="1">
+        <x:v>1705701</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C18" s="1">
+      <x:c r="C19" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -181,6 +181,15 @@
   </x:si>
   <x:si>
     <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
   </x:si>
   <x:si>
     <x:t>TORRES, RITCHIE JOHN</x:t>
@@ -314,8 +323,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G42" totalsRowShown="0">
-  <x:autoFilter ref="A1:G42"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G43" totalsRowShown="0">
+  <x:autoFilter ref="A1:G43"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -330,8 +339,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E30" totalsRowShown="0">
-  <x:autoFilter ref="A1:E30"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E31" totalsRowShown="0">
+  <x:autoFilter ref="A1:E31"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -344,8 +353,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D28" totalsRowShown="0">
-  <x:autoFilter ref="A1:D28"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D29" totalsRowShown="0">
+  <x:autoFilter ref="A1:D29"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -357,8 +366,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C17" totalsRowShown="0">
-  <x:autoFilter ref="A1:C17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C18" totalsRowShown="0">
+  <x:autoFilter ref="A1:C18"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -369,8 +378,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B14" totalsRowShown="0">
-  <x:autoFilter ref="A1:B14"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B15" totalsRowShown="0">
+  <x:autoFilter ref="A1:B15"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -380,8 +389,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C19" totalsRowShown="0">
-  <x:autoFilter ref="A1:C19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C20" totalsRowShown="0">
+  <x:autoFilter ref="A1:C20"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -679,7 +688,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G42"/>
+  <x:dimension ref="A1:G43"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1275,16 +1284,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>5031161</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>21</x:v>
@@ -1292,22 +1301,22 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>50875</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>21</x:v>
@@ -1324,16 +1333,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>56045</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
@@ -1344,19 +1353,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>2704261</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
@@ -1367,16 +1376,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>41493</x:v>
+        <x:v>2704261</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>21</x:v>
@@ -1390,16 +1399,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>141486</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>21</x:v>
@@ -1413,19 +1422,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>119644</x:v>
+        <x:v>141486</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
@@ -1436,19 +1445,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>285008</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
@@ -1459,16 +1468,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>21</x:v>
@@ -1476,22 +1485,22 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>300000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>21</x:v>
@@ -1499,22 +1508,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>350000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>21</x:v>
@@ -1522,19 +1531,19 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F37" s="1">
         <x:v>350000</x:v>
@@ -1545,22 +1554,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>850000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>21</x:v>
@@ -1568,22 +1577,22 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>250000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>21</x:v>
@@ -1591,22 +1600,22 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>21</x:v>
@@ -1614,13 +1623,13 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
         <x:v>16</x:v>
@@ -1637,24 +1646,47 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F42" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G42" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:7">
+      <x:c r="A43" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F42" s="1">
+      <x:c r="F43" s="1">
         <x:v>1750000</x:v>
       </x:c>
-      <x:c r="G42" s="1" t="s">
+      <x:c r="G43" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1674,7 +1706,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E30"/>
+  <x:dimension ref="A1:E31"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1772,13 +1804,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>350000</x:v>
@@ -1789,13 +1821,13 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>56045</x:v>
@@ -1806,13 +1838,13 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>2704261</x:v>
@@ -1823,13 +1855,13 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>300000</x:v>
@@ -1840,10 +1872,10 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>11</x:v>
@@ -1857,10 +1889,10 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>11</x:v>
@@ -1959,16 +1991,16 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>850000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>21</x:v>
@@ -1976,16 +2008,16 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>350000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>21</x:v>
@@ -1993,16 +2025,16 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>21</x:v>
@@ -2010,16 +2042,16 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>91847</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>21</x:v>
@@ -2027,16 +2059,16 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>21</x:v>
@@ -2044,16 +2076,16 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>21</x:v>
@@ -2061,16 +2093,16 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>50875</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>21</x:v>
@@ -2078,16 +2110,16 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>1750000</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>21</x:v>
@@ -2095,16 +2127,16 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>21</x:v>
@@ -2112,16 +2144,16 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>21</x:v>
@@ -2129,16 +2161,16 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>1705701</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>21</x:v>
@@ -2146,16 +2178,16 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>282526</x:v>
+        <x:v>1705701</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>21</x:v>
@@ -2163,24 +2195,24 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>20483</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>47</x:v>
@@ -2189,9 +2221,26 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D30" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:5">
+      <x:c r="A31" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D31" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E30" s="1" t="s">
+      <x:c r="E31" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2211,7 +2260,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D28"/>
+  <x:dimension ref="A1:D29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2296,7 +2345,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>350000</x:v>
@@ -2310,7 +2359,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>56045</x:v>
@@ -2324,7 +2373,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2704261</x:v>
@@ -2338,7 +2387,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>300000</x:v>
@@ -2349,7 +2398,7 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>11</x:v>
@@ -2433,13 +2482,13 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>850000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>21</x:v>
@@ -2450,10 +2499,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>600000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>21</x:v>
@@ -2464,10 +2513,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>91847</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
         <x:v>21</x:v>
@@ -2475,13 +2524,13 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>21</x:v>
@@ -2489,13 +2538,13 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>21</x:v>
@@ -2503,13 +2552,13 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>50875</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>21</x:v>
@@ -2517,13 +2566,13 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>1750000</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>21</x:v>
@@ -2531,13 +2580,13 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>21</x:v>
@@ -2545,13 +2594,13 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>21</x:v>
@@ -2559,13 +2608,13 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>1705701</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>21</x:v>
@@ -2573,13 +2622,13 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>282526</x:v>
+        <x:v>1705701</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>21</x:v>
@@ -2587,16 +2636,16 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>20483</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
@@ -2607,9 +2656,23 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C28" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:4">
+      <x:c r="A29" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C29" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
+      <x:c r="D29" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2629,7 +2692,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C17"/>
+  <x:dimension ref="A1:C18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2684,7 +2747,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>56045</x:v>
@@ -2695,7 +2758,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>3354261</x:v>
@@ -2728,10 +2791,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>850000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>21</x:v>
@@ -2739,10 +2802,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>600000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>21</x:v>
@@ -2750,10 +2813,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>91847</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>21</x:v>
@@ -2761,10 +2824,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>21</x:v>
@@ -2772,10 +2835,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>21</x:v>
@@ -2783,10 +2846,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>50875</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>21</x:v>
@@ -2794,10 +2857,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>5464855</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>21</x:v>
@@ -2805,13 +2868,13 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>20483</x:v>
+        <x:v>5464855</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -2819,9 +2882,20 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B17" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B18" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="s">
+      <x:c r="C18" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2841,7 +2915,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B14"/>
+  <x:dimension ref="A1:B15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2883,7 +2957,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>3410306</x:v>
@@ -2899,65 +2973,73 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>850000</x:v>
+        <x:v>513868</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>600000</x:v>
+        <x:v>850000</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>91847</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>50875</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>5464855</x:v>
+        <x:v>50875</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B14" s="1">
+        <x:v>5464855</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:2">
+      <x:c r="A15" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B14" s="1">
+      <x:c r="B15" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>
@@ -2977,7 +3059,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C19"/>
+  <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3010,7 +3092,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>38</x:v>
@@ -3043,10 +3125,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>650000</x:v>
@@ -3057,7 +3139,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2760306</x:v>
@@ -3087,101 +3169,101 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>850000</x:v>
+        <x:v>513868</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>600000</x:v>
+        <x:v>850000</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>91847</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>50875</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>2009154</x:v>
+        <x:v>50875</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2009154</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>1705701</x:v>
+        <x:v>1750000</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -3189,9 +3271,20 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C19" s="1">
+        <x:v>1705701</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C19" s="1">
+      <x:c r="C20" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -1431,7 +1431,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>141486</x:v>
+        <x:v>188648</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>21</x:v>
@@ -2187,7 +2187,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>1705701</x:v>
+        <x:v>1752863</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>21</x:v>
@@ -2628,7 +2628,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>1705701</x:v>
+        <x:v>1752863</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>21</x:v>
@@ -2871,7 +2871,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>5464855</x:v>
+        <x:v>5512017</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>21</x:v>
@@ -3032,7 +3032,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>5464855</x:v>
+        <x:v>5512017</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -3274,7 +3274,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>1705701</x:v>
+        <x:v>1752863</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -183,6 +183,18 @@
     <x:t>MI</x:t>
   </x:si>
   <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
     <x:t>BAIRD, JAMES R DR.</x:t>
   </x:si>
   <x:si>
@@ -204,9 +216,6 @@
     <x:t>SCOTT, DAVID ALBERT</x:t>
   </x:si>
   <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLARK, JASMINE</x:t>
   </x:si>
   <x:si>
@@ -223,9 +232,6 @@
   </x:si>
   <x:si>
     <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
   </x:si>
   <x:si>
     <x:t>COLLINS, MICHAEL A JR</x:t>
@@ -323,8 +329,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G43" totalsRowShown="0">
-  <x:autoFilter ref="A1:G43"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G46" totalsRowShown="0">
+  <x:autoFilter ref="A1:G46"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -339,8 +345,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E31" totalsRowShown="0">
-  <x:autoFilter ref="A1:E31"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E33" totalsRowShown="0">
+  <x:autoFilter ref="A1:E33"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -353,8 +359,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D29" totalsRowShown="0">
-  <x:autoFilter ref="A1:D29"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D31" totalsRowShown="0">
+  <x:autoFilter ref="A1:D31"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -389,8 +395,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C20" totalsRowShown="0">
-  <x:autoFilter ref="A1:C20"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C21" totalsRowShown="0">
+  <x:autoFilter ref="A1:C21"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -688,7 +694,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G43"/>
+  <x:dimension ref="A1:G46"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1169,16 +1175,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>418060</x:v>
+        <x:v>63285</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>21</x:v>
@@ -1192,16 +1198,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>80948</x:v>
+        <x:v>54935</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>21</x:v>
@@ -1215,16 +1221,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>771658</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>21</x:v>
@@ -1238,16 +1244,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>91656</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>21</x:v>
@@ -1261,16 +1267,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>141263</x:v>
+        <x:v>64338</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>21</x:v>
@@ -1284,16 +1290,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>513868</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>21</x:v>
@@ -1307,16 +1313,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>5031161</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>21</x:v>
@@ -1324,22 +1330,22 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>50875</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>21</x:v>
@@ -1347,45 +1353,45 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="F29" s="1">
-        <x:v>56045</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>2704261</x:v>
+        <x:v>5031161</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>21</x:v>
@@ -1399,16 +1405,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>41493</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>21</x:v>
@@ -1422,19 +1428,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>188648</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
@@ -1445,19 +1451,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>119644</x:v>
+        <x:v>2761006</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
@@ -1468,16 +1474,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>285008</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>21</x:v>
@@ -1491,16 +1497,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>30183</x:v>
+        <x:v>188648</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>21</x:v>
@@ -1508,45 +1514,45 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>300000</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B37" s="1" t="s">
+      <x:c r="D37" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C37" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>350000</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>21</x:v>
@@ -1554,22 +1560,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C38" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D38" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>21</x:v>
@@ -1577,22 +1583,22 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>850000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>21</x:v>
@@ -1600,22 +1606,22 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>21</x:v>
@@ -1623,19 +1629,19 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F41" s="1">
         <x:v>350000</x:v>
@@ -1646,22 +1652,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>350000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>21</x:v>
@@ -1669,24 +1675,93 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F43" s="1">
+        <x:v>250000</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:7">
+      <x:c r="A44" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F44" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G44" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:7">
+      <x:c r="A45" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F45" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G45" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:7">
+      <x:c r="A46" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F43" s="1">
+      <x:c r="F46" s="1">
         <x:v>1750000</x:v>
       </x:c>
-      <x:c r="G43" s="1" t="s">
+      <x:c r="G46" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1706,7 +1781,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E31"/>
+  <x:dimension ref="A1:E33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1804,13 +1879,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>350000</x:v>
@@ -1821,33 +1896,33 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>56045</x:v>
+        <x:v>54935</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>2704261</x:v>
+        <x:v>64338</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>21</x:v>
@@ -1855,33 +1930,33 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>300000</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>285008</x:v>
+        <x:v>2761006</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>21</x:v>
@@ -1889,16 +1964,16 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>30183</x:v>
+        <x:v>363285</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>21</x:v>
@@ -1906,50 +1981,50 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>9985740</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>817066</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>2475786</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>12</x:v>
@@ -1957,50 +2032,50 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>557012</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>83860</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>513868</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>21</x:v>
@@ -2008,16 +2083,16 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>850000</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>21</x:v>
@@ -2025,16 +2100,16 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>350000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>21</x:v>
@@ -2051,7 +2126,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>250000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>21</x:v>
@@ -2059,16 +2134,16 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>91847</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>21</x:v>
@@ -2076,16 +2151,16 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>161896</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>21</x:v>
@@ -2093,16 +2168,16 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>350000</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>21</x:v>
@@ -2110,16 +2185,16 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>50875</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>21</x:v>
@@ -2133,10 +2208,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>1750000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>21</x:v>
@@ -2144,16 +2219,16 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>1543316</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>21</x:v>
@@ -2161,16 +2236,16 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>183312</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>21</x:v>
@@ -2178,16 +2253,16 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>1752863</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>21</x:v>
@@ -2195,16 +2270,16 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>282526</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>21</x:v>
@@ -2212,35 +2287,69 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>20483</x:v>
+        <x:v>1752863</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D31" s="1">
+        <x:v>282526</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:5">
+      <x:c r="A32" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D32" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:5">
+      <x:c r="A33" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B31" s="1" t="s">
+      <x:c r="B33" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C31" s="1" t="s">
+      <x:c r="C33" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D31" s="1">
+      <x:c r="D33" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E31" s="1" t="s">
+      <x:c r="E33" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2260,7 +2369,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D29"/>
+  <x:dimension ref="A1:D31"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2345,7 +2454,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>350000</x:v>
@@ -2356,27 +2465,27 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>56045</x:v>
+        <x:v>54935</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>2704261</x:v>
+        <x:v>64338</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>21</x:v>
@@ -2384,27 +2493,27 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>300000</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>315191</x:v>
+        <x:v>2761006</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>21</x:v>
@@ -2412,41 +2521,41 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>9985740</x:v>
+        <x:v>363285</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>817066</x:v>
+        <x:v>315191</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>2475786</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>12</x:v>
@@ -2454,41 +2563,41 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>557012</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>83860</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>513868</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>21</x:v>
@@ -2496,13 +2605,13 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>850000</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>21</x:v>
@@ -2510,13 +2619,13 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>600000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
         <x:v>21</x:v>
@@ -2527,10 +2636,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>91847</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>21</x:v>
@@ -2538,13 +2647,13 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>161896</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>21</x:v>
@@ -2555,10 +2664,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>350000</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>21</x:v>
@@ -2566,13 +2675,13 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>50875</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>21</x:v>
@@ -2583,10 +2692,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>1750000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>21</x:v>
@@ -2594,13 +2703,13 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>1543316</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>21</x:v>
@@ -2608,13 +2717,13 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>183312</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>21</x:v>
@@ -2622,13 +2731,13 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>1752863</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>21</x:v>
@@ -2636,13 +2745,13 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>282526</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>21</x:v>
@@ -2650,29 +2759,57 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>20483</x:v>
+        <x:v>1752863</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C29" s="1">
+        <x:v>282526</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:4">
+      <x:c r="A30" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B29" s="1" t="s">
+      <x:c r="B30" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C29" s="1">
+      <x:c r="C30" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:4">
+      <x:c r="A31" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C31" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D29" s="1" t="s">
+      <x:c r="D31" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2747,7 +2884,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>56045</x:v>
@@ -2758,10 +2895,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>3354261</x:v>
+        <x:v>3593564</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>21</x:v>
@@ -2791,7 +2928,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>513868</x:v>
@@ -2802,7 +2939,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>850000</x:v>
@@ -2813,7 +2950,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>600000</x:v>
@@ -2846,7 +2983,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>350000</x:v>
@@ -2857,7 +2994,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>50875</x:v>
@@ -2957,10 +3094,10 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>3410306</x:v>
+        <x:v>3649609</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -2973,7 +3110,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>513868</x:v>
@@ -2981,7 +3118,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>850000</x:v>
@@ -2989,7 +3126,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>600000</x:v>
@@ -3013,7 +3150,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>350000</x:v>
@@ -3021,7 +3158,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>50875</x:v>
@@ -3059,7 +3196,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C20"/>
+  <x:dimension ref="A1:C21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3092,7 +3229,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>38</x:v>
@@ -3125,156 +3262,156 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>650000</x:v>
+        <x:v>182558</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>2760306</x:v>
+        <x:v>650000</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>13158948</x:v>
+        <x:v>2817051</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>1075707</x:v>
+        <x:v>13158948</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>513868</x:v>
+        <x:v>1075707</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>850000</x:v>
+        <x:v>513868</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>600000</x:v>
+        <x:v>850000</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>91847</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>50875</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>2009154</x:v>
+        <x:v>50875</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2009154</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>1752863</x:v>
+        <x:v>1750000</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -3282,9 +3419,20 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C20" s="1">
+        <x:v>1752863</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C20" s="1">
+      <x:c r="C21" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -189,12 +189,27 @@
     <x:t>GA</x:t>
   </x:si>
   <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
     <x:t>KINGSTON, JACK REP.</x:t>
   </x:si>
   <x:si>
     <x:t>GAINES, HOUSTON</x:t>
   </x:si>
   <x:si>
+    <x:t>SMITH, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
     <x:t>BAIRD, JAMES R DR.</x:t>
   </x:si>
   <x:si>
@@ -240,9 +255,6 @@
     <x:t>MORRIS, NATE</x:t>
   </x:si>
   <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
     <x:t>MIGUEZ, BLAKE</x:t>
   </x:si>
   <x:si>
@@ -253,9 +265,6 @@
   </x:si>
   <x:si>
     <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
   </x:si>
   <x:si>
     <x:t>PAXTON, WARREN KENNETH JR.</x:t>
@@ -329,8 +338,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G46" totalsRowShown="0">
-  <x:autoFilter ref="A1:G46"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G48" totalsRowShown="0">
+  <x:autoFilter ref="A1:G48"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -345,8 +354,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E33" totalsRowShown="0">
-  <x:autoFilter ref="A1:E33"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E35" totalsRowShown="0">
+  <x:autoFilter ref="A1:E35"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -359,8 +368,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D31" totalsRowShown="0">
-  <x:autoFilter ref="A1:D31"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D33" totalsRowShown="0">
+  <x:autoFilter ref="A1:D33"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -395,8 +404,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C21" totalsRowShown="0">
-  <x:autoFilter ref="A1:C21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C23" totalsRowShown="0">
+  <x:autoFilter ref="A1:C23"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -694,7 +703,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G46"/>
+  <x:dimension ref="A1:G48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1201,13 +1210,13 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>54935</x:v>
+        <x:v>3590517</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>21</x:v>
@@ -1221,16 +1230,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>418060</x:v>
+        <x:v>54935</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>21</x:v>
@@ -1244,16 +1253,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>80948</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>21</x:v>
@@ -1267,16 +1276,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>64338</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>21</x:v>
@@ -1290,16 +1299,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>771658</x:v>
+        <x:v>64338</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>21</x:v>
@@ -1313,16 +1322,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>91656</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>21</x:v>
@@ -1336,16 +1345,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>141263</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>21</x:v>
@@ -1359,16 +1368,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>513868</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>21</x:v>
@@ -1382,16 +1391,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>5031161</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>21</x:v>
@@ -1399,22 +1408,22 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>50875</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>21</x:v>
@@ -1422,25 +1431,25 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>56045</x:v>
+        <x:v>6576247</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
@@ -1451,16 +1460,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>2761006</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>21</x:v>
@@ -1474,19 +1483,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>41493</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
@@ -1497,16 +1506,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>188648</x:v>
+        <x:v>3343831</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>21</x:v>
@@ -1520,19 +1529,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>119644</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
@@ -1543,16 +1552,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>285008</x:v>
+        <x:v>1215641</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>21</x:v>
@@ -1566,39 +1575,39 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>30183</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>300000</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>21</x:v>
@@ -1606,22 +1615,22 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>21</x:v>
@@ -1629,22 +1638,22 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>350000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>21</x:v>
@@ -1652,22 +1661,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>850000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>21</x:v>
@@ -1675,22 +1684,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>21</x:v>
@@ -1698,22 +1707,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>350000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>21</x:v>
@@ -1721,22 +1730,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>21</x:v>
@@ -1744,24 +1753,70 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F46" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G46" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:7">
+      <x:c r="A47" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F47" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G47" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:7">
+      <x:c r="A48" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F46" s="1">
+      <x:c r="F48" s="1">
         <x:v>1750000</x:v>
       </x:c>
-      <x:c r="G46" s="1" t="s">
+      <x:c r="G48" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1781,7 +1836,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E33"/>
+  <x:dimension ref="A1:E35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1820,7 +1875,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>10399014</x:v>
+        <x:v>11944100</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
         <x:v>21</x:v>
@@ -1879,7 +1934,7 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>16</x:v>
@@ -1896,7 +1951,7 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>26</x:v>
@@ -1913,7 +1968,7 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>34</x:v>
@@ -1930,7 +1985,7 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>42</x:v>
@@ -1947,7 +2002,7 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>42</x:v>
@@ -1956,7 +2011,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>2761006</x:v>
+        <x:v>3343831</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>21</x:v>
@@ -1981,10 +2036,10 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>11</x:v>
@@ -1998,10 +2053,10 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>11</x:v>
@@ -2100,13 +2155,13 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>513868</x:v>
@@ -2117,13 +2172,13 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>850000</x:v>
@@ -2134,16 +2189,16 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>350000</x:v>
+        <x:v>3590517</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>21</x:v>
@@ -2151,16 +2206,16 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>21</x:v>
@@ -2168,16 +2223,16 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>91847</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>21</x:v>
@@ -2185,16 +2240,16 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>21</x:v>
@@ -2202,16 +2257,16 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>21</x:v>
@@ -2219,16 +2274,16 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="D26" s="1">
-        <x:v>50875</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>21</x:v>
@@ -2236,16 +2291,16 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>1750000</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>21</x:v>
@@ -2253,16 +2308,16 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>1543316</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>21</x:v>
@@ -2270,16 +2325,16 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>183312</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>21</x:v>
@@ -2287,16 +2342,16 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>1752863</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>21</x:v>
@@ -2304,16 +2359,16 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>282526</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>21</x:v>
@@ -2321,35 +2376,69 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>20483</x:v>
+        <x:v>2779856</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D33" s="1">
+        <x:v>282526</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:5">
+      <x:c r="A34" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D34" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:5">
+      <x:c r="A35" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B33" s="1" t="s">
+      <x:c r="B35" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C33" s="1" t="s">
+      <x:c r="C35" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D33" s="1">
+      <x:c r="D35" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E33" s="1" t="s">
+      <x:c r="E35" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2369,7 +2458,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D31"/>
+  <x:dimension ref="A1:D33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2401,7 +2490,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>10399014</x:v>
+        <x:v>11944100</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>21</x:v>
@@ -2513,7 +2602,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>2761006</x:v>
+        <x:v>3343831</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>21</x:v>
@@ -2535,7 +2624,7 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>11</x:v>
@@ -2619,10 +2708,10 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>513868</x:v>
@@ -2636,7 +2725,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>850000</x:v>
@@ -2647,13 +2736,13 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>600000</x:v>
+        <x:v>3590517</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>21</x:v>
@@ -2664,10 +2753,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>91847</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>21</x:v>
@@ -2675,13 +2764,13 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>21</x:v>
@@ -2689,13 +2778,13 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>21</x:v>
@@ -2703,13 +2792,13 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B24" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="C24" s="1">
-        <x:v>50875</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>21</x:v>
@@ -2717,13 +2806,13 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>1750000</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>21</x:v>
@@ -2731,13 +2820,13 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>1543316</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>21</x:v>
@@ -2745,13 +2834,13 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>183312</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>21</x:v>
@@ -2759,13 +2848,13 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>1752863</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>21</x:v>
@@ -2773,13 +2862,13 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>282526</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>21</x:v>
@@ -2787,29 +2876,57 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>20483</x:v>
+        <x:v>2779856</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C31" s="1">
+        <x:v>282526</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:4">
+      <x:c r="A32" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B31" s="1" t="s">
+      <x:c r="B32" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C31" s="1">
+      <x:c r="C32" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:4">
+      <x:c r="A33" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C33" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
+      <x:c r="D33" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2854,7 +2971,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>10399014</x:v>
+        <x:v>11944100</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>21</x:v>
@@ -2898,7 +3015,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>3593564</x:v>
+        <x:v>4176389</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>21</x:v>
@@ -2928,7 +3045,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>513868</x:v>
@@ -2939,10 +3056,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>850000</x:v>
+        <x:v>4440517</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>21</x:v>
@@ -2950,7 +3067,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>600000</x:v>
@@ -2983,10 +3100,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>350000</x:v>
+        <x:v>632975</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>21</x:v>
@@ -2994,7 +3111,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>50875</x:v>
@@ -3008,7 +3125,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>5512017</x:v>
+        <x:v>6539010</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>21</x:v>
@@ -3073,7 +3190,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>10399014</x:v>
+        <x:v>11944100</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -3097,7 +3214,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>3649609</x:v>
+        <x:v>4232434</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -3110,7 +3227,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>513868</x:v>
@@ -3118,15 +3235,15 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>850000</x:v>
+        <x:v>4440517</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>600000</x:v>
@@ -3150,15 +3267,15 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>350000</x:v>
+        <x:v>632975</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>50875</x:v>
@@ -3169,7 +3286,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>5512017</x:v>
+        <x:v>6539010</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -3196,7 +3313,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C21"/>
+  <x:dimension ref="A1:C23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3224,12 +3341,12 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>10049014</x:v>
+        <x:v>11594100</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>38</x:v>
@@ -3273,7 +3390,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>55</x:v>
@@ -3290,7 +3407,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>2817051</x:v>
+        <x:v>3399876</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -3320,7 +3437,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>513868</x:v>
@@ -3328,111 +3445,133 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>850000</x:v>
+        <x:v>3590517</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>600000</x:v>
+        <x:v>850000</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>91847</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>50875</x:v>
+        <x:v>282975</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>2009154</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>1750000</x:v>
+        <x:v>50875</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>1752863</x:v>
+        <x:v>2009154</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C21" s="1">
+        <x:v>1750000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B21" s="1" t="s">
+      <x:c r="B22" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C22" s="1">
+        <x:v>2779856</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C21" s="1">
+      <x:c r="C23" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -232,6 +232,15 @@
   </x:si>
   <x:si>
     <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
   </x:si>
   <x:si>
     <x:t>KELLY, ROBIN</x:t>
@@ -338,8 +347,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G48" totalsRowShown="0">
-  <x:autoFilter ref="A1:G48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G49" totalsRowShown="0">
+  <x:autoFilter ref="A1:G49"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -354,8 +363,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E35" totalsRowShown="0">
-  <x:autoFilter ref="A1:E35"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E36" totalsRowShown="0">
+  <x:autoFilter ref="A1:E36"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -368,8 +377,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D33" totalsRowShown="0">
-  <x:autoFilter ref="A1:D33"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D34" totalsRowShown="0">
+  <x:autoFilter ref="A1:D34"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -381,8 +390,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C18" totalsRowShown="0">
-  <x:autoFilter ref="A1:C18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C19" totalsRowShown="0">
+  <x:autoFilter ref="A1:C19"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -393,8 +402,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B15" totalsRowShown="0">
-  <x:autoFilter ref="A1:B15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B16" totalsRowShown="0">
+  <x:autoFilter ref="A1:B16"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -404,8 +413,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C23" totalsRowShown="0">
-  <x:autoFilter ref="A1:C23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C24" totalsRowShown="0">
+  <x:autoFilter ref="A1:C24"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -703,7 +712,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G48"/>
+  <x:dimension ref="A1:G49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1515,7 +1524,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>3343831</x:v>
+        <x:v>3399876</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>21</x:v>
@@ -1552,16 +1561,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>1215641</x:v>
+        <x:v>243968</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>21</x:v>
@@ -1575,19 +1584,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>119644</x:v>
+        <x:v>1215641</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
@@ -1598,19 +1607,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>285008</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
@@ -1621,16 +1630,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>21</x:v>
@@ -1638,22 +1647,22 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C41" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D41" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>300000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>21</x:v>
@@ -1661,22 +1670,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>350000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>21</x:v>
@@ -1684,19 +1693,19 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F43" s="1">
         <x:v>350000</x:v>
@@ -1707,22 +1716,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>850000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>21</x:v>
@@ -1730,22 +1739,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>250000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>21</x:v>
@@ -1753,22 +1762,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>21</x:v>
@@ -1776,19 +1785,19 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F47" s="1">
         <x:v>350000</x:v>
@@ -1799,24 +1808,47 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F48" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:7">
+      <x:c r="A49" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F48" s="1">
+      <x:c r="F49" s="1">
         <x:v>1750000</x:v>
       </x:c>
-      <x:c r="G48" s="1" t="s">
+      <x:c r="G49" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1836,7 +1868,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E35"/>
+  <x:dimension ref="A1:E36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1934,7 +1966,7 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>16</x:v>
@@ -2011,7 +2043,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>3343831</x:v>
+        <x:v>3399876</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>21</x:v>
@@ -2036,10 +2068,10 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>11</x:v>
@@ -2053,10 +2085,10 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>11</x:v>
@@ -2172,7 +2204,7 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>16</x:v>
@@ -2206,13 +2238,13 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>350000</x:v>
@@ -2223,13 +2255,13 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>250000</x:v>
@@ -2240,16 +2272,16 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>91847</x:v>
+        <x:v>243968</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>21</x:v>
@@ -2257,16 +2289,16 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>21</x:v>
@@ -2274,16 +2306,16 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>21</x:v>
@@ -2291,16 +2323,16 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>21</x:v>
@@ -2308,16 +2340,16 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>50875</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>21</x:v>
@@ -2325,16 +2357,16 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>1750000</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>21</x:v>
@@ -2342,16 +2374,16 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>21</x:v>
@@ -2359,16 +2391,16 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>21</x:v>
@@ -2376,16 +2408,16 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>2779856</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>21</x:v>
@@ -2393,16 +2425,16 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>282526</x:v>
+        <x:v>2779856</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>21</x:v>
@@ -2410,24 +2442,24 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>20483</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>47</x:v>
@@ -2436,9 +2468,26 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D35" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:5">
+      <x:c r="A36" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D36" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E35" s="1" t="s">
+      <x:c r="E36" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2458,7 +2507,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D33"/>
+  <x:dimension ref="A1:D34"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2602,7 +2651,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>3343831</x:v>
+        <x:v>3399876</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>21</x:v>
@@ -2624,7 +2673,7 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>11</x:v>
@@ -2753,7 +2802,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>600000</x:v>
@@ -2764,13 +2813,13 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>91847</x:v>
+        <x:v>243968</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>21</x:v>
@@ -2778,13 +2827,13 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>21</x:v>
@@ -2792,13 +2841,13 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>21</x:v>
@@ -2806,13 +2855,13 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>21</x:v>
@@ -2820,13 +2869,13 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>50875</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>21</x:v>
@@ -2834,13 +2883,13 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>1750000</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>21</x:v>
@@ -2848,13 +2897,13 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>21</x:v>
@@ -2862,13 +2911,13 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>21</x:v>
@@ -2876,13 +2925,13 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>2779856</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
         <x:v>21</x:v>
@@ -2890,13 +2939,13 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>282526</x:v>
+        <x:v>2779856</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>21</x:v>
@@ -2904,16 +2953,16 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>20483</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
@@ -2924,9 +2973,23 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C33" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:4">
+      <x:c r="A34" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C34" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D33" s="1" t="s">
+      <x:c r="D34" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2946,7 +3009,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C18"/>
+  <x:dimension ref="A1:C19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3015,7 +3078,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>4176389</x:v>
+        <x:v>4232434</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>21</x:v>
@@ -3067,7 +3130,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>600000</x:v>
@@ -3078,10 +3141,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>91847</x:v>
+        <x:v>243968</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>21</x:v>
@@ -3089,10 +3152,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>21</x:v>
@@ -3100,10 +3163,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>632975</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>21</x:v>
@@ -3111,10 +3174,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>50875</x:v>
+        <x:v>632975</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>21</x:v>
@@ -3122,10 +3185,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>6539010</x:v>
+        <x:v>50875</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>21</x:v>
@@ -3133,13 +3196,13 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>20483</x:v>
+        <x:v>6539010</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -3147,9 +3210,20 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B18" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B19" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
+      <x:c r="C19" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -3169,7 +3243,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B15"/>
+  <x:dimension ref="A1:B16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3214,7 +3288,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>4232434</x:v>
+        <x:v>4288479</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -3243,7 +3317,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>600000</x:v>
@@ -3251,49 +3325,57 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>91847</x:v>
+        <x:v>243968</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>632975</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>50875</x:v>
+        <x:v>632975</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>6539010</x:v>
+        <x:v>50875</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B15" s="1">
+        <x:v>6539010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:2">
+      <x:c r="A16" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B15" s="1">
+      <x:c r="B16" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>
@@ -3313,7 +3395,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C23"/>
+  <x:dimension ref="A1:C24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3346,7 +3428,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>38</x:v>
@@ -3390,7 +3472,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>55</x:v>
@@ -3407,7 +3489,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>3399876</x:v>
+        <x:v>3455921</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -3456,7 +3538,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>57</x:v>
@@ -3467,10 +3549,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>600000</x:v>
@@ -3478,24 +3560,24 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>91847</x:v>
+        <x:v>243968</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -3503,65 +3585,65 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>282975</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>350000</x:v>
+        <x:v>282975</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>50875</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>2009154</x:v>
+        <x:v>50875</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2009154</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>2779856</x:v>
+        <x:v>1750000</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -3569,9 +3651,20 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C23" s="1">
+        <x:v>2779856</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C23" s="1">
+      <x:c r="C24" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -347,8 +347,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G49" totalsRowShown="0">
-  <x:autoFilter ref="A1:G49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G50" totalsRowShown="0">
+  <x:autoFilter ref="A1:G50"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -363,8 +363,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E36" totalsRowShown="0">
-  <x:autoFilter ref="A1:E36"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E37" totalsRowShown="0">
+  <x:autoFilter ref="A1:E37"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -712,7 +712,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G49"/>
+  <x:dimension ref="A1:G50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1202,7 +1202,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>63285</x:v>
+        <x:v>328576</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>21</x:v>
@@ -1248,7 +1248,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>54935</x:v>
+        <x:v>320996</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>21</x:v>
@@ -1317,7 +1317,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>64338</x:v>
+        <x:v>580151</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>21</x:v>
@@ -1478,7 +1478,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>50875</x:v>
+        <x:v>101750</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>21</x:v>
@@ -1593,7 +1593,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>1215641</x:v>
+        <x:v>1262803</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>21</x:v>
@@ -1745,7 +1745,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
         <x:v>16</x:v>
@@ -1754,7 +1754,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>850000</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>21</x:v>
@@ -1768,16 +1768,16 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>250000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>21</x:v>
@@ -1791,7 +1791,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
         <x:v>16</x:v>
@@ -1800,7 +1800,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>21</x:v>
@@ -1814,13 +1814,13 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F48" s="1">
         <x:v>350000</x:v>
@@ -1837,18 +1837,41 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F49" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G49" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:7">
+      <x:c r="A50" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F49" s="1">
+      <x:c r="F50" s="1">
         <x:v>1750000</x:v>
       </x:c>
-      <x:c r="G49" s="1" t="s">
+      <x:c r="G50" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1868,7 +1891,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E36"/>
+  <x:dimension ref="A1:E37"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1992,7 +2015,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>54935</x:v>
+        <x:v>320996</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>21</x:v>
@@ -2009,7 +2032,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>64338</x:v>
+        <x:v>580151</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>21</x:v>
@@ -2060,7 +2083,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>363285</x:v>
+        <x:v>628576</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>21</x:v>
@@ -2204,7 +2227,7 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>16</x:v>
@@ -2213,7 +2236,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>850000</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>21</x:v>
@@ -2221,16 +2244,16 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>3590517</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>21</x:v>
@@ -2238,16 +2261,16 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>350000</x:v>
+        <x:v>3590517</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>21</x:v>
@@ -2255,7 +2278,7 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>16</x:v>
@@ -2264,7 +2287,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>21</x:v>
@@ -2272,16 +2295,16 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>243968</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>21</x:v>
@@ -2289,16 +2312,16 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>91847</x:v>
+        <x:v>243968</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>21</x:v>
@@ -2306,16 +2329,16 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>21</x:v>
@@ -2323,16 +2346,16 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>21</x:v>
@@ -2340,16 +2363,16 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>21</x:v>
@@ -2357,16 +2380,16 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>50875</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>21</x:v>
@@ -2374,16 +2397,16 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>1750000</x:v>
+        <x:v>101750</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>21</x:v>
@@ -2391,16 +2414,16 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>21</x:v>
@@ -2408,16 +2431,16 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>21</x:v>
@@ -2425,16 +2448,16 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>2779856</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>21</x:v>
@@ -2442,16 +2465,16 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>282526</x:v>
+        <x:v>2827018</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>21</x:v>
@@ -2459,24 +2482,24 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>20483</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>47</x:v>
@@ -2485,9 +2508,26 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D36" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:5">
+      <x:c r="A37" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D37" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E36" s="1" t="s">
+      <x:c r="E37" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2609,7 +2649,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>54935</x:v>
+        <x:v>320996</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>21</x:v>
@@ -2623,7 +2663,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>64338</x:v>
+        <x:v>580151</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>21</x:v>
@@ -2665,7 +2705,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>363285</x:v>
+        <x:v>628576</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
         <x:v>21</x:v>
@@ -2889,7 +2929,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>50875</x:v>
+        <x:v>101750</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>21</x:v>
@@ -2945,7 +2985,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>2779856</x:v>
+        <x:v>2827018</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>21</x:v>
@@ -3078,7 +3118,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>4232434</x:v>
+        <x:v>5279599</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>21</x:v>
@@ -3188,7 +3228,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>50875</x:v>
+        <x:v>101750</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>21</x:v>
@@ -3199,7 +3239,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>6539010</x:v>
+        <x:v>6586172</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>21</x:v>
@@ -3288,7 +3328,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>4288479</x:v>
+        <x:v>5335644</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -3360,7 +3400,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>50875</x:v>
+        <x:v>101750</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -3368,7 +3408,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>6539010</x:v>
+        <x:v>6586172</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
@@ -3467,7 +3507,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>182558</x:v>
+        <x:v>1229723</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -3621,7 +3661,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>50875</x:v>
+        <x:v>101750</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -3654,7 +3694,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>2779856</x:v>
+        <x:v>2827018</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -48,117 +48,213 @@
     <x:t>FAIRSHAKE</x:t>
   </x:si>
   <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMITH, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TORRES, RITCHIE JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
     <x:t>PETERS, ROBERT JAMES</x:t>
   </x:si>
   <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
     <x:t>PATRONIS, JIMMY JR.</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
     <x:t>FL</x:t>
   </x:si>
   <x:si>
     <x:t>FINE, RANDY</x:t>
   </x:si>
   <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
     <x:t>BUDZINSKI, NIKKI</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
     <x:t>WALKINSHAW, JAMES</x:t>
   </x:si>
   <x:si>
@@ -181,102 +277,6 @@
   </x:si>
   <x:si>
     <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMITH, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TORRES, RITCHIE JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -765,7 +765,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>817066</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -788,7 +788,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>1803694</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -796,148 +796,148 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>5168736</x:v>
+        <x:v>328576</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>418058</x:v>
+        <x:v>3590517</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>80948</x:v>
+        <x:v>320996</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>558813</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>1673736</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>771658</x:v>
+        <x:v>580151</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>33</x:v>
@@ -946,171 +946,171 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>91656</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>141263</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>5017853</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="D13" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>83860</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>515519</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>1564215</x:v>
+        <x:v>6576247</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>1012792</x:v>
+        <x:v>101750</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>20483</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1118,390 +1118,390 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>91847</x:v>
+        <x:v>3455921</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>672092</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>4697360</x:v>
+        <x:v>243968</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>328576</x:v>
+        <x:v>1309965</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>3590517</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>320996</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>418060</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B25" s="1" t="s">
+      <x:c r="D25" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>80948</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>580151</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>771658</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>91656</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>141263</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>513868</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>6576247</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>101750</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>56045</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1509,370 +1509,370 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>3399876</x:v>
+        <x:v>1803694</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>41493</x:v>
+        <x:v>5168736</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>243968</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>1262803</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>119644</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F40" s="1">
-        <x:v>285008</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>30183</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>300000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>350000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>350000</x:v>
+        <x:v>5017853</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B45" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C45" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>628597</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>221403</x:v>
+        <x:v>515519</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>250000</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C48" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>350000</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>350000</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D50" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E50" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="F50" s="1">
-        <x:v>1750000</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1921,132 +1921,132 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>11944100</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>320996</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>580151</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>56045</x:v>
@@ -2057,44 +2057,44 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>3399876</x:v>
+        <x:v>3455921</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>628576</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>11</x:v>
@@ -2103,15 +2103,15 @@
         <x:v>285008</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>11</x:v>
@@ -2120,15 +2120,15 @@
         <x:v>30183</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>11</x:v>
@@ -2142,10 +2142,10 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>11</x:v>
@@ -2159,10 +2159,10 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>11</x:v>
@@ -2176,10 +2176,10 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>11</x:v>
@@ -2188,15 +2188,15 @@
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>11</x:v>
@@ -2205,307 +2205,307 @@
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>513868</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>628597</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>221403</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>3590517</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>250000</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>243968</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>282975</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>101750</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>1750000</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>2827018</x:v>
+        <x:v>2874180</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>20483</x:v>
@@ -2516,19 +2516,19 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2573,108 +2573,108 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>11944100</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>320996</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>580151</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>56045</x:v>
@@ -2685,35 +2685,35 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>3399876</x:v>
+        <x:v>3455921</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>628576</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>11</x:v>
@@ -2722,12 +2722,12 @@
         <x:v>315191</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>11</x:v>
@@ -2741,7 +2741,7 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>11</x:v>
@@ -2755,7 +2755,7 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>11</x:v>
@@ -2769,7 +2769,7 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>11</x:v>
@@ -2778,12 +2778,12 @@
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>11</x:v>
@@ -2792,225 +2792,225 @@
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>513868</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>3590517</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>243968</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>282975</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>101750</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>1750000</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>2827018</x:v>
+        <x:v>2874180</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>20483</x:v>
@@ -3021,16 +3021,16 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3071,40 +3071,40 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>11944100</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2232549</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>56045</x:v>
@@ -3115,13 +3115,13 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>5279599</x:v>
+        <x:v>5335644</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -3143,111 +3143,111 @@
         <x:v>956063</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>513868</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>4440517</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>243968</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>632975</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>101750</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>6586172</x:v>
+        <x:v>6633334</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>20483</x:v>
@@ -3258,13 +3258,13 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3301,7 +3301,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>11944100</x:v>
@@ -3309,7 +3309,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
@@ -3317,7 +3317,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2232549</x:v>
@@ -3325,10 +3325,10 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>5335644</x:v>
+        <x:v>5391689</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -3341,7 +3341,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>513868</x:v>
@@ -3349,7 +3349,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>4440517</x:v>
@@ -3357,7 +3357,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>600000</x:v>
@@ -3365,7 +3365,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>243968</x:v>
@@ -3373,7 +3373,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>91847</x:v>
@@ -3381,7 +3381,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>161896</x:v>
@@ -3389,7 +3389,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>632975</x:v>
@@ -3397,7 +3397,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>101750</x:v>
@@ -3405,15 +3405,15 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>6586172</x:v>
+        <x:v>6633334</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>1033275</x:v>
@@ -3457,10 +3457,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>11594100</x:v>
@@ -3468,10 +3468,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>350000</x:v>
@@ -3479,10 +3479,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>836118</x:v>
@@ -3490,10 +3490,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>2232549</x:v>
@@ -3501,10 +3501,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>1229723</x:v>
@@ -3512,10 +3512,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>650000</x:v>
@@ -3523,13 +3523,13 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>3455921</x:v>
+        <x:v>3511966</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -3545,7 +3545,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>11</x:v>
@@ -3556,10 +3556,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>513868</x:v>
@@ -3567,10 +3567,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>3590517</x:v>
@@ -3578,10 +3578,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>850000</x:v>
@@ -3589,10 +3589,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>600000</x:v>
@@ -3600,10 +3600,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>243968</x:v>
@@ -3611,10 +3611,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>91847</x:v>
@@ -3622,10 +3622,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>161896</x:v>
@@ -3633,10 +3633,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>282975</x:v>
@@ -3644,10 +3644,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>350000</x:v>
@@ -3655,10 +3655,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>101750</x:v>
@@ -3666,10 +3666,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>2009154</x:v>
@@ -3677,10 +3677,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>1750000</x:v>
@@ -3688,21 +3688,21 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>2827018</x:v>
+        <x:v>2874180</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1033275</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -48,18 +48,24 @@
     <x:t>FAIRSHAKE</x:t>
   </x:si>
   <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>FORD, LA SHAWN K</x:t>
   </x:si>
   <x:si>
     <x:t>07</x:t>
   </x:si>
   <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>STRATTON, JULIANA</x:t>
   </x:si>
   <x:si>
@@ -102,9 +108,6 @@
     <x:t>HILL, JAMES FRENCH</x:t>
   </x:si>
   <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
     <x:t>AR</x:t>
   </x:si>
   <x:si>
@@ -183,6 +186,9 @@
     <x:t>13</x:t>
   </x:si>
   <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
     <x:t>CLARK, JASMINE</x:t>
   </x:si>
   <x:si>
@@ -238,45 +244,6 @@
   </x:si>
   <x:si>
     <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATRONIS, JIMMY JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALKINSHAW, JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKARSKY, STELLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00894428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROGERS, MICHAEL J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -347,8 +314,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G50" totalsRowShown="0">
-  <x:autoFilter ref="A1:G50"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G35" totalsRowShown="0">
+  <x:autoFilter ref="A1:G35"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -363,8 +330,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E37" totalsRowShown="0">
-  <x:autoFilter ref="A1:E37"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E32" totalsRowShown="0">
+  <x:autoFilter ref="A1:E32"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -377,8 +344,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D34" totalsRowShown="0">
-  <x:autoFilter ref="A1:D34"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D29" totalsRowShown="0">
+  <x:autoFilter ref="A1:D29"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -390,8 +357,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C19" totalsRowShown="0">
-  <x:autoFilter ref="A1:C19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C15" totalsRowShown="0">
+  <x:autoFilter ref="A1:C15"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -402,8 +369,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B16" totalsRowShown="0">
-  <x:autoFilter ref="A1:B16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B13" totalsRowShown="0">
+  <x:autoFilter ref="A1:B13"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -413,8 +380,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C24" totalsRowShown="0">
-  <x:autoFilter ref="A1:C24"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C21" totalsRowShown="0">
+  <x:autoFilter ref="A1:C21"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -712,12 +679,12 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G50"/>
+  <x:dimension ref="A1:G35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
     <x:col min="1" max="1" width="15.710625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="24.282054" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="23.424911" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="29.424911" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="25.282054" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="23.424911" style="1" customWidth="1"/>
@@ -765,7 +732,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>672092</x:v>
+        <x:v>817065</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -788,7 +755,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>4697360</x:v>
+        <x:v>2475788</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -796,79 +763,79 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>328576</x:v>
+        <x:v>9866096</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="F5" s="1">
-        <x:v>3590517</x:v>
+        <x:v>328576</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>320996</x:v>
+        <x:v>3590517</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>26</x:v>
@@ -877,366 +844,366 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>418060</x:v>
+        <x:v>320996</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="F8" s="1">
-        <x:v>80948</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="F9" s="1">
-        <x:v>580151</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>282975</x:v>
+        <x:v>580151</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="F11" s="1">
-        <x:v>771658</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="F12" s="1">
-        <x:v>91656</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>141263</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>513868</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="F15" s="1">
-        <x:v>6576247</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="F16" s="1">
-        <x:v>101750</x:v>
+        <x:v>6576247</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="F17" s="1">
-        <x:v>56045</x:v>
+        <x:v>101750</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>3455921</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>41493</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>243968</x:v>
+        <x:v>3455921</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>1309965</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>119644</x:v>
+        <x:v>303642</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>61</x:v>
@@ -1245,634 +1212,289 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>285008</x:v>
+        <x:v>2874180</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>30183</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>300000</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>350000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>628597</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>221403</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>250000</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>350000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="F32" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>1750000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>817066</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>1803694</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:7">
-      <x:c r="A36" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B36" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C36" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F36" s="1">
-        <x:v>5168736</x:v>
-      </x:c>
-      <x:c r="G36" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:7">
-      <x:c r="A37" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B37" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C37" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F37" s="1">
-        <x:v>418058</x:v>
-      </x:c>
-      <x:c r="G37" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:7">
-      <x:c r="A38" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B38" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C38" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D38" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F38" s="1">
-        <x:v>80948</x:v>
-      </x:c>
-      <x:c r="G38" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:7">
-      <x:c r="A39" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B39" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C39" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D39" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E39" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F39" s="1">
-        <x:v>558813</x:v>
-      </x:c>
-      <x:c r="G39" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:7">
-      <x:c r="A40" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B40" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C40" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D40" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F40" s="1">
-        <x:v>1673736</x:v>
-      </x:c>
-      <x:c r="G40" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:7">
-      <x:c r="A41" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B41" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C41" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D41" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F41" s="1">
-        <x:v>771658</x:v>
-      </x:c>
-      <x:c r="G41" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:7">
-      <x:c r="A42" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B42" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C42" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D42" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F42" s="1">
-        <x:v>91656</x:v>
-      </x:c>
-      <x:c r="G42" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:7">
-      <x:c r="A43" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B43" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C43" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D43" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F43" s="1">
-        <x:v>141263</x:v>
-      </x:c>
-      <x:c r="G43" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:7">
-      <x:c r="A44" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B44" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C44" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D44" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E44" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F44" s="1">
-        <x:v>5017853</x:v>
-      </x:c>
-      <x:c r="G44" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:7">
-      <x:c r="A45" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B45" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C45" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D45" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E45" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F45" s="1">
-        <x:v>83860</x:v>
-      </x:c>
-      <x:c r="G45" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:7">
-      <x:c r="A46" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B46" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C46" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D46" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F46" s="1">
-        <x:v>515519</x:v>
-      </x:c>
-      <x:c r="G46" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:7">
-      <x:c r="A47" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B47" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C47" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D47" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F47" s="1">
-        <x:v>1564215</x:v>
-      </x:c>
-      <x:c r="G47" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:7">
-      <x:c r="A48" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B48" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C48" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D48" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E48" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F48" s="1">
-        <x:v>1012792</x:v>
-      </x:c>
-      <x:c r="G48" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:7">
-      <x:c r="A49" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B49" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C49" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D49" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F49" s="1">
-        <x:v>20483</x:v>
-      </x:c>
-      <x:c r="G49" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:7">
-      <x:c r="A50" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B50" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C50" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D50" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E50" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F50" s="1">
-        <x:v>91847</x:v>
-      </x:c>
-      <x:c r="G50" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1891,7 +1513,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E37"/>
+  <x:dimension ref="A1:E32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1921,206 +1543,206 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>11944100</x:v>
+        <x:v>6926247</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D3" s="1">
-        <x:v>836118</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>558813</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>1673736</x:v>
+        <x:v>320996</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>350000</x:v>
+        <x:v>580151</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>320996</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>580151</x:v>
+        <x:v>3455921</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>56045</x:v>
+        <x:v>628576</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>3455921</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>628576</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>285008</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>30183</x:v>
+        <x:v>817065</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
@@ -2134,7 +1756,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>9985740</x:v>
+        <x:v>2475788</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>12</x:v>
@@ -2142,393 +1764,308 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>817066</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>2475786</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>557012</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>83860</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>513868</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>628597</x:v>
+        <x:v>3590517</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>221403</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>3590517</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>350000</x:v>
+        <x:v>303642</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>250000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>243968</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>91847</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>161896</x:v>
+        <x:v>101750</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>282975</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>101750</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2874180</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>1543316</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:5">
-      <x:c r="A33" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B33" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C33" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D33" s="1">
-        <x:v>183312</x:v>
-      </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:5">
-      <x:c r="A34" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B34" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C34" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D34" s="1">
-        <x:v>2874180</x:v>
-      </x:c>
-      <x:c r="E34" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:5">
-      <x:c r="A35" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B35" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C35" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D35" s="1">
-        <x:v>282526</x:v>
-      </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:5">
-      <x:c r="A36" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B36" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C36" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D36" s="1">
-        <x:v>20483</x:v>
-      </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:5">
-      <x:c r="A37" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B37" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C37" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D37" s="1">
-        <x:v>1012792</x:v>
-      </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2547,7 +2084,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D34"/>
+  <x:dimension ref="A1:D29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2573,156 +2110,156 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>11944100</x:v>
+        <x:v>6926247</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>836118</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>558813</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>1673736</x:v>
+        <x:v>320996</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>350000</x:v>
+        <x:v>580151</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>320996</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>580151</x:v>
+        <x:v>3455921</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>56045</x:v>
+        <x:v>628576</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>3455921</x:v>
+        <x:v>315191</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>628576</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>315191</x:v>
+        <x:v>817065</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
@@ -2733,7 +2270,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>9985740</x:v>
+        <x:v>2475788</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>12</x:v>
@@ -2741,296 +2278,226 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>817066</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>2475786</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>557012</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>83860</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>513868</x:v>
+        <x:v>3590517</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>850000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>3590517</x:v>
+        <x:v>303642</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>600000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>243968</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>91847</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>161896</x:v>
+        <x:v>101750</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>350000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>282975</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>101750</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2874180</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>1543316</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:4">
-      <x:c r="A30" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B30" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C30" s="1">
-        <x:v>183312</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:4">
-      <x:c r="A31" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B31" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C31" s="1">
-        <x:v>2874180</x:v>
-      </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:4">
-      <x:c r="A32" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B32" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C32" s="1">
-        <x:v>282526</x:v>
-      </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:4">
-      <x:c r="A33" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B33" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C33" s="1">
-        <x:v>20483</x:v>
-      </x:c>
-      <x:c r="D33" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:4">
-      <x:c r="A34" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B34" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C34" s="1">
-        <x:v>1012792</x:v>
-      </x:c>
-      <x:c r="D34" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3049,7 +2516,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C19"/>
+  <x:dimension ref="A1:C15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3071,57 +2538,57 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>11944100</x:v>
+        <x:v>6926247</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>836118</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>2232549</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>56045</x:v>
+        <x:v>5335644</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>5335644</x:v>
+        <x:v>13278593</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -3129,142 +2596,98 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>13278592</x:v>
+        <x:v>956063</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>956063</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>513868</x:v>
+        <x:v>4440517</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>4440517</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>600000</x:v>
+        <x:v>303642</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>243968</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>91847</x:v>
+        <x:v>632975</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>161896</x:v>
+        <x:v>101750</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>632975</x:v>
+        <x:v>5628757</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:3">
-      <x:c r="A16" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B16" s="1">
-        <x:v>101750</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:3">
-      <x:c r="A17" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B17" s="1">
-        <x:v>6633334</x:v>
-      </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:3">
-      <x:c r="A18" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B18" s="1">
-        <x:v>20483</x:v>
-      </x:c>
-      <x:c r="C18" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:3">
-      <x:c r="A19" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B19" s="1">
-        <x:v>1012792</x:v>
-      </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3283,7 +2706,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B16"/>
+  <x:dimension ref="A1:B13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3301,122 +2724,98 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>11944100</x:v>
+        <x:v>6926247</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>836118</x:v>
+        <x:v>418060</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>2232549</x:v>
+        <x:v>5391689</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>5391689</x:v>
+        <x:v>14234656</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>14234655</x:v>
+        <x:v>513868</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>513868</x:v>
+        <x:v>4440517</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>4440517</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>600000</x:v>
+        <x:v>303642</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>243968</x:v>
+        <x:v>80948</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>91847</x:v>
+        <x:v>632975</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>161896</x:v>
+        <x:v>101750</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>632975</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:2">
-      <x:c r="A14" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B14" s="1">
-        <x:v>101750</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:2">
-      <x:c r="A15" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B15" s="1">
-        <x:v>6633334</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:2">
-      <x:c r="A16" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B16" s="1">
-        <x:v>1033275</x:v>
+        <x:v>5628757</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3435,12 +2834,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C24"/>
+  <x:dimension ref="A1:C21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
-    <x:col min="1" max="1" width="24.282054" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="23.424911" style="1" customWidth="1"/>
+    <x:col min="1" max="2" width="23.424911" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="13.853482" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -3457,21 +2855,21 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>11594100</x:v>
+        <x:v>6576247</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>350000</x:v>
@@ -3479,233 +2877,200 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>836118</x:v>
+        <x:v>418060</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>2232549</x:v>
+        <x:v>1229723</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>1229723</x:v>
+        <x:v>650000</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>650000</x:v>
+        <x:v>3511966</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>3511966</x:v>
+        <x:v>13158949</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>13158948</x:v>
+        <x:v>1075707</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>1075707</x:v>
+        <x:v>513868</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>513868</x:v>
+        <x:v>3590517</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>3590517</x:v>
+        <x:v>850000</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>850000</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>600000</x:v>
+        <x:v>303642</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>243968</x:v>
+        <x:v>80948</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>91847</x:v>
+        <x:v>282975</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>161896</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>282975</x:v>
+        <x:v>101750</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>350000</x:v>
+        <x:v>1004577</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>101750</x:v>
+        <x:v>1750000</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>2009154</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B22" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C22" s="1">
-        <x:v>1750000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:3">
-      <x:c r="A23" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B23" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C23" s="1">
         <x:v>2874180</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B24" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C24" s="1">
-        <x:v>1033275</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -1215,7 +1215,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>2874180</x:v>
+        <x:v>3442924</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>22</x:v>
@@ -2045,7 +2045,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>2874180</x:v>
+        <x:v>3442924</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>22</x:v>
@@ -2480,7 +2480,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>2874180</x:v>
+        <x:v>3442924</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>22</x:v>
@@ -2684,7 +2684,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>5628757</x:v>
+        <x:v>6197501</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>22</x:v>
@@ -2815,7 +2815,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>5628757</x:v>
+        <x:v>6197501</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3070,7 +3070,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>2874180</x:v>
+        <x:v>3442924</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -801,7 +801,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>328576</x:v>
+        <x:v>391861</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>22</x:v>
@@ -847,7 +847,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>320996</x:v>
+        <x:v>375931</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>22</x:v>
@@ -916,7 +916,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>580151</x:v>
+        <x:v>644489</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>22</x:v>
@@ -1054,7 +1054,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>6576247</x:v>
+        <x:v>6774919</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>22</x:v>
@@ -1077,7 +1077,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>101750</x:v>
+        <x:v>144600</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>22</x:v>
@@ -1146,7 +1146,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>3455921</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>22</x:v>
@@ -1552,7 +1552,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>6926247</x:v>
+        <x:v>7124919</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
         <x:v>22</x:v>
@@ -1603,7 +1603,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>320996</x:v>
+        <x:v>375931</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>22</x:v>
@@ -1620,7 +1620,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>580151</x:v>
+        <x:v>644489</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>22</x:v>
@@ -1654,7 +1654,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>3455921</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>22</x:v>
@@ -1671,7 +1671,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>628576</x:v>
+        <x:v>691861</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>22</x:v>
@@ -1977,7 +1977,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>101750</x:v>
+        <x:v>144600</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>22</x:v>
@@ -2116,7 +2116,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>6926247</x:v>
+        <x:v>7124919</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>22</x:v>
@@ -2158,7 +2158,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>320996</x:v>
+        <x:v>375931</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>22</x:v>
@@ -2172,7 +2172,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>580151</x:v>
+        <x:v>644489</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>22</x:v>
@@ -2200,7 +2200,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>3455921</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>22</x:v>
@@ -2214,7 +2214,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>628576</x:v>
+        <x:v>691861</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>22</x:v>
@@ -2424,7 +2424,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>101750</x:v>
+        <x:v>144600</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>22</x:v>
@@ -2541,7 +2541,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>6926247</x:v>
+        <x:v>7124919</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>22</x:v>
@@ -2574,7 +2574,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>5335644</x:v>
+        <x:v>6272674</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>22</x:v>
@@ -2673,7 +2673,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>101750</x:v>
+        <x:v>144600</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>22</x:v>
@@ -2727,7 +2727,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>6926247</x:v>
+        <x:v>7124919</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -2743,7 +2743,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>5391689</x:v>
+        <x:v>6328719</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -2807,7 +2807,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>101750</x:v>
+        <x:v>144600</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
@@ -2861,7 +2861,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>6576247</x:v>
+        <x:v>6774919</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -2894,7 +2894,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>1229723</x:v>
+        <x:v>1412281</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -2916,7 +2916,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>3511966</x:v>
+        <x:v>4266438</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -3037,7 +3037,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>101750</x:v>
+        <x:v>144600</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -801,7 +801,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>391861</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>22</x:v>
@@ -824,7 +824,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>3590517</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>22</x:v>
@@ -847,7 +847,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>375931</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>22</x:v>
@@ -916,7 +916,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>644489</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>22</x:v>
@@ -1054,7 +1054,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>6774919</x:v>
+        <x:v>7217154</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>22</x:v>
@@ -1192,7 +1192,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>303642</x:v>
+        <x:v>535135</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>22</x:v>
@@ -1215,7 +1215,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>3442924</x:v>
+        <x:v>3490086</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>22</x:v>
@@ -1552,7 +1552,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>7124919</x:v>
+        <x:v>7567154</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
         <x:v>22</x:v>
@@ -1603,7 +1603,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>375931</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>22</x:v>
@@ -1620,7 +1620,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>644489</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>22</x:v>
@@ -1671,7 +1671,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>691861</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>22</x:v>
@@ -1858,7 +1858,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>3590517</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>22</x:v>
@@ -1909,7 +1909,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>303642</x:v>
+        <x:v>535135</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>22</x:v>
@@ -2045,7 +2045,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>3442924</x:v>
+        <x:v>3490086</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>22</x:v>
@@ -2116,7 +2116,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>7124919</x:v>
+        <x:v>7567154</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>22</x:v>
@@ -2158,7 +2158,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>375931</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>22</x:v>
@@ -2172,7 +2172,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>644489</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>22</x:v>
@@ -2214,7 +2214,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>691861</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>22</x:v>
@@ -2340,7 +2340,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>3590517</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
         <x:v>22</x:v>
@@ -2368,7 +2368,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>303642</x:v>
+        <x:v>535135</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>22</x:v>
@@ -2480,7 +2480,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>3442924</x:v>
+        <x:v>3490086</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>22</x:v>
@@ -2541,7 +2541,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>7124919</x:v>
+        <x:v>7567154</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>22</x:v>
@@ -2574,7 +2574,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>6272674</x:v>
+        <x:v>6455232</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>22</x:v>
@@ -2618,7 +2618,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>4440517</x:v>
+        <x:v>8020138</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>22</x:v>
@@ -2640,7 +2640,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>303642</x:v>
+        <x:v>535135</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>22</x:v>
@@ -2684,7 +2684,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>6197501</x:v>
+        <x:v>6244663</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>22</x:v>
@@ -2727,7 +2727,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>7124919</x:v>
+        <x:v>7567154</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -2743,7 +2743,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>6328719</x:v>
+        <x:v>6511277</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -2767,7 +2767,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>4440517</x:v>
+        <x:v>8020138</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -2783,7 +2783,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>303642</x:v>
+        <x:v>535135</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
@@ -2815,7 +2815,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>6197501</x:v>
+        <x:v>6244663</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2861,7 +2861,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>6774919</x:v>
+        <x:v>7217154</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -2894,7 +2894,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>1412281</x:v>
+        <x:v>1594839</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -2960,7 +2960,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>3590517</x:v>
+        <x:v>7170138</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -2993,7 +2993,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>303642</x:v>
+        <x:v>535135</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -3070,7 +3070,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>3442924</x:v>
+        <x:v>3490086</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -132,18 +132,30 @@
     <x:t>NE</x:t>
   </x:si>
   <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
     <x:t>STEINMANN, JESSICA HART</x:t>
   </x:si>
   <x:si>
     <x:t>08</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
     <x:t>GOBER, CHRIS</x:t>
   </x:si>
   <x:si>
+    <x:t>SELL, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
     <x:t>NEHLS, TREVER</x:t>
   </x:si>
   <x:si>
@@ -159,6 +171,12 @@
     <x:t>IN</x:t>
   </x:si>
   <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOORE, FELIX BARRY</x:t>
   </x:si>
   <x:si>
@@ -187,6 +205,12 @@
   </x:si>
   <x:si>
     <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENENDEZ, ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
   </x:si>
   <x:si>
     <x:t>CLARK, JASMINE</x:t>
@@ -314,8 +338,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G35" totalsRowShown="0">
-  <x:autoFilter ref="A1:G35"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G39" totalsRowShown="0">
+  <x:autoFilter ref="A1:G39"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -330,8 +354,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E32" totalsRowShown="0">
-  <x:autoFilter ref="A1:E32"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E36" totalsRowShown="0">
+  <x:autoFilter ref="A1:E36"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -344,8 +368,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D29" totalsRowShown="0">
-  <x:autoFilter ref="A1:D29"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D33" totalsRowShown="0">
+  <x:autoFilter ref="A1:D33"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -357,8 +381,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C15" totalsRowShown="0">
-  <x:autoFilter ref="A1:C15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C17" totalsRowShown="0">
+  <x:autoFilter ref="A1:C17"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -369,8 +393,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B13" totalsRowShown="0">
-  <x:autoFilter ref="A1:B13"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B15" totalsRowShown="0">
+  <x:autoFilter ref="A1:B15"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -380,8 +404,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C21" totalsRowShown="0">
-  <x:autoFilter ref="A1:C21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C23" totalsRowShown="0">
+  <x:autoFilter ref="A1:C23"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -679,7 +703,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G35"/>
+  <x:dimension ref="A1:G39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -962,7 +986,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>771658</x:v>
+        <x:v>42720</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>22</x:v>
@@ -979,13 +1003,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>91656</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>22</x:v>
@@ -999,16 +1023,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>141263</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>22</x:v>
@@ -1028,10 +1052,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>513868</x:v>
+        <x:v>54372</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>22</x:v>
@@ -1045,16 +1069,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>7217154</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>22</x:v>
@@ -1062,22 +1086,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="F17" s="1">
-        <x:v>144600</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>22</x:v>
@@ -1085,45 +1109,45 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B18" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C18" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>56045</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>83860</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>22</x:v>
@@ -1131,22 +1155,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>4210393</x:v>
+        <x:v>144600</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>22</x:v>
@@ -1154,45 +1178,45 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>557012</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>535135</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>22</x:v>
@@ -1200,22 +1224,22 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>3490086</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>22</x:v>
@@ -1223,45 +1247,45 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>119644</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>285008</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>22</x:v>
@@ -1269,22 +1293,22 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>30183</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>22</x:v>
@@ -1292,22 +1316,22 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>300000</x:v>
+        <x:v>4345153</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>22</x:v>
@@ -1315,45 +1339,45 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>350000</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>350000</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>22</x:v>
@@ -1361,22 +1385,22 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>628597</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>22</x:v>
@@ -1384,22 +1408,22 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>221403</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>22</x:v>
@@ -1407,22 +1431,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>22</x:v>
@@ -1430,19 +1454,19 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F33" s="1">
         <x:v>350000</x:v>
@@ -1453,22 +1477,22 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>350000</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>22</x:v>
@@ -1476,24 +1500,116 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F35" s="1">
+        <x:v>221403</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:7">
+      <x:c r="A36" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F36" s="1">
+        <x:v>250000</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:7">
+      <x:c r="A37" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F37" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:7">
+      <x:c r="A38" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F38" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:7">
+      <x:c r="A39" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F35" s="1">
+      <x:c r="F39" s="1">
         <x:v>1750000</x:v>
       </x:c>
-      <x:c r="G35" s="1" t="s">
+      <x:c r="G39" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
@@ -1513,7 +1629,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E32"/>
+  <x:dimension ref="A1:E36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1543,16 +1659,16 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>7567154</x:v>
+        <x:v>7765826</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
         <x:v>22</x:v>
@@ -1577,7 +1693,7 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>16</x:v>
@@ -1628,10 +1744,10 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>21</x:v>
@@ -1645,10 +1761,10 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>21</x:v>
@@ -1679,10 +1795,10 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>11</x:v>
@@ -1696,10 +1812,10 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>11</x:v>
@@ -1764,10 +1880,10 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>11</x:v>
@@ -1781,10 +1897,10 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>11</x:v>
@@ -1798,13 +1914,13 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>513868</x:v>
@@ -1832,7 +1948,7 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>16</x:v>
@@ -1866,13 +1982,13 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>350000</x:v>
@@ -1883,13 +1999,13 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>250000</x:v>
@@ -1900,16 +2016,16 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>535135</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>22</x:v>
@@ -1934,7 +2050,7 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>16</x:v>
@@ -1968,16 +2084,16 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>144600</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>22</x:v>
@@ -1985,16 +2101,16 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>1750000</x:v>
+        <x:v>144600</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>22</x:v>
@@ -2002,16 +2118,16 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>771658</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>22</x:v>
@@ -2019,16 +2135,16 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>91656</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>22</x:v>
@@ -2036,16 +2152,16 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>3490086</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>22</x:v>
@@ -2053,18 +2169,86 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D32" s="1">
+        <x:v>91656</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:5">
+      <x:c r="A33" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D33" s="1">
+        <x:v>4345153</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:5">
+      <x:c r="A34" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D34" s="1">
+        <x:v>54372</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:5">
+      <x:c r="A35" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D35" s="1">
         <x:v>141263</x:v>
       </x:c>
-      <x:c r="E32" s="1" t="s">
+      <x:c r="E35" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:5">
+      <x:c r="A36" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D36" s="1">
+        <x:v>42720</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
@@ -2084,7 +2268,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D29"/>
+  <x:dimension ref="A1:D33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2113,10 +2297,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>7567154</x:v>
+        <x:v>7765826</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>22</x:v>
@@ -2180,7 +2364,7 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>21</x:v>
@@ -2194,7 +2378,7 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>21</x:v>
@@ -2222,7 +2406,7 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>11</x:v>
@@ -2278,7 +2462,7 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>11</x:v>
@@ -2292,7 +2476,7 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>11</x:v>
@@ -2306,10 +2490,10 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>513868</x:v>
@@ -2351,7 +2535,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>600000</x:v>
@@ -2362,13 +2546,13 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>535135</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>22</x:v>
@@ -2418,13 +2602,13 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>144600</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>22</x:v>
@@ -2432,13 +2616,13 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>1750000</x:v>
+        <x:v>144600</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>22</x:v>
@@ -2446,13 +2630,13 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>771658</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>22</x:v>
@@ -2460,13 +2644,13 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>91656</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>22</x:v>
@@ -2474,13 +2658,13 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>3490086</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>22</x:v>
@@ -2488,15 +2672,71 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C29" s="1">
+        <x:v>91656</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:4">
+      <x:c r="A30" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C30" s="1">
+        <x:v>4345153</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:4">
+      <x:c r="A31" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C31" s="1">
+        <x:v>54372</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:4">
+      <x:c r="A32" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C32" s="1">
         <x:v>141263</x:v>
       </x:c>
-      <x:c r="D29" s="1" t="s">
+      <x:c r="D32" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:4">
+      <x:c r="A33" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C33" s="1">
+        <x:v>42720</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
@@ -2516,7 +2756,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C15"/>
+  <x:dimension ref="A1:C17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2538,10 +2778,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>7567154</x:v>
+        <x:v>7765826</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>22</x:v>
@@ -2604,7 +2844,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>513868</x:v>
@@ -2626,7 +2866,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>600000</x:v>
@@ -2637,10 +2877,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>535135</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>22</x:v>
@@ -2670,10 +2910,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>144600</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>22</x:v>
@@ -2681,12 +2921,34 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B15" s="1">
+        <x:v>144600</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B16" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B15" s="1">
-        <x:v>6244663</x:v>
-      </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="B17" s="1">
+        <x:v>7196822</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
@@ -2706,7 +2968,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B13"/>
+  <x:dimension ref="A1:B15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2724,10 +2986,10 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>7567154</x:v>
+        <x:v>7765826</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -2756,7 +3018,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>513868</x:v>
@@ -2772,7 +3034,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>600000</x:v>
@@ -2780,10 +3042,10 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>535135</x:v>
+        <x:v>1069843</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
@@ -2804,18 +3066,34 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>144600</x:v>
+        <x:v>64395</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B13" s="1">
+        <x:v>144600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:2">
+      <x:c r="A14" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B14" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:2">
+      <x:c r="A15" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B13" s="1">
-        <x:v>6244663</x:v>
+      <x:c r="B15" s="1">
+        <x:v>7196822</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2834,7 +3112,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C21"/>
+  <x:dimension ref="A1:C23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2858,18 +3136,18 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>7217154</x:v>
+        <x:v>7415826</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>350000</x:v>
@@ -2899,7 +3177,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>21</x:v>
@@ -2910,7 +3188,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>21</x:v>
@@ -2932,7 +3210,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>11</x:v>
@@ -2946,7 +3224,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>513868</x:v>
@@ -2965,7 +3243,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>25</x:v>
@@ -2976,10 +3254,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>600000</x:v>
@@ -2987,13 +3265,13 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>535135</x:v>
+        <x:v>1069843</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -3020,7 +3298,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>36</x:v>
@@ -3031,46 +3309,68 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>144600</x:v>
+        <x:v>64395</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>1004577</x:v>
+        <x:v>144600</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>1750000</x:v>
+        <x:v>56118</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>3490086</x:v>
+        <x:v>1101669</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C22" s="1">
+        <x:v>1750000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C23" s="1">
+        <x:v>4345153</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -162,6 +162,12 @@
     <x:t>22</x:t>
   </x:si>
   <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
     <x:t>BAIRD, JAMES R DR.</x:t>
   </x:si>
   <x:si>
@@ -213,6 +219,12 @@
     <x:t>NJ</x:t>
   </x:si>
   <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
     <x:t>CLARK, JASMINE</x:t>
   </x:si>
   <x:si>
@@ -229,9 +241,6 @@
   </x:si>
   <x:si>
     <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
   </x:si>
   <x:si>
     <x:t>KELLY, ROBIN</x:t>
@@ -338,8 +347,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G39" totalsRowShown="0">
-  <x:autoFilter ref="A1:G39"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G41" totalsRowShown="0">
+  <x:autoFilter ref="A1:G41"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -354,8 +363,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E36" totalsRowShown="0">
-  <x:autoFilter ref="A1:E36"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E38" totalsRowShown="0">
+  <x:autoFilter ref="A1:E38"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -368,8 +377,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D33" totalsRowShown="0">
-  <x:autoFilter ref="A1:D33"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D35" totalsRowShown="0">
+  <x:autoFilter ref="A1:D35"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -381,8 +390,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C17" totalsRowShown="0">
-  <x:autoFilter ref="A1:C17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C18" totalsRowShown="0">
+  <x:autoFilter ref="A1:C18"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -703,7 +712,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G39"/>
+  <x:dimension ref="A1:G41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -986,7 +995,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>42720</x:v>
+        <x:v>85440</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>22</x:v>
@@ -1055,7 +1064,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>54372</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>22</x:v>
@@ -1098,10 +1107,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>513868</x:v>
+        <x:v>35211</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>22</x:v>
@@ -1115,16 +1124,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>56118</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>22</x:v>
@@ -1141,13 +1150,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>7415826</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>22</x:v>
@@ -1155,22 +1164,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
+      <x:c r="D20" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="F20" s="1">
-        <x:v>144600</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>22</x:v>
@@ -1178,68 +1187,68 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="E21" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="F21" s="1">
-        <x:v>56045</x:v>
+        <x:v>144600</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>83860</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>64395</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>22</x:v>
@@ -1247,22 +1256,22 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>4210393</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>22</x:v>
@@ -1270,45 +1279,45 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>557012</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>1069843</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>22</x:v>
@@ -1316,22 +1325,22 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>4345153</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>22</x:v>
@@ -1339,45 +1348,45 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>119644</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>285008</x:v>
+        <x:v>4345153</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>22</x:v>
@@ -1385,45 +1394,45 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>30183</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B31" s="1" t="s">
+      <x:c r="D31" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C31" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>300000</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>22</x:v>
@@ -1431,22 +1440,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C32" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>22</x:v>
@@ -1454,22 +1463,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>350000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>22</x:v>
@@ -1477,22 +1486,22 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>628597</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>22</x:v>
@@ -1500,22 +1509,22 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>221403</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>22</x:v>
@@ -1523,22 +1532,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>250000</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>22</x:v>
@@ -1546,10 +1555,10 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>80</x:v>
@@ -1558,10 +1567,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>350000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>22</x:v>
@@ -1569,10 +1578,10 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>81</x:v>
@@ -1581,10 +1590,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>22</x:v>
@@ -1592,24 +1601,70 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F39" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:7">
+      <x:c r="A40" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F40" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:7">
+      <x:c r="A41" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F39" s="1">
+      <x:c r="F41" s="1">
         <x:v>1750000</x:v>
       </x:c>
-      <x:c r="G39" s="1" t="s">
+      <x:c r="G41" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
@@ -1629,7 +1684,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E36"/>
+  <x:dimension ref="A1:E38"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1659,13 +1714,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>7765826</x:v>
@@ -1693,7 +1748,7 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>16</x:v>
@@ -1744,10 +1799,10 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>21</x:v>
@@ -1761,10 +1816,10 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>21</x:v>
@@ -1795,10 +1850,10 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>11</x:v>
@@ -1812,10 +1867,10 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>11</x:v>
@@ -1880,7 +1935,7 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>41</x:v>
@@ -1897,10 +1952,10 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>11</x:v>
@@ -1914,13 +1969,13 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>513868</x:v>
@@ -1948,7 +2003,7 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>16</x:v>
@@ -1982,13 +2037,13 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>350000</x:v>
@@ -1999,13 +2054,13 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>250000</x:v>
@@ -2016,13 +2071,13 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>1069843</x:v>
@@ -2050,7 +2105,7 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>16</x:v>
@@ -2084,13 +2139,13 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>64395</x:v>
@@ -2101,13 +2156,13 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>144600</x:v>
@@ -2118,13 +2173,13 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>56118</x:v>
@@ -2135,7 +2190,7 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>16</x:v>
@@ -2186,33 +2241,33 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>4345153</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>54372</x:v>
+        <x:v>4345153</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>22</x:v>
@@ -2220,16 +2275,16 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>141263</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>22</x:v>
@@ -2237,18 +2292,52 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>42720</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:5">
+      <x:c r="A37" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D37" s="1">
+        <x:v>35211</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:5">
+      <x:c r="A38" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D38" s="1">
+        <x:v>85440</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
@@ -2268,7 +2357,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D33"/>
+  <x:dimension ref="A1:D35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2297,7 +2386,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>7765826</x:v>
@@ -2364,7 +2453,7 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>21</x:v>
@@ -2378,7 +2467,7 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>21</x:v>
@@ -2406,7 +2495,7 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>11</x:v>
@@ -2476,7 +2565,7 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>11</x:v>
@@ -2490,10 +2579,10 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>513868</x:v>
@@ -2535,7 +2624,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>600000</x:v>
@@ -2546,10 +2635,10 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>1069843</x:v>
@@ -2605,7 +2694,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>64395</x:v>
@@ -2616,10 +2705,10 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>144600</x:v>
@@ -2630,10 +2719,10 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>56118</x:v>
@@ -2686,27 +2775,27 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>4345153</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>54372</x:v>
+        <x:v>4345153</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>22</x:v>
@@ -2714,13 +2803,13 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>141263</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>22</x:v>
@@ -2728,15 +2817,43 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>42720</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:4">
+      <x:c r="A34" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C34" s="1">
+        <x:v>35211</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:4">
+      <x:c r="A35" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C35" s="1">
+        <x:v>85440</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
@@ -2756,7 +2873,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C17"/>
+  <x:dimension ref="A1:C18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2778,7 +2895,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>7765826</x:v>
@@ -2844,7 +2961,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>513868</x:v>
@@ -2866,7 +2983,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>600000</x:v>
@@ -2877,7 +2994,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>1069843</x:v>
@@ -2910,7 +3027,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>64395</x:v>
@@ -2921,7 +3038,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>144600</x:v>
@@ -2932,7 +3049,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>56118</x:v>
@@ -2946,9 +3063,20 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>7196822</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B18" s="1">
+        <x:v>7329125</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
@@ -2986,7 +3114,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>7765826</x:v>
@@ -3018,7 +3146,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>513868</x:v>
@@ -3034,7 +3162,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>600000</x:v>
@@ -3042,7 +3170,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>1069843</x:v>
@@ -3066,7 +3194,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>64395</x:v>
@@ -3074,7 +3202,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>144600</x:v>
@@ -3082,7 +3210,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>56118</x:v>
@@ -3093,7 +3221,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>7196822</x:v>
+        <x:v>7376287</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3136,7 +3264,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>7415826</x:v>
@@ -3144,10 +3272,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>350000</x:v>
@@ -3177,7 +3305,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>21</x:v>
@@ -3188,7 +3316,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>21</x:v>
@@ -3210,7 +3338,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>11</x:v>
@@ -3224,7 +3352,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>513868</x:v>
@@ -3243,7 +3371,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>25</x:v>
@@ -3254,10 +3382,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>600000</x:v>
@@ -3265,10 +3393,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1069843</x:v>
@@ -3298,7 +3426,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>36</x:v>
@@ -3309,10 +3437,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>64395</x:v>
@@ -3320,10 +3448,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>144600</x:v>
@@ -3334,7 +3462,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>56118</x:v>
@@ -3348,12 +3476,12 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>1101669</x:v>
+        <x:v>1233972</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>39</x:v>
@@ -3364,13 +3492,13 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>4345153</x:v>
+        <x:v>4392315</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -78,49 +78,166 @@
     <x:t>DEFEND AMERICAN JOBS</x:t>
   </x:si>
   <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATRONIS, JIMMY JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALKINSHAW, JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKARSKY, STELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
     <x:t>FULLER, CLAY</x:t>
   </x:si>
   <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
     <x:t>GA</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
   </x:si>
   <x:si>
     <x:t>BARR, GARLAND ANDY</x:t>
   </x:si>
   <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
     <x:t>KY</x:t>
   </x:si>
   <x:si>
+    <x:t>TORRES, RITCHIE JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
     <x:t>KINGSTON, JACK REP.</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENENDEZ, ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
   </x:si>
   <x:si>
     <x:t>GAINES, HOUSTON</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
   </x:si>
   <x:si>
     <x:t>SMITH, ADRIAN</x:t>
@@ -138,30 +255,12 @@
     <x:t>38</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
     <x:t>SELL, TOM</x:t>
   </x:si>
   <x:si>
     <x:t>19</x:t>
   </x:si>
   <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
     <x:t>DE LA CRUZ, CARLOS JR.</x:t>
   </x:si>
   <x:si>
@@ -183,64 +282,7 @@
     <x:t>SC</x:t>
   </x:si>
   <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TORRES, RITCHIE JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENENDEZ, ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN, ALEXANDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
   </x:si>
   <x:si>
     <x:t>KELLY, ROBIN</x:t>
@@ -250,15 +292,6 @@
   </x:si>
   <x:si>
     <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
   </x:si>
   <x:si>
     <x:t>MORRIS, NATE</x:t>
@@ -347,8 +380,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G41" totalsRowShown="0">
-  <x:autoFilter ref="A1:G41"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G56" totalsRowShown="0">
+  <x:autoFilter ref="A1:G56"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -363,8 +396,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E38" totalsRowShown="0">
-  <x:autoFilter ref="A1:E38"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E43" totalsRowShown="0">
+  <x:autoFilter ref="A1:E43"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -377,8 +410,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D35" totalsRowShown="0">
-  <x:autoFilter ref="A1:D35"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D40" totalsRowShown="0">
+  <x:autoFilter ref="A1:D40"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -390,8 +423,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C18" totalsRowShown="0">
-  <x:autoFilter ref="A1:C18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C22" totalsRowShown="0">
+  <x:autoFilter ref="A1:C22"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -402,8 +435,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B15" totalsRowShown="0">
-  <x:autoFilter ref="A1:B15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B18" totalsRowShown="0">
+  <x:autoFilter ref="A1:B18"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -413,8 +446,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C23" totalsRowShown="0">
-  <x:autoFilter ref="A1:C23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C26" totalsRowShown="0">
+  <x:autoFilter ref="A1:C26"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -712,12 +745,12 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G41"/>
+  <x:dimension ref="A1:G56"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
     <x:col min="1" max="1" width="15.710625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="23.424911" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="24.282054" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="29.424911" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="25.282054" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="23.424911" style="1" customWidth="1"/>
@@ -765,7 +798,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>817065</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -788,7 +821,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>2475788</x:v>
+        <x:v>1803694</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -811,7 +844,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>9866096</x:v>
+        <x:v>5168736</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -828,16 +861,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="F5" s="1">
-        <x:v>455146</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
@@ -848,19 +881,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>7170138</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
@@ -871,19 +904,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+      <x:c r="E7" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="F7" s="1">
-        <x:v>430866</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
@@ -897,16 +930,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>418060</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
@@ -920,16 +953,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>80948</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
@@ -940,19 +973,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="F10" s="1">
-        <x:v>708827</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
@@ -963,19 +996,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>282975</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
@@ -989,154 +1022,154 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="F12" s="1">
-        <x:v>85440</x:v>
+        <x:v>5017853</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>771658</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>91656</x:v>
+        <x:v>515519</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>108744</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>141263</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="F17" s="1">
-        <x:v>35211</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>513868</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
@@ -1147,525 +1180,870 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>56118</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>7415826</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="F21" s="1">
-        <x:v>144600</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="E22" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="F22" s="1">
-        <x:v>56045</x:v>
+        <x:v>187450</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>83860</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>64395</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="F25" s="1">
-        <x:v>47162</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>4210393</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>557012</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>1069843</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>4345153</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>119644</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>285008</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>30183</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>300000</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>350000</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B35" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C35" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>350000</x:v>
+        <x:v>85440</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>628597</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>221403</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>250000</x:v>
+        <x:v>2780938</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C39" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>350000</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>350000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F41" s="1">
+        <x:v>35211</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:7">
+      <x:c r="A42" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F42" s="1">
+        <x:v>513868</x:v>
+      </x:c>
+      <x:c r="G42" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:7">
+      <x:c r="A43" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D41" s="1" t="s">
+      <x:c r="D43" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F43" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:7">
+      <x:c r="A44" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E41" s="1" t="s">
+      <x:c r="E44" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F44" s="1">
+        <x:v>7415826</x:v>
+      </x:c>
+      <x:c r="G44" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:7">
+      <x:c r="A45" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F45" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G45" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:7">
+      <x:c r="A46" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F46" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G46" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:7">
+      <x:c r="A47" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F47" s="1">
+        <x:v>4697360</x:v>
+      </x:c>
+      <x:c r="G47" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:7">
+      <x:c r="A48" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F41" s="1">
+      <x:c r="B48" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F48" s="1">
+        <x:v>119644</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:7">
+      <x:c r="A49" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F49" s="1">
+        <x:v>285008</x:v>
+      </x:c>
+      <x:c r="G49" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:7">
+      <x:c r="A50" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F50" s="1">
+        <x:v>30183</x:v>
+      </x:c>
+      <x:c r="G50" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:7">
+      <x:c r="A51" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E51" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F51" s="1">
+        <x:v>628597</x:v>
+      </x:c>
+      <x:c r="G51" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:7">
+      <x:c r="A52" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F52" s="1">
+        <x:v>221403</x:v>
+      </x:c>
+      <x:c r="G52" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:7">
+      <x:c r="A53" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F53" s="1">
+        <x:v>250000</x:v>
+      </x:c>
+      <x:c r="G53" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:7">
+      <x:c r="A54" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B54" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F54" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G54" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:7">
+      <x:c r="A55" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B55" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C55" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D55" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E55" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F55" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G55" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:7">
+      <x:c r="A56" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D56" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F56" s="1">
         <x:v>1750000</x:v>
       </x:c>
-      <x:c r="G41" s="1" t="s">
-        <x:v>22</x:v>
+      <x:c r="G56" s="1" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1684,7 +2062,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E38"/>
+  <x:dimension ref="A1:E43"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1714,104 +2092,104 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>7765826</x:v>
+        <x:v>12783679</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="1">
-        <x:v>418060</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>350000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="D5" s="1">
-        <x:v>430866</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>708827</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>56045</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
@@ -1819,115 +2197,115 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>4210393</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>755146</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>285008</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>30183</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>9985740</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>817065</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>2475788</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>12</x:v>
@@ -1935,410 +2313,495 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>557012</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>83860</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>513868</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>628597</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>221403</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>7170138</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>350000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>250000</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>1069843</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>80948</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>350000</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>282975</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>64395</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>144600</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>56118</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>1750000</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>771658</x:v>
+        <x:v>187450</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>91656</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>47162</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>4345153</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>108744</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B36" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>141263</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>35211</x:v>
+        <x:v>4345153</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D38" s="1">
+        <x:v>108744</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:5">
+      <x:c r="A39" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D39" s="1">
+        <x:v>282526</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:5">
+      <x:c r="A40" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D40" s="1">
+        <x:v>35211</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:5">
+      <x:c r="A41" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D41" s="1">
         <x:v>85440</x:v>
       </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>22</x:v>
+      <x:c r="E41" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:5">
+      <x:c r="A42" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D42" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:5">
+      <x:c r="A43" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D43" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2357,7 +2820,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D35"/>
+  <x:dimension ref="A1:D40"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2386,13 +2849,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>7765826</x:v>
+        <x:v>12783679</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
@@ -2400,150 +2863,150 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>418060</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>350000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="C5" s="1">
-        <x:v>430866</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>708827</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>56045</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>4210393</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>755146</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>315191</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>9985740</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>817065</x:v>
+        <x:v>315191</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>2475788</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>12</x:v>
@@ -2551,72 +3014,72 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>557012</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>83860</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>513868</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>850000</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>7170138</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
@@ -2624,237 +3087,307 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>600000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>1069843</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>80948</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>350000</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>282975</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>64395</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>144600</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>56118</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>1750000</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>771658</x:v>
+        <x:v>187450</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>91656</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>47162</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>4345153</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>108744</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>141263</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>35211</x:v>
+        <x:v>4345153</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C35" s="1">
+        <x:v>108744</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:4">
+      <x:c r="A36" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C36" s="1">
+        <x:v>282526</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:4">
+      <x:c r="A37" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C37" s="1">
+        <x:v>35211</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:4">
+      <x:c r="A38" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C38" s="1">
         <x:v>85440</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>22</x:v>
+      <x:c r="D38" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:4">
+      <x:c r="A39" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C39" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:4">
+      <x:c r="A40" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C40" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2873,7 +3406,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C18"/>
+  <x:dimension ref="A1:C22"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2895,57 +3428,57 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>7765826</x:v>
+        <x:v>12783679</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>418060</x:v>
+        <x:v>836118</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>56045</x:v>
+        <x:v>2232549</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>6455232</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>13278593</x:v>
+        <x:v>6455232</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -2953,131 +3486,175 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>956063</x:v>
+        <x:v>13278592</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>513868</x:v>
+        <x:v>956063</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>8020138</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>600000</x:v>
+        <x:v>8020138</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>1069843</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>80948</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>632975</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>64395</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>144600</x:v>
+        <x:v>632975</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>56118</x:v>
+        <x:v>64395</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>47162</x:v>
+        <x:v>187450</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>7329125</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B19" s="1">
+        <x:v>47162</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B20" s="1">
+        <x:v>8333702</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B21" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B22" s="1">
+        <x:v>1012792</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3096,7 +3673,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B15"/>
+  <x:dimension ref="A1:B18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3114,114 +3691,138 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>7765826</x:v>
+        <x:v>12783679</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>418060</x:v>
+        <x:v>836118</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>6511277</x:v>
+        <x:v>2232549</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>14234656</x:v>
+        <x:v>6511277</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>513868</x:v>
+        <x:v>14234655</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>8020138</x:v>
+        <x:v>513868</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>600000</x:v>
+        <x:v>8020138</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>1069843</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>80948</x:v>
+        <x:v>1069843</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>632975</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>64395</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>144600</x:v>
+        <x:v>632975</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>56118</x:v>
+        <x:v>64395</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>7376287</x:v>
+        <x:v>187450</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:2">
+      <x:c r="A16" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B16" s="1">
+        <x:v>56118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:2">
+      <x:c r="A17" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B17" s="1">
+        <x:v>8380864</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:2">
+      <x:c r="A18" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B18" s="1">
+        <x:v>1033275</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3240,11 +3841,12 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C23"/>
+  <x:dimension ref="A1:C26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
-    <x:col min="1" max="2" width="23.424911" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="24.282054" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="23.424911" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="13.853482" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -3264,18 +3866,18 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>7415826</x:v>
+        <x:v>12433679</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>350000</x:v>
@@ -3286,10 +3888,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>418060</x:v>
+        <x:v>836118</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -3297,21 +3899,21 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>1594839</x:v>
+        <x:v>2232549</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>650000</x:v>
+        <x:v>1594839</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -3319,43 +3921,43 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>4266438</x:v>
+        <x:v>650000</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>13158949</x:v>
+        <x:v>4266438</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>1075707</x:v>
+        <x:v>13158948</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>513868</x:v>
+        <x:v>1075707</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -3363,32 +3965,32 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>7170138</x:v>
+        <x:v>513868</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>850000</x:v>
+        <x:v>7170138</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>600000</x:v>
+        <x:v>850000</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -3396,54 +3998,54 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>1069843</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>80948</x:v>
+        <x:v>1069843</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>282975</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>64395</x:v>
+        <x:v>282975</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -3451,54 +4053,87 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>144600</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>56118</x:v>
+        <x:v>64395</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>1233972</x:v>
+        <x:v>187450</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>1750000</x:v>
+        <x:v>56118</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C23" s="1">
+        <x:v>2238549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B23" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C23" s="1">
+      <x:c r="B24" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C24" s="1">
+        <x:v>1750000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C25" s="1">
         <x:v>4392315</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C26" s="1">
+        <x:v>1033275</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -225,6 +225,9 @@
     <x:t>GREEN, ALEXANDER</x:t>
   </x:si>
   <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAINES, HOUSTON</x:t>
   </x:si>
   <x:si>
@@ -255,6 +258,12 @@
     <x:t>38</x:t>
   </x:si>
   <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
     <x:t>SELL, TOM</x:t>
   </x:si>
   <x:si>
@@ -280,6 +289,9 @@
   </x:si>
   <x:si>
     <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
   </x:si>
   <x:si>
     <x:t>COLLINS, MICHAEL A JR</x:t>
@@ -380,8 +392,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G56" totalsRowShown="0">
-  <x:autoFilter ref="A1:G56"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G60" totalsRowShown="0">
+  <x:autoFilter ref="A1:G60"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -396,8 +408,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E43" totalsRowShown="0">
-  <x:autoFilter ref="A1:E43"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E46" totalsRowShown="0">
+  <x:autoFilter ref="A1:E46"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -410,8 +422,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D40" totalsRowShown="0">
-  <x:autoFilter ref="A1:D40"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D42" totalsRowShown="0">
+  <x:autoFilter ref="A1:D42"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -446,8 +458,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C26" totalsRowShown="0">
-  <x:autoFilter ref="A1:C26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C27" totalsRowShown="0">
+  <x:autoFilter ref="A1:C27"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -745,7 +757,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G56"/>
+  <x:dimension ref="A1:G60"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1335,22 +1347,22 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>418060</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>21</x:v>
@@ -1364,16 +1376,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>80948</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>21</x:v>
@@ -1381,68 +1393,68 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>47162</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>708827</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>4210393</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>21</x:v>
@@ -1450,25 +1462,25 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>672092</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
@@ -1479,16 +1491,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>41493</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>21</x:v>
@@ -1496,45 +1508,45 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>1069843</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>282975</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>21</x:v>
@@ -1542,22 +1554,22 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>85440</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>21</x:v>
@@ -1571,16 +1583,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>771658</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>21</x:v>
@@ -1594,16 +1606,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>91656</x:v>
+        <x:v>85440</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>21</x:v>
@@ -1611,22 +1623,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>2780938</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>21</x:v>
@@ -1640,16 +1652,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>108744</x:v>
+        <x:v>25663</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>21</x:v>
@@ -1663,16 +1675,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>141263</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>21</x:v>
@@ -1680,22 +1692,22 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>35211</x:v>
+        <x:v>4085945</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>21</x:v>
@@ -1709,16 +1721,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="D42" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>513868</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>21</x:v>
@@ -1732,16 +1744,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>56118</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>21</x:v>
@@ -1755,16 +1767,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>7415826</x:v>
+        <x:v>70422</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>21</x:v>
@@ -1772,22 +1784,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>350000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>21</x:v>
@@ -1795,22 +1807,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>350000</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>21</x:v>
@@ -1818,68 +1830,68 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>4697360</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>119644</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>285008</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>21</x:v>
@@ -1887,22 +1899,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>30183</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>21</x:v>
@@ -1910,68 +1922,68 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>628597</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>221403</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>250000</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>21</x:v>
@@ -1979,22 +1991,22 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>350000</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>21</x:v>
@@ -2008,16 +2020,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>350000</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>21</x:v>
@@ -2031,18 +2043,110 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F56" s="1">
+        <x:v>221403</x:v>
+      </x:c>
+      <x:c r="G56" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:7">
+      <x:c r="A57" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B57" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C57" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E57" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F57" s="1">
+        <x:v>250000</x:v>
+      </x:c>
+      <x:c r="G57" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:7">
+      <x:c r="A58" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B58" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E58" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F58" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G58" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:7">
+      <x:c r="A59" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B59" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E59" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F59" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G59" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:7">
+      <x:c r="A60" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B60" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C60" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D60" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E60" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F56" s="1">
+      <x:c r="F60" s="1">
         <x:v>1750000</x:v>
       </x:c>
-      <x:c r="G56" s="1" t="s">
+      <x:c r="G60" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2062,7 +2166,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E43"/>
+  <x:dimension ref="A1:E46"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2160,7 +2264,7 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>16</x:v>
@@ -2197,13 +2301,13 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>708827</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>21</x:v>
@@ -2211,24 +2315,24 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>56045</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>42</x:v>
@@ -2237,24 +2341,24 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>4210393</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>755146</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>21</x:v>
@@ -2262,16 +2366,16 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>285008</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>21</x:v>
@@ -2279,16 +2383,16 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>21</x:v>
@@ -2296,33 +2400,33 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>9985740</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>817066</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>12</x:v>
@@ -2330,16 +2434,16 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>2475786</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>12</x:v>
@@ -2347,33 +2451,33 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>557012</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>83860</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>21</x:v>
@@ -2381,16 +2485,16 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>513868</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>21</x:v>
@@ -2398,16 +2502,16 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>628597</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>21</x:v>
@@ -2415,7 +2519,7 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>16</x:v>
@@ -2424,7 +2528,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>221403</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>21</x:v>
@@ -2432,16 +2536,16 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>7170138</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>21</x:v>
@@ -2449,16 +2553,16 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>350000</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>21</x:v>
@@ -2466,16 +2570,16 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>21</x:v>
@@ -2483,16 +2587,16 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>1069843</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>21</x:v>
@@ -2500,16 +2604,16 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>91847</x:v>
+        <x:v>1069843</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>21</x:v>
@@ -2517,16 +2621,16 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>21</x:v>
@@ -2534,16 +2638,16 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>21</x:v>
@@ -2551,16 +2655,16 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>21</x:v>
@@ -2568,16 +2672,16 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>64395</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>21</x:v>
@@ -2585,16 +2689,16 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>187450</x:v>
+        <x:v>99285</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>21</x:v>
@@ -2602,16 +2706,16 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>56118</x:v>
+        <x:v>187450</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>21</x:v>
@@ -2619,16 +2723,16 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>1750000</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>21</x:v>
@@ -2636,16 +2740,16 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>1543316</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>21</x:v>
@@ -2653,16 +2757,16 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>183312</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>21</x:v>
@@ -2670,33 +2774,33 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>47162</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>4345153</x:v>
+        <x:v>25663</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>21</x:v>
@@ -2704,16 +2808,16 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>108744</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>21</x:v>
@@ -2721,33 +2825,33 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>282526</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>35211</x:v>
+        <x:v>5650160</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>21</x:v>
@@ -2755,16 +2859,16 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>85440</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>21</x:v>
@@ -2772,35 +2876,86 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>20483</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D43" s="1">
+        <x:v>70422</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:5">
+      <x:c r="A44" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D44" s="1">
+        <x:v>85440</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:5">
+      <x:c r="A45" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D45" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:5">
+      <x:c r="A46" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B43" s="1" t="s">
+      <x:c r="B46" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C43" s="1" t="s">
+      <x:c r="C46" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D43" s="1">
+      <x:c r="D46" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E43" s="1" t="s">
+      <x:c r="E46" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2820,7 +2975,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D40"/>
+  <x:dimension ref="A1:D42"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2922,7 +3077,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>430866</x:v>
+        <x:v>861732</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>21</x:v>
@@ -2986,7 +3141,7 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>11</x:v>
@@ -3070,10 +3225,10 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>513868</x:v>
@@ -3115,7 +3270,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>600000</x:v>
@@ -3126,10 +3281,10 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>1069843</x:v>
@@ -3171,7 +3326,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>350000</x:v>
@@ -3182,10 +3337,10 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>282975</x:v>
@@ -3202,7 +3357,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>64395</x:v>
+        <x:v>99285</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>21</x:v>
@@ -3224,13 +3379,13 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>56118</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>21</x:v>
@@ -3238,13 +3393,13 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>1750000</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
         <x:v>21</x:v>
@@ -3252,13 +3407,13 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>1543316</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>21</x:v>
@@ -3266,13 +3421,13 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>21</x:v>
@@ -3280,27 +3435,27 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>47162</x:v>
+        <x:v>25663</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>4345153</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
         <x:v>21</x:v>
@@ -3308,27 +3463,27 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>108744</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>282526</x:v>
+        <x:v>5650160</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
         <x:v>21</x:v>
@@ -3336,13 +3491,13 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>35211</x:v>
+        <x:v>108744</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>21</x:v>
@@ -3350,13 +3505,13 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>85440</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
         <x:v>21</x:v>
@@ -3364,29 +3519,57 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>20483</x:v>
+        <x:v>70422</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C40" s="1">
+        <x:v>85440</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:4">
+      <x:c r="A41" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B40" s="1" t="s">
+      <x:c r="B41" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C40" s="1">
+      <x:c r="C41" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:4">
+      <x:c r="A42" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C42" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D40" s="1" t="s">
+      <x:c r="D42" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -3475,7 +3658,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>6455232</x:v>
+        <x:v>6886098</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>21</x:v>
@@ -3505,7 +3688,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>513868</x:v>
@@ -3527,7 +3710,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>600000</x:v>
@@ -3538,7 +3721,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1069843</x:v>
@@ -3571,7 +3754,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>632975</x:v>
@@ -3585,7 +3768,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>64395</x:v>
+        <x:v>99285</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>21</x:v>
@@ -3604,10 +3787,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>56118</x:v>
+        <x:v>606118</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>21</x:v>
@@ -3629,7 +3812,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>8333702</x:v>
+        <x:v>9699583</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>21</x:v>
@@ -3718,7 +3901,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>6511277</x:v>
+        <x:v>6942143</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -3731,7 +3914,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>513868</x:v>
@@ -3747,7 +3930,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>600000</x:v>
@@ -3755,7 +3938,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1069843</x:v>
@@ -3779,7 +3962,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>632975</x:v>
@@ -3790,7 +3973,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>64395</x:v>
+        <x:v>99285</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -3803,10 +3986,10 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>56118</x:v>
+        <x:v>606118</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
@@ -3814,7 +3997,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>8380864</x:v>
+        <x:v>9746745</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -3841,7 +4024,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C26"/>
+  <x:dimension ref="A1:C27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3913,7 +4096,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>1594839</x:v>
+        <x:v>2025705</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -3965,7 +4148,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>513868</x:v>
@@ -3998,7 +4181,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>600000</x:v>
@@ -4009,7 +4192,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>1069843</x:v>
@@ -4042,7 +4225,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>282975</x:v>
@@ -4053,7 +4236,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>350000</x:v>
@@ -4067,7 +4250,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>64395</x:v>
+        <x:v>99285</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -4086,7 +4269,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>56118</x:v>
@@ -4094,35 +4277,35 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>2238549</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2299423</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>4392315</x:v>
+        <x:v>1750000</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -4130,9 +4313,20 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C26" s="1">
+        <x:v>5697322</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C26" s="1">
+      <x:c r="C27" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -1569,7 +1569,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>1069843</x:v>
+        <x:v>2062516</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>21</x:v>
@@ -1615,7 +1615,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>85440</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>21</x:v>
@@ -1661,7 +1661,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>25663</x:v>
+        <x:v>436280</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>21</x:v>
@@ -1707,7 +1707,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>4085945</x:v>
+        <x:v>4103505</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>21</x:v>
@@ -1730,7 +1730,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>108744</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>21</x:v>
@@ -1776,7 +1776,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>70422</x:v>
+        <x:v>581175</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>21</x:v>
@@ -2144,7 +2144,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>21</x:v>
@@ -2613,7 +2613,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>1069843</x:v>
+        <x:v>2062516</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>21</x:v>
@@ -2766,7 +2766,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>21</x:v>
@@ -2800,7 +2800,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>25663</x:v>
+        <x:v>436280</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>21</x:v>
@@ -2851,7 +2851,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>5650160</x:v>
+        <x:v>5667720</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>21</x:v>
@@ -2868,7 +2868,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>108744</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>21</x:v>
@@ -2902,7 +2902,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>70422</x:v>
+        <x:v>581175</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>21</x:v>
@@ -2919,7 +2919,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>85440</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>21</x:v>
@@ -3287,7 +3287,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>1069843</x:v>
+        <x:v>2062516</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>21</x:v>
@@ -3413,7 +3413,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>21</x:v>
@@ -3441,7 +3441,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>25663</x:v>
+        <x:v>436280</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>21</x:v>
@@ -3483,7 +3483,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>5650160</x:v>
+        <x:v>5667720</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
         <x:v>21</x:v>
@@ -3497,7 +3497,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>108744</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>21</x:v>
@@ -3525,7 +3525,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>70422</x:v>
+        <x:v>581175</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>21</x:v>
@@ -3539,7 +3539,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>85440</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
         <x:v>21</x:v>
@@ -3724,7 +3724,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>1069843</x:v>
+        <x:v>2062516</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>21</x:v>
@@ -3812,7 +3812,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>9699583</x:v>
+        <x:v>11719042</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>21</x:v>
@@ -3941,7 +3941,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>1069843</x:v>
+        <x:v>2062516</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -3997,7 +3997,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>9746745</x:v>
+        <x:v>11766204</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -4195,7 +4195,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>1069843</x:v>
+        <x:v>2062516</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -4294,7 +4294,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>2299423</x:v>
+        <x:v>3801322</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -4305,7 +4305,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -4316,7 +4316,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>5697322</x:v>
+        <x:v>5714882</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,66 +42,264 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENENDEZ, ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIMON, LATEEFAH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIEU, TED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIN, DAVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORREA, LOU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
     <x:t>FAIRSHAKE</x:t>
   </x:si>
   <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMITH, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELL, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
     <x:t>PETERS, ROBERT JAMES</x:t>
   </x:si>
   <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
     <x:t>PATRONIS, JIMMY JR.</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
     <x:t>FL</x:t>
   </x:si>
   <x:si>
@@ -111,54 +309,9 @@
     <x:t>06</x:t>
   </x:si>
   <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
     <x:t>BUDZINSKI, NIKKI</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
     <x:t>WALKINSHAW, JAMES</x:t>
   </x:si>
   <x:si>
@@ -186,21 +339,6 @@
     <x:t>FULLER, CLAY</x:t>
   </x:si>
   <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
     <x:t>TORRES, RITCHIE JOHN</x:t>
   </x:si>
   <x:si>
@@ -214,114 +352,6 @@
   </x:si>
   <x:si>
     <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENENDEZ, ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN, ALEXANDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMITH, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEALER, ALEXANDRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELL, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -392,8 +422,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G60" totalsRowShown="0">
-  <x:autoFilter ref="A1:G60"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G65" totalsRowShown="0">
+  <x:autoFilter ref="A1:G65"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -408,8 +438,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E46" totalsRowShown="0">
-  <x:autoFilter ref="A1:E46"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E51" totalsRowShown="0">
+  <x:autoFilter ref="A1:E51"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -422,8 +452,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D42" totalsRowShown="0">
-  <x:autoFilter ref="A1:D42"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D47" totalsRowShown="0">
+  <x:autoFilter ref="A1:D47"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -435,8 +465,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C22" totalsRowShown="0">
-  <x:autoFilter ref="A1:C22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C23" totalsRowShown="0">
+  <x:autoFilter ref="A1:C23"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -447,8 +477,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B18" totalsRowShown="0">
-  <x:autoFilter ref="A1:B18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B19" totalsRowShown="0">
+  <x:autoFilter ref="A1:B19"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -458,8 +488,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C27" totalsRowShown="0">
-  <x:autoFilter ref="A1:C27"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C28" totalsRowShown="0">
+  <x:autoFilter ref="A1:C28"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -757,7 +787,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G60"/>
+  <x:dimension ref="A1:G65"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -810,7 +840,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>817066</x:v>
+        <x:v>128790</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -824,16 +854,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>1803694</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -841,10 +871,10 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>15</x:v>
@@ -853,10 +883,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>5168736</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -864,240 +894,240 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>418058</x:v>
+        <x:v>55799</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>80948</x:v>
+        <x:v>54637</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>558813</x:v>
+        <x:v>53174</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>1673736</x:v>
+        <x:v>53970</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>771658</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F10" s="1">
+        <x:v>47162</x:v>
+      </x:c>
+      <x:c r="G10" s="1" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="F10" s="1">
-        <x:v>91656</x:v>
-      </x:c>
-      <x:c r="G10" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>141263</x:v>
+        <x:v>53694</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="F12" s="1">
-        <x:v>5017853</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C13" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>83860</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>515519</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>44</x:v>
@@ -1106,56 +1136,56 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F15" s="1">
+        <x:v>672092</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="F15" s="1">
-        <x:v>1564215</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="F16" s="1">
-        <x:v>1012792</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>20483</x:v>
+        <x:v>2062516</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1163,160 +1193,160 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
+      <x:c r="D18" s="1" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>91847</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>455146</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>300000</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>7170138</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B22" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>187450</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>430866</x:v>
+        <x:v>4150667</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>56045</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>12</x:v>
@@ -1324,114 +1354,114 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="F25" s="1">
-        <x:v>64395</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="F26" s="1">
-        <x:v>34890</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>418060</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>80948</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>47162</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1439,505 +1469,505 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>430866</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>708827</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>4210393</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>672092</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>41493</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>2062516</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>282975</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>348433</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>771658</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>436280</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>91656</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>4103505</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>426280</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F43" s="1">
+        <x:v>817066</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="F43" s="1">
-        <x:v>141263</x:v>
-      </x:c>
-      <x:c r="G43" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F44" s="1">
+        <x:v>1803694</x:v>
+      </x:c>
+      <x:c r="G44" s="1" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="F44" s="1">
-        <x:v>581175</x:v>
-      </x:c>
-      <x:c r="G44" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>513868</x:v>
+        <x:v>5168736</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B46" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C46" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D46" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="F46" s="1">
-        <x:v>56118</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>550000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>7415826</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>350000</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B50" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C50" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>350000</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>4697360</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -1945,22 +1975,22 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>119644</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>12</x:v>
@@ -1968,186 +1998,301 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>285008</x:v>
+        <x:v>5017853</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>30183</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>628597</x:v>
+        <x:v>515519</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>221403</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>250000</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="D58" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>350000</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>350000</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F60" s="1">
+        <x:v>455146</x:v>
+      </x:c>
+      <x:c r="G60" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:7">
+      <x:c r="A61" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B61" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C61" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D61" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E61" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F61" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="G61" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:7">
+      <x:c r="A62" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B62" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D62" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E62" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F62" s="1">
+        <x:v>7170138</x:v>
+      </x:c>
+      <x:c r="G62" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:7">
+      <x:c r="A63" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B63" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C63" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D63" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E63" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F63" s="1">
+        <x:v>187450</x:v>
+      </x:c>
+      <x:c r="G63" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:7">
+      <x:c r="A64" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B64" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C64" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D64" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E64" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F64" s="1">
+        <x:v>430866</x:v>
+      </x:c>
+      <x:c r="G64" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:7">
+      <x:c r="A65" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B65" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C65" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D65" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E65" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F65" s="1">
+        <x:v>56045</x:v>
+      </x:c>
+      <x:c r="G65" s="1" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="F60" s="1">
-        <x:v>2250000</x:v>
-      </x:c>
-      <x:c r="G60" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2166,7 +2311,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E46"/>
+  <x:dimension ref="A1:E51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2196,152 +2341,152 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>12783679</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>558813</x:v>
+        <x:v>55799</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>1673736</x:v>
+        <x:v>54637</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>350000</x:v>
+        <x:v>53174</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>430866</x:v>
+        <x:v>53694</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>430866</x:v>
+        <x:v>53970</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>708827</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>56045</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>12</x:v>
@@ -2349,101 +2494,101 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>4210393</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>755146</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>285008</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>30183</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>9985740</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>817066</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>12</x:v>
@@ -2451,16 +2596,16 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>2475786</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>12</x:v>
@@ -2468,373 +2613,373 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>557012</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>83860</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>513868</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>628597</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>221403</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>7170138</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>350000</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>250000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>2062516</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>91847</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>161896</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>282975</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>99285</x:v>
+        <x:v>2062516</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>187450</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>550000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>56118</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>2250000</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>1543316</x:v>
+        <x:v>163680</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>436280</x:v>
+        <x:v>187450</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>183312</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>47162</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>12</x:v>
@@ -2842,101 +2987,101 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>5667720</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>426280</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>282526</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>581175</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D44" s="1">
+        <x:v>47162</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="D44" s="1">
-        <x:v>348433</x:v>
-      </x:c>
-      <x:c r="E44" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>20483</x:v>
+        <x:v>5714882</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>12</x:v>
@@ -2944,19 +3089,104 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D46" s="1">
+        <x:v>426280</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:5">
+      <x:c r="A47" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D47" s="1">
+        <x:v>282526</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:5">
+      <x:c r="A48" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D48" s="1">
+        <x:v>616386</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:5">
+      <x:c r="A49" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D49" s="1">
+        <x:v>348433</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:5">
+      <x:c r="A50" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D50" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:5">
+      <x:c r="A51" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D51" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>21</x:v>
+      <x:c r="E51" s="1" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2975,7 +3205,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D42"/>
+  <x:dimension ref="A1:D47"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3001,111 +3231,111 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>12783679</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>558813</x:v>
+        <x:v>55799</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>1673736</x:v>
+        <x:v>54637</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>350000</x:v>
+        <x:v>53174</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>861732</x:v>
+        <x:v>53694</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>708827</x:v>
+        <x:v>53970</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>56045</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>12</x:v>
@@ -3113,55 +3343,55 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>4210393</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>755146</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>315191</x:v>
+        <x:v>861732</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>9985740</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>12</x:v>
@@ -3169,27 +3399,27 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>817066</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>2475786</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>12</x:v>
@@ -3197,44 +3427,44 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>557012</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>83860</x:v>
+        <x:v>315191</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>513868</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
@@ -3242,97 +3472,97 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>850000</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>7170138</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>600000</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>2062516</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>91847</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>161896</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>350000</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
@@ -3340,136 +3570,136 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>282975</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>99285</x:v>
+        <x:v>2062516</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>187450</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>550000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>56118</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>2250000</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>1543316</x:v>
+        <x:v>163680</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>436280</x:v>
+        <x:v>187450</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>183312</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>47162</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>12</x:v>
@@ -3477,83 +3707,83 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>5667720</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>426280</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>282526</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>581175</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C40" s="1">
+        <x:v>47162</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="C40" s="1">
-        <x:v>348433</x:v>
-      </x:c>
-      <x:c r="D40" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>20483</x:v>
+        <x:v>5714882</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
         <x:v>12</x:v>
@@ -3561,16 +3791,86 @@
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C42" s="1">
+        <x:v>426280</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:4">
+      <x:c r="A43" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C43" s="1">
+        <x:v>282526</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:4">
+      <x:c r="A44" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C44" s="1">
+        <x:v>616386</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:4">
+      <x:c r="A45" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C45" s="1">
+        <x:v>348433</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:4">
+      <x:c r="A46" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C46" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:4">
+      <x:c r="A47" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C47" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D42" s="1" t="s">
-        <x:v>21</x:v>
+      <x:c r="D47" s="1" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3589,7 +3889,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C22"/>
+  <x:dimension ref="A1:C23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3611,43 +3911,43 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>12783679</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>2232549</x:v>
+        <x:v>271274</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>56045</x:v>
+        <x:v>2232549</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>12</x:v>
@@ -3655,21 +3955,21 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>6886098</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>13278592</x:v>
+        <x:v>6886098</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>12</x:v>
@@ -3677,131 +3977,131 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>956063</x:v>
+        <x:v>13278592</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>513868</x:v>
+        <x:v>956063</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>8020138</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>600000</x:v>
+        <x:v>8020138</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>2062516</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>91847</x:v>
+        <x:v>2062516</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>632975</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>99285</x:v>
+        <x:v>632975</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>187450</x:v>
+        <x:v>163680</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>606118</x:v>
+        <x:v>187450</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>47162</x:v>
+        <x:v>606118</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>12</x:v>
@@ -3809,21 +4109,21 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B20" s="1">
+        <x:v>47162</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B20" s="1">
-        <x:v>11719042</x:v>
-      </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>20483</x:v>
+        <x:v>11827078</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>12</x:v>
@@ -3831,13 +4131,24 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B22" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B23" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>21</x:v>
+      <x:c r="C23" s="1" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3856,7 +4167,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B18"/>
+  <x:dimension ref="A1:B19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3874,7 +4185,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>12783679</x:v>
@@ -3882,7 +4193,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
@@ -3890,121 +4201,129 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>2232549</x:v>
+        <x:v>271274</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>6942143</x:v>
+        <x:v>2232549</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>14234655</x:v>
+        <x:v>6942143</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>513868</x:v>
+        <x:v>14234655</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>8020138</x:v>
+        <x:v>513868</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>600000</x:v>
+        <x:v>8020138</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>2062516</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>91847</x:v>
+        <x:v>2062516</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>632975</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>99285</x:v>
+        <x:v>632975</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>187450</x:v>
+        <x:v>163680</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>606118</x:v>
+        <x:v>187450</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>11766204</x:v>
+        <x:v>606118</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B18" s="1">
+        <x:v>11874240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:2">
+      <x:c r="A19" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B19" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>
@@ -4024,7 +4343,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C27"/>
+  <x:dimension ref="A1:C28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4046,10 +4365,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>12433679</x:v>
@@ -4057,10 +4376,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>350000</x:v>
@@ -4068,10 +4387,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>836118</x:v>
@@ -4079,46 +4398,46 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>2232549</x:v>
+        <x:v>271274</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>2025705</x:v>
+        <x:v>2232549</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>650000</x:v>
+        <x:v>2025705</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>4266438</x:v>
+        <x:v>650000</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -4126,207 +4445,218 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>13158948</x:v>
+        <x:v>4266438</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>1075707</x:v>
+        <x:v>13158948</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>513868</x:v>
+        <x:v>1075707</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>7170138</x:v>
+        <x:v>513868</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>850000</x:v>
+        <x:v>7170138</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>600000</x:v>
+        <x:v>850000</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>2062516</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>91847</x:v>
+        <x:v>2062516</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>282975</x:v>
+        <x:v>161896</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>350000</x:v>
+        <x:v>282975</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>99285</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>187450</x:v>
+        <x:v>163680</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>56118</x:v>
+        <x:v>187450</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>550000</x:v>
+        <x:v>56118</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>3801322</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>2250000</x:v>
+        <x:v>3862196</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>5714882</x:v>
+        <x:v>2250000</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C27" s="1">
+        <x:v>5762044</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C28" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,39 +42,186 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATRONIS, JIMMY JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00848440</x:t>
   </x:si>
   <x:si>
     <x:t>PROTECT PROGRESS</x:t>
   </x:si>
   <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALKINSHAW, JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKARSKY, STELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TORRES, RITCHIE JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
     <x:t>MENENDEZ, ROBERT</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
     <x:t>NJ</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
     <x:t>SIMON, LATEEFAH</x:t>
   </x:si>
   <x:si>
@@ -87,9 +234,6 @@
     <x:t>LOFGREN, ZOE</x:t>
   </x:si>
   <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
     <x:t>LIEU, TED</x:t>
   </x:si>
   <x:si>
@@ -102,24 +246,9 @@
     <x:t>47</x:t>
   </x:si>
   <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
     <x:t>GREEN, ALEXANDER</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>CORREA, LOU</x:t>
   </x:si>
   <x:si>
@@ -129,42 +258,12 @@
     <x:t>KINGSTON, JAMES MORRIS</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
     <x:t>GAINES, HOUSTON</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
     <x:t>CLARK, JASMINE</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
     <x:t>BOAFO, ADRIAN</x:t>
   </x:si>
   <x:si>
@@ -189,33 +288,18 @@
     <x:t>38</x:t>
   </x:si>
   <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
     <x:t>MEALER, ALEXANDRA</x:t>
   </x:si>
   <x:si>
     <x:t>09</x:t>
   </x:si>
   <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>SELL, TOM</x:t>
   </x:si>
   <x:si>
     <x:t>19</x:t>
   </x:si>
   <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
     <x:t>DE LA CRUZ, CARLOS JR.</x:t>
   </x:si>
   <x:si>
@@ -237,30 +321,12 @@
     <x:t>SC</x:t>
   </x:si>
   <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>GRAHAM, LINDSEY O.</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
     <x:t>COLLINS, MICHAEL A JR</x:t>
   </x:si>
   <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
     <x:t>KELLY, ROBIN</x:t>
   </x:si>
   <x:si>
@@ -270,12 +336,6 @@
     <x:t>KRISHNAMOORTHI, S</x:t>
   </x:si>
   <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
     <x:t>MORRIS, NATE</x:t>
   </x:si>
   <x:si>
@@ -292,66 +352,6 @@
   </x:si>
   <x:si>
     <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATRONIS, JIMMY JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALKINSHAW, JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKARSKY, STELLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00894428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROGERS, MICHAEL J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TORRES, RITCHIE JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -840,7 +840,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>128790</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -854,16 +854,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>34890</x:v>
+        <x:v>1803694</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -871,10 +871,10 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>15</x:v>
@@ -883,10 +883,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>418060</x:v>
+        <x:v>5168736</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -894,240 +894,240 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>55799</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>54637</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>53174</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>53970</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>80948</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>47162</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>53694</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>430866</x:v>
+        <x:v>5017853</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>708827</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>4210393</x:v>
+        <x:v>515519</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>44</x:v>
@@ -1136,56 +1136,56 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>672092</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>41493</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="F17" s="1">
-        <x:v>2062516</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1193,160 +1193,160 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>282975</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F19" s="1">
-        <x:v>348433</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>771658</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>461943</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>91656</x:v>
+        <x:v>231242</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>4150667</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>426280</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>12</x:v>
@@ -1354,321 +1354,321 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>141263</x:v>
+        <x:v>128790</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F26" s="1">
-        <x:v>616386</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>513868</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>56118</x:v>
+        <x:v>55799</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>550000</x:v>
+        <x:v>54637</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>7415826</x:v>
+        <x:v>53174</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C31" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>350000</x:v>
+        <x:v>53970</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>350000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>4697360</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>119644</x:v>
+        <x:v>53694</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>285008</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>30183</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>628597</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>221403</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>12</x:v>
@@ -1676,393 +1676,393 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>250000</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>350000</x:v>
+        <x:v>2062516</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>350000</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>2250000</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>817066</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>1803694</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>5168736</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>418058</x:v>
+        <x:v>4150667</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>80948</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>558813</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="D49" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>1673736</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>771658</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>91656</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>141263</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>5017853</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>83860</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>515519</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
@@ -2073,16 +2073,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>1564215</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2090,22 +2090,22 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>1012792</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2113,186 +2113,186 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>20483</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="D59" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>91847</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>455146</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>300000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>7170138</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E63" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="E63" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
       <x:c r="F63" s="1">
-        <x:v>187450</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
         <x:v>109</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>430866</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>110</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>56045</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2341,852 +2341,852 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>12783679</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>55799</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>54637</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>53174</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>53694</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>53970</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>430866</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>430866</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>708827</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>4210393</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>755146</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>285008</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>30183</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>513868</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>628597</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>221403</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>7170138</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>250000</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>2062516</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>282975</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>163680</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>187450</x:v>
+        <x:v>231242</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>550000</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>56118</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>2250000</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>461943</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>5714882</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>426280</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>616386</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>348433</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3231,646 +3231,646 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>12783679</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>55799</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>54637</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>53174</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>53694</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>53970</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>861732</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>708827</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>4210393</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>755146</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>315191</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>513868</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>7170138</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>2062516</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>282975</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>163680</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>187450</x:v>
+        <x:v>231242</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>550000</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>56118</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>2250000</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>461943</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>5714882</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>426280</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>616386</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>348433</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3911,244 +3911,244 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>12783679</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>271274</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>2232549</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>6886098</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>13278592</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>956063</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>513868</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>8020138</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>2062516</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>632975</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>163680</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>187450</x:v>
+        <x:v>231242</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>606118</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>11827078</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4185,7 +4185,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>12783679</x:v>
@@ -4193,7 +4193,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
@@ -4201,7 +4201,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>271274</x:v>
@@ -4209,7 +4209,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>2232549</x:v>
@@ -4217,7 +4217,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>6942143</x:v>
@@ -4225,7 +4225,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>14234655</x:v>
@@ -4233,7 +4233,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>513868</x:v>
@@ -4241,7 +4241,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>8020138</x:v>
@@ -4249,7 +4249,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>600000</x:v>
@@ -4257,7 +4257,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>2062516</x:v>
@@ -4265,7 +4265,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>91847</x:v>
@@ -4273,7 +4273,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>161896</x:v>
@@ -4281,7 +4281,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>632975</x:v>
@@ -4289,7 +4289,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>163680</x:v>
@@ -4297,15 +4297,15 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>187450</x:v>
+        <x:v>231242</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>606118</x:v>
@@ -4313,7 +4313,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>11874240</x:v>
@@ -4321,7 +4321,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>1033275</x:v>
@@ -4365,10 +4365,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>12433679</x:v>
@@ -4376,10 +4376,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>350000</x:v>
@@ -4387,10 +4387,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>836118</x:v>
@@ -4398,10 +4398,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>271274</x:v>
@@ -4409,10 +4409,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>2232549</x:v>
@@ -4420,10 +4420,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2025705</x:v>
@@ -4431,10 +4431,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>650000</x:v>
@@ -4442,10 +4442,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>4266438</x:v>
@@ -4453,10 +4453,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>13158948</x:v>
@@ -4464,10 +4464,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1075707</x:v>
@@ -4475,10 +4475,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>513868</x:v>
@@ -4486,10 +4486,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>7170138</x:v>
@@ -4497,10 +4497,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>850000</x:v>
@@ -4508,10 +4508,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>600000</x:v>
@@ -4519,10 +4519,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>2062516</x:v>
@@ -4530,10 +4530,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>91847</x:v>
@@ -4541,10 +4541,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>161896</x:v>
@@ -4552,10 +4552,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>282975</x:v>
@@ -4563,10 +4563,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>350000</x:v>
@@ -4574,10 +4574,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>163680</x:v>
@@ -4585,21 +4585,21 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>187450</x:v>
+        <x:v>231242</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>56118</x:v>
@@ -4607,10 +4607,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>550000</x:v>
@@ -4618,10 +4618,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>3862196</x:v>
@@ -4629,10 +4629,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>2250000</x:v>
@@ -4640,10 +4640,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>5762044</x:v>
@@ -4651,10 +4651,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>1033275</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -247,6 +247,9 @@
   </x:si>
   <x:si>
     <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCGUIRE, MIKE</x:t>
   </x:si>
   <x:si>
     <x:t>CORREA, LOU</x:t>
@@ -422,8 +425,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G65" totalsRowShown="0">
-  <x:autoFilter ref="A1:G65"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G66" totalsRowShown="0">
+  <x:autoFilter ref="A1:G66"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -438,8 +441,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E51" totalsRowShown="0">
-  <x:autoFilter ref="A1:E51"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E52" totalsRowShown="0">
+  <x:autoFilter ref="A1:E52"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -452,8 +455,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D47" totalsRowShown="0">
-  <x:autoFilter ref="A1:D47"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D48" totalsRowShown="0">
+  <x:autoFilter ref="A1:D48"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -787,7 +790,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G65"/>
+  <x:dimension ref="A1:G66"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1570,13 +1573,13 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>53694</x:v>
+        <x:v>55720</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>21</x:v>
@@ -1584,22 +1587,22 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>430866</x:v>
+        <x:v>53694</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>21</x:v>
@@ -1616,13 +1619,13 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>708827</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>21</x:v>
@@ -1630,22 +1633,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>4210393</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>21</x:v>
@@ -1653,48 +1656,48 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>672092</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>41493</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
@@ -1705,16 +1708,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>2062516</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>21</x:v>
@@ -1722,22 +1725,22 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="D41" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
       <x:c r="F41" s="1">
-        <x:v>282975</x:v>
+        <x:v>2122190</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>21</x:v>
@@ -1751,16 +1754,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="D42" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="F42" s="1">
-        <x:v>348433</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>21</x:v>
@@ -1774,16 +1777,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>771658</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>21</x:v>
@@ -1797,16 +1800,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>461943</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>21</x:v>
@@ -1820,16 +1823,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>91656</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>21</x:v>
@@ -1837,22 +1840,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>4150667</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>21</x:v>
@@ -1860,22 +1863,22 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>426280</x:v>
+        <x:v>4150667</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>21</x:v>
@@ -1889,16 +1892,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>141263</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>21</x:v>
@@ -1912,16 +1915,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>616386</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>21</x:v>
@@ -1935,16 +1938,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="D50" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>513868</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>21</x:v>
@@ -1958,16 +1961,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E51" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="D51" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="E51" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="F51" s="1">
-        <x:v>56118</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>21</x:v>
@@ -1975,22 +1978,22 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D52" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E52" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="F52" s="1">
-        <x:v>550000</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>21</x:v>
@@ -1998,22 +2001,22 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>7415826</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>21</x:v>
@@ -2021,10 +2024,10 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>37</x:v>
@@ -2036,7 +2039,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>350000</x:v>
+        <x:v>7415826</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>21</x:v>
@@ -2050,13 +2053,13 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F55" s="1">
         <x:v>350000</x:v>
@@ -2067,33 +2070,33 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>4697360</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
         <x:v>15</x:v>
@@ -2105,7 +2108,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>119644</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2119,19 +2122,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>285008</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
@@ -2142,16 +2145,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="D59" s="1" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>21</x:v>
@@ -2159,22 +2162,22 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>628597</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>21</x:v>
@@ -2188,7 +2191,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
         <x:v>16</x:v>
@@ -2197,7 +2200,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>221403</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>21</x:v>
@@ -2217,10 +2220,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>250000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>21</x:v>
@@ -2234,16 +2237,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>21</x:v>
@@ -2263,7 +2266,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F64" s="1">
         <x:v>350000</x:v>
@@ -2286,12 +2289,35 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F65" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G65" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:7">
+      <x:c r="A66" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B66" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C66" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D66" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E66" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F65" s="1">
+      <x:c r="F66" s="1">
         <x:v>2250000</x:v>
       </x:c>
-      <x:c r="G65" s="1" t="s">
+      <x:c r="G66" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2311,7 +2337,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E51"/>
+  <x:dimension ref="A1:E52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2375,16 +2401,16 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>55799</x:v>
+        <x:v>55720</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>21</x:v>
@@ -2392,16 +2418,16 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>54637</x:v>
+        <x:v>55799</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>21</x:v>
@@ -2409,16 +2435,16 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>53174</x:v>
+        <x:v>54637</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>21</x:v>
@@ -2426,16 +2452,16 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>53694</x:v>
+        <x:v>53174</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>21</x:v>
@@ -2443,16 +2469,16 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>53970</x:v>
+        <x:v>53694</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>21</x:v>
@@ -2460,16 +2486,16 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>558813</x:v>
+        <x:v>53970</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>21</x:v>
@@ -2477,16 +2503,16 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>1673736</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>21</x:v>
@@ -2494,16 +2520,16 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>350000</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>21</x:v>
@@ -2511,16 +2537,16 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>430866</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>21</x:v>
@@ -2528,7 +2554,7 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>26</x:v>
@@ -2548,13 +2574,13 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>708827</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>21</x:v>
@@ -2562,24 +2588,24 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>56045</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>42</x:v>
@@ -2588,24 +2614,24 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>4210393</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>755146</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>21</x:v>
@@ -2613,16 +2639,16 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>285008</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>21</x:v>
@@ -2630,16 +2656,16 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="B19" s="1" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>21</x:v>
@@ -2647,33 +2673,33 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>9985740</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>817066</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>12</x:v>
@@ -2681,16 +2707,16 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>2475786</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>12</x:v>
@@ -2698,33 +2724,33 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>557012</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>83860</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>21</x:v>
@@ -2732,16 +2758,16 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>513868</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>21</x:v>
@@ -2749,16 +2775,16 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>628597</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>21</x:v>
@@ -2766,7 +2792,7 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>16</x:v>
@@ -2775,7 +2801,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>221403</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>21</x:v>
@@ -2783,16 +2809,16 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>7170138</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>21</x:v>
@@ -2800,16 +2826,16 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>350000</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>21</x:v>
@@ -2817,16 +2843,16 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>21</x:v>
@@ -2834,16 +2860,16 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>2062516</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>21</x:v>
@@ -2851,16 +2877,16 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>91847</x:v>
+        <x:v>2122190</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>21</x:v>
@@ -2868,16 +2894,16 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>21</x:v>
@@ -2885,16 +2911,16 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>21</x:v>
@@ -2902,16 +2928,16 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>21</x:v>
@@ -2919,16 +2945,16 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>163680</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>21</x:v>
@@ -2936,16 +2962,16 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>231242</x:v>
+        <x:v>163680</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>21</x:v>
@@ -2953,16 +2979,16 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>550000</x:v>
+        <x:v>231242</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>21</x:v>
@@ -2970,16 +2996,16 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>56118</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>21</x:v>
@@ -2987,16 +3013,16 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>2250000</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>21</x:v>
@@ -3004,16 +3030,16 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>21</x:v>
@@ -3021,16 +3047,16 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>461943</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>21</x:v>
@@ -3038,16 +3064,16 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>183312</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>21</x:v>
@@ -3055,24 +3081,24 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>47162</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>45</x:v>
@@ -3081,24 +3107,24 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>5714882</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>426280</x:v>
+        <x:v>5714882</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>21</x:v>
@@ -3106,16 +3132,16 @@
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D47" s="1">
-        <x:v>282526</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>21</x:v>
@@ -3123,16 +3149,16 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D48" s="1">
-        <x:v>616386</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>21</x:v>
@@ -3140,16 +3166,16 @@
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D49" s="1">
-        <x:v>348433</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>21</x:v>
@@ -3157,24 +3183,24 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D50" s="1">
-        <x:v>20483</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
         <x:v>47</x:v>
@@ -3183,9 +3209,26 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D51" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E51" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:5">
+      <x:c r="A52" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D52" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E51" s="1" t="s">
+      <x:c r="E52" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -3205,7 +3248,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D47"/>
+  <x:dimension ref="A1:D48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3259,13 +3302,13 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>55799</x:v>
+        <x:v>55720</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
         <x:v>21</x:v>
@@ -3273,13 +3316,13 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>54637</x:v>
+        <x:v>55799</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>21</x:v>
@@ -3287,13 +3330,13 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>53174</x:v>
+        <x:v>54637</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>21</x:v>
@@ -3301,13 +3344,13 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>53694</x:v>
+        <x:v>53174</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>21</x:v>
@@ -3315,13 +3358,13 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>53970</x:v>
+        <x:v>53694</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>21</x:v>
@@ -3329,13 +3372,13 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>558813</x:v>
+        <x:v>53970</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>21</x:v>
@@ -3343,13 +3386,13 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>1673736</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>21</x:v>
@@ -3357,13 +3400,13 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>350000</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
         <x:v>21</x:v>
@@ -3371,13 +3414,13 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>861732</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
         <x:v>21</x:v>
@@ -3385,13 +3428,13 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>708827</x:v>
+        <x:v>861732</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>21</x:v>
@@ -3399,16 +3442,16 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>56045</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
@@ -3419,21 +3462,21 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>4210393</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>755146</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>21</x:v>
@@ -3441,13 +3484,13 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>315191</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>21</x:v>
@@ -3455,27 +3498,27 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>9985740</x:v>
+        <x:v>315191</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>817066</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>12</x:v>
@@ -3483,13 +3526,13 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>2475786</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>12</x:v>
@@ -3497,27 +3540,27 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>557012</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>83860</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>21</x:v>
@@ -3525,13 +3568,13 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>513868</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>21</x:v>
@@ -3539,13 +3582,13 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>850000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>21</x:v>
@@ -3553,13 +3596,13 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>7170138</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>21</x:v>
@@ -3567,13 +3610,13 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>600000</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>21</x:v>
@@ -3581,13 +3624,13 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>2062516</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>21</x:v>
@@ -3595,13 +3638,13 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>91847</x:v>
+        <x:v>2122190</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>21</x:v>
@@ -3609,13 +3652,13 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>21</x:v>
@@ -3623,13 +3666,13 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
         <x:v>21</x:v>
@@ -3637,13 +3680,13 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>21</x:v>
@@ -3651,13 +3694,13 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>163680</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>21</x:v>
@@ -3665,13 +3708,13 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>231242</x:v>
+        <x:v>163680</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>21</x:v>
@@ -3679,13 +3722,13 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>550000</x:v>
+        <x:v>231242</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
         <x:v>21</x:v>
@@ -3693,13 +3736,13 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>56118</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>21</x:v>
@@ -3707,13 +3750,13 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>2250000</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
         <x:v>21</x:v>
@@ -3721,13 +3764,13 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>21</x:v>
@@ -3735,13 +3778,13 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>461943</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
         <x:v>21</x:v>
@@ -3749,13 +3792,13 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>183312</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>21</x:v>
@@ -3763,16 +3806,16 @@
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>47162</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
@@ -3783,21 +3826,21 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>5714882</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>426280</x:v>
+        <x:v>5714882</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>21</x:v>
@@ -3805,13 +3848,13 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>282526</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
         <x:v>21</x:v>
@@ -3819,13 +3862,13 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>616386</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
         <x:v>21</x:v>
@@ -3833,13 +3876,13 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C45" s="1">
-        <x:v>348433</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
         <x:v>21</x:v>
@@ -3847,16 +3890,16 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C46" s="1">
-        <x:v>20483</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
@@ -3867,9 +3910,23 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C47" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:4">
+      <x:c r="A48" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C48" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D47" s="1" t="s">
+      <x:c r="D48" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -3936,7 +3993,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>271274</x:v>
+        <x:v>326994</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>21</x:v>
@@ -3999,7 +4056,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>513868</x:v>
@@ -4021,7 +4078,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>600000</x:v>
@@ -4032,10 +4089,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>2062516</x:v>
+        <x:v>2122190</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>21</x:v>
@@ -4065,7 +4122,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>632975</x:v>
@@ -4098,7 +4155,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>606118</x:v>
@@ -4204,7 +4261,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>271274</x:v>
+        <x:v>326994</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -4233,7 +4290,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>513868</x:v>
@@ -4249,7 +4306,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>600000</x:v>
@@ -4257,10 +4314,10 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>2062516</x:v>
+        <x:v>2122190</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
@@ -4281,7 +4338,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>632975</x:v>
@@ -4305,7 +4362,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>606118</x:v>
@@ -4404,7 +4461,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>271274</x:v>
+        <x:v>326994</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -4478,7 +4535,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>513868</x:v>
@@ -4511,7 +4568,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>600000</x:v>
@@ -4522,10 +4579,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>2062516</x:v>
+        <x:v>2122190</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -4555,7 +4612,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>282975</x:v>
@@ -4566,7 +4623,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>350000</x:v>
@@ -4599,7 +4656,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>56118</x:v>
@@ -4610,7 +4667,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>550000</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -1878,7 +1878,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>4150667</x:v>
+        <x:v>4903859</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>21</x:v>
@@ -2039,7 +2039,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>7415826</x:v>
+        <x:v>8423195</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>21</x:v>
@@ -2376,7 +2376,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>12783679</x:v>
+        <x:v>13791048</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
         <x:v>21</x:v>
@@ -3124,7 +3124,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>5714882</x:v>
+        <x:v>6468074</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>21</x:v>
@@ -3280,7 +3280,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>12783679</x:v>
+        <x:v>13791048</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>21</x:v>
@@ -3840,7 +3840,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>5714882</x:v>
+        <x:v>6468074</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>21</x:v>
@@ -3971,7 +3971,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>12783679</x:v>
+        <x:v>13791048</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>21</x:v>
@@ -4180,7 +4180,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>11827078</x:v>
+        <x:v>12580270</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>21</x:v>
@@ -4245,7 +4245,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>12783679</x:v>
+        <x:v>13791048</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -4373,7 +4373,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>11874240</x:v>
+        <x:v>12627432</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
@@ -4428,7 +4428,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>12433679</x:v>
+        <x:v>13441048</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -4703,7 +4703,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>5762044</x:v>
+        <x:v>6515236</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -252,6 +252,18 @@
     <x:t>MCGUIRE, MIKE</x:t>
   </x:si>
   <x:si>
+    <x:t>IRWIN, JACQUI V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIS, HILDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
     <x:t>CORREA, LOU</x:t>
   </x:si>
   <x:si>
@@ -286,9 +298,6 @@
   </x:si>
   <x:si>
     <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
   </x:si>
   <x:si>
     <x:t>MEALER, ALEXANDRA</x:t>
@@ -425,8 +434,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G66" totalsRowShown="0">
-  <x:autoFilter ref="A1:G66"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G68" totalsRowShown="0">
+  <x:autoFilter ref="A1:G68"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -441,8 +450,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E52" totalsRowShown="0">
-  <x:autoFilter ref="A1:E52"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E54" totalsRowShown="0">
+  <x:autoFilter ref="A1:E54"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -455,8 +464,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D48" totalsRowShown="0">
-  <x:autoFilter ref="A1:D48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D50" totalsRowShown="0">
+  <x:autoFilter ref="A1:D50"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -790,7 +799,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G66"/>
+  <x:dimension ref="A1:G68"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1303,7 +1312,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>231242</x:v>
+        <x:v>275034</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>21</x:v>
@@ -1372,7 +1381,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>128790</x:v>
+        <x:v>163680</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>21</x:v>
@@ -1441,7 +1450,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>55799</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>21</x:v>
@@ -1464,7 +1473,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>54637</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>21</x:v>
@@ -1487,7 +1496,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>53174</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>21</x:v>
@@ -1510,7 +1519,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>53970</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>21</x:v>
@@ -1579,7 +1588,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>55720</x:v>
+        <x:v>111440</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>21</x:v>
@@ -1602,7 +1611,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>53694</x:v>
+        <x:v>54932</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>21</x:v>
@@ -1610,22 +1619,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>430866</x:v>
+        <x:v>54685</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>21</x:v>
@@ -1633,22 +1642,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>708827</x:v>
+        <x:v>107388</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>21</x:v>
@@ -1656,22 +1665,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>4210393</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>21</x:v>
@@ -1679,25 +1688,25 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>672092</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
@@ -1708,16 +1717,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>41493</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>21</x:v>
@@ -1725,45 +1734,45 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>2122190</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>282975</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>21</x:v>
@@ -1771,22 +1780,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D43" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="F43" s="1">
-        <x:v>348433</x:v>
+        <x:v>3114863</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>21</x:v>
@@ -1800,16 +1809,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>771658</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>21</x:v>
@@ -1823,16 +1832,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>461943</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>21</x:v>
@@ -1846,16 +1855,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>91656</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>21</x:v>
@@ -1863,22 +1872,22 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>4903859</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>21</x:v>
@@ -1892,16 +1901,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>426280</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>21</x:v>
@@ -1909,22 +1918,22 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>141263</x:v>
+        <x:v>4903859</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>21</x:v>
@@ -1938,16 +1947,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>616386</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>21</x:v>
@@ -1961,16 +1970,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>513868</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>21</x:v>
@@ -1984,16 +1993,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>56118</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>21</x:v>
@@ -2001,22 +2010,22 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D53" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E53" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="F53" s="1">
-        <x:v>550000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>21</x:v>
@@ -2030,16 +2039,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>8423195</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>21</x:v>
@@ -2053,16 +2062,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>350000</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>21</x:v>
@@ -2070,22 +2079,22 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>350000</x:v>
+        <x:v>8423195</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>21</x:v>
@@ -2093,71 +2102,71 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>4697360</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>119644</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>285008</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
@@ -2168,39 +2177,39 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>30183</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>628597</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>21</x:v>
@@ -2208,22 +2217,22 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>221403</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>21</x:v>
@@ -2237,16 +2246,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>250000</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>21</x:v>
@@ -2266,10 +2275,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>350000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>21</x:v>
@@ -2289,10 +2298,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>21</x:v>
@@ -2306,18 +2315,64 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F66" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G66" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:7">
+      <x:c r="A67" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B67" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C67" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D67" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E67" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F67" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G67" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:7">
+      <x:c r="A68" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B68" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C68" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D68" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E68" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F66" s="1">
+      <x:c r="F68" s="1">
         <x:v>2250000</x:v>
       </x:c>
-      <x:c r="G66" s="1" t="s">
+      <x:c r="G68" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2337,7 +2392,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E52"/>
+  <x:dimension ref="A1:E54"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2410,7 +2465,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>55720</x:v>
+        <x:v>111440</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>21</x:v>
@@ -2427,7 +2482,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>55799</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>21</x:v>
@@ -2444,7 +2499,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>54637</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>21</x:v>
@@ -2452,16 +2507,16 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>53174</x:v>
+        <x:v>54932</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>21</x:v>
@@ -2469,16 +2524,16 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>53694</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>21</x:v>
@@ -2486,16 +2541,16 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>53970</x:v>
+        <x:v>54685</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>21</x:v>
@@ -2503,16 +2558,16 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>558813</x:v>
+        <x:v>107388</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>21</x:v>
@@ -2520,16 +2575,16 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>1673736</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>21</x:v>
@@ -2537,16 +2592,16 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>350000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>21</x:v>
@@ -2554,16 +2609,16 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>430866</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>21</x:v>
@@ -2571,16 +2626,16 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>430866</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>21</x:v>
@@ -2588,16 +2643,16 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>708827</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>21</x:v>
@@ -2605,33 +2660,33 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>56045</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>4210393</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>21</x:v>
@@ -2639,33 +2694,33 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>755146</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>285008</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>21</x:v>
@@ -2673,16 +2728,16 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>30183</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>21</x:v>
@@ -2690,50 +2745,50 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>9985740</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>817066</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>2475786</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>12</x:v>
@@ -2741,50 +2796,50 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>557012</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>83860</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>513868</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>21</x:v>
@@ -2792,16 +2847,16 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>628597</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>21</x:v>
@@ -2809,16 +2864,16 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>221403</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>21</x:v>
@@ -2829,13 +2884,13 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>7170138</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>21</x:v>
@@ -2849,10 +2904,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>350000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>21</x:v>
@@ -2860,16 +2915,16 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>250000</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>21</x:v>
@@ -2877,16 +2932,16 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>2122190</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>21</x:v>
@@ -2894,16 +2949,16 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>91847</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>21</x:v>
@@ -2911,16 +2966,16 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>161896</x:v>
+        <x:v>3114863</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>21</x:v>
@@ -2928,16 +2983,16 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>350000</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>21</x:v>
@@ -2945,16 +3000,16 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>282975</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>21</x:v>
@@ -2962,16 +3017,16 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>163680</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>21</x:v>
@@ -2979,16 +3034,16 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>231242</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>21</x:v>
@@ -2996,16 +3051,16 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>550000</x:v>
+        <x:v>198570</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>21</x:v>
@@ -3013,16 +3068,16 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>56118</x:v>
+        <x:v>275034</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>21</x:v>
@@ -3030,16 +3085,16 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>2250000</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>21</x:v>
@@ -3047,16 +3102,16 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>1543316</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>21</x:v>
@@ -3064,16 +3119,16 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>461943</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>21</x:v>
@@ -3081,16 +3136,16 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>21</x:v>
@@ -3098,33 +3153,33 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>47162</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>6468074</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>21</x:v>
@@ -3132,33 +3187,33 @@
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D47" s="1">
-        <x:v>426280</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D48" s="1">
-        <x:v>282526</x:v>
+        <x:v>6468074</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>21</x:v>
@@ -3166,16 +3221,16 @@
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D49" s="1">
-        <x:v>616386</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>21</x:v>
@@ -3183,16 +3238,16 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D50" s="1">
-        <x:v>348433</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>21</x:v>
@@ -3200,35 +3255,69 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D51" s="1">
-        <x:v>20483</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D52" s="1">
+        <x:v>348433</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:5">
+      <x:c r="A53" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D53" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:5">
+      <x:c r="A54" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B52" s="1" t="s">
+      <x:c r="B54" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C52" s="1" t="s">
+      <x:c r="C54" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D52" s="1">
+      <x:c r="D54" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E52" s="1" t="s">
+      <x:c r="E54" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -3248,7 +3337,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D48"/>
+  <x:dimension ref="A1:D50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3308,7 +3397,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>55720</x:v>
+        <x:v>111440</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
         <x:v>21</x:v>
@@ -3322,7 +3411,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>55799</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>21</x:v>
@@ -3336,7 +3425,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>54637</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>21</x:v>
@@ -3344,13 +3433,13 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>53174</x:v>
+        <x:v>54932</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>21</x:v>
@@ -3358,13 +3447,13 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>53694</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>21</x:v>
@@ -3372,13 +3461,13 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>53970</x:v>
+        <x:v>54685</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>21</x:v>
@@ -3386,13 +3475,13 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>558813</x:v>
+        <x:v>107388</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>21</x:v>
@@ -3400,13 +3489,13 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>1673736</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
         <x:v>21</x:v>
@@ -3414,13 +3503,13 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>350000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
         <x:v>21</x:v>
@@ -3428,13 +3517,13 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>861732</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>21</x:v>
@@ -3442,13 +3531,13 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>708827</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>21</x:v>
@@ -3456,27 +3545,27 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>56045</x:v>
+        <x:v>861732</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>4210393</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>21</x:v>
@@ -3484,27 +3573,27 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>755146</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>315191</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
         <x:v>21</x:v>
@@ -3512,41 +3601,41 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>9985740</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>817066</x:v>
+        <x:v>315191</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>2475786</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>12</x:v>
@@ -3554,41 +3643,41 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>557012</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>83860</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>513868</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>21</x:v>
@@ -3596,13 +3685,13 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>850000</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>21</x:v>
@@ -3610,13 +3699,13 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>7170138</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>21</x:v>
@@ -3627,10 +3716,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>600000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>21</x:v>
@@ -3638,13 +3727,13 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>2122190</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>21</x:v>
@@ -3655,10 +3744,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>91847</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>21</x:v>
@@ -3666,13 +3755,13 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>161896</x:v>
+        <x:v>3114863</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
         <x:v>21</x:v>
@@ -3683,10 +3772,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>350000</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>21</x:v>
@@ -3694,13 +3783,13 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>282975</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>21</x:v>
@@ -3708,13 +3797,13 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>163680</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>21</x:v>
@@ -3722,13 +3811,13 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>231242</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
         <x:v>21</x:v>
@@ -3736,13 +3825,13 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>550000</x:v>
+        <x:v>198570</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>21</x:v>
@@ -3750,13 +3839,13 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>56118</x:v>
+        <x:v>275034</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
         <x:v>21</x:v>
@@ -3767,10 +3856,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>2250000</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>21</x:v>
@@ -3778,13 +3867,13 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>1543316</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
         <x:v>21</x:v>
@@ -3792,13 +3881,13 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>461943</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>21</x:v>
@@ -3806,13 +3895,13 @@
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>183312</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
         <x:v>21</x:v>
@@ -3820,27 +3909,27 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>47162</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>6468074</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>21</x:v>
@@ -3848,27 +3937,27 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>426280</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>282526</x:v>
+        <x:v>6468074</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
         <x:v>21</x:v>
@@ -3876,13 +3965,13 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C45" s="1">
-        <x:v>616386</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
         <x:v>21</x:v>
@@ -3890,13 +3979,13 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C46" s="1">
-        <x:v>348433</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
         <x:v>21</x:v>
@@ -3904,29 +3993,57 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C47" s="1">
-        <x:v>20483</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C48" s="1">
+        <x:v>348433</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:4">
+      <x:c r="A49" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B48" s="1" t="s">
+      <x:c r="B49" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C48" s="1">
+      <x:c r="C49" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:4">
+      <x:c r="A50" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C50" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D48" s="1" t="s">
+      <x:c r="D50" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -3993,7 +4110,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>326994</x:v>
+        <x:v>763605</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>21</x:v>
@@ -4056,7 +4173,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>513868</x:v>
@@ -4078,7 +4195,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>600000</x:v>
@@ -4089,10 +4206,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>2122190</x:v>
+        <x:v>3114863</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>21</x:v>
@@ -4122,7 +4239,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>632975</x:v>
@@ -4136,7 +4253,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>163680</x:v>
+        <x:v>198570</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>21</x:v>
@@ -4147,7 +4264,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>231242</x:v>
+        <x:v>275034</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>21</x:v>
@@ -4155,7 +4272,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>606118</x:v>
@@ -4261,7 +4378,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>326994</x:v>
+        <x:v>763605</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -4290,7 +4407,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>513868</x:v>
@@ -4306,7 +4423,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>600000</x:v>
@@ -4314,10 +4431,10 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>2122190</x:v>
+        <x:v>3114863</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
@@ -4338,7 +4455,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>632975</x:v>
@@ -4349,7 +4466,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>163680</x:v>
+        <x:v>198570</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
@@ -4357,12 +4474,12 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>231242</x:v>
+        <x:v>275034</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>606118</x:v>
@@ -4461,7 +4578,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>326994</x:v>
+        <x:v>763605</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -4535,7 +4652,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>513868</x:v>
@@ -4568,7 +4685,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>600000</x:v>
@@ -4579,10 +4696,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>2122190</x:v>
+        <x:v>3114863</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -4612,7 +4729,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>282975</x:v>
@@ -4623,7 +4740,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>350000</x:v>
@@ -4637,7 +4754,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>163680</x:v>
+        <x:v>198570</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -4648,7 +4765,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>231242</x:v>
+        <x:v>275034</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -4656,7 +4773,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>56118</x:v>
@@ -4667,7 +4784,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>550000</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -232,6 +232,12 @@
   </x:si>
   <x:si>
     <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WHITESIDES, GEORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
   </x:si>
   <x:si>
     <x:t>LIEU, TED</x:t>
@@ -434,8 +440,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G68" totalsRowShown="0">
-  <x:autoFilter ref="A1:G68"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G69" totalsRowShown="0">
+  <x:autoFilter ref="A1:G69"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -450,8 +456,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E54" totalsRowShown="0">
-  <x:autoFilter ref="A1:E54"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E55" totalsRowShown="0">
+  <x:autoFilter ref="A1:E55"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -464,8 +470,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D50" totalsRowShown="0">
-  <x:autoFilter ref="A1:D50"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D51" totalsRowShown="0">
+  <x:autoFilter ref="A1:D51"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -799,7 +805,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G68"/>
+  <x:dimension ref="A1:G69"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1381,7 +1387,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>163680</x:v>
+        <x:v>228075</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>21</x:v>
@@ -1496,7 +1502,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>106348</x:v>
+        <x:v>476254</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>21</x:v>
@@ -1519,7 +1525,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>107940</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>21</x:v>
@@ -1527,22 +1533,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>80948</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>21</x:v>
@@ -1550,25 +1556,25 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>47162</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
@@ -1579,19 +1585,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>111440</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
@@ -1602,16 +1608,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>54932</x:v>
+        <x:v>372060</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>21</x:v>
@@ -1634,7 +1640,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>54685</x:v>
+        <x:v>366028</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>21</x:v>
@@ -1657,7 +1663,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>107388</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>21</x:v>
@@ -1665,22 +1671,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>430866</x:v>
+        <x:v>107388</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>21</x:v>
@@ -1694,16 +1700,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>708827</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>21</x:v>
@@ -1711,22 +1717,22 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>4210393</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>21</x:v>
@@ -1734,48 +1740,48 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>672092</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>41493</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
@@ -1786,16 +1792,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>3114863</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>21</x:v>
@@ -1803,22 +1809,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="D44" s="1" t="s">
+      <x:c r="E44" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="E44" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="F44" s="1">
-        <x:v>282975</x:v>
+        <x:v>3114863</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>21</x:v>
@@ -1832,16 +1838,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D45" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>348433</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>21</x:v>
@@ -1855,16 +1861,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>771658</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>21</x:v>
@@ -1878,16 +1884,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>461943</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>21</x:v>
@@ -1901,16 +1907,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>91656</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>21</x:v>
@@ -1918,22 +1924,22 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>4903859</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>21</x:v>
@@ -1941,22 +1947,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>426280</x:v>
+        <x:v>4903859</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>21</x:v>
@@ -1970,16 +1976,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>141263</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>21</x:v>
@@ -1993,16 +1999,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>616386</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>21</x:v>
@@ -2022,10 +2028,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>513868</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>21</x:v>
@@ -2039,16 +2045,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="D54" s="1" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>56118</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>21</x:v>
@@ -2056,22 +2062,22 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>550000</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>21</x:v>
@@ -2079,22 +2085,22 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>8423195</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>21</x:v>
@@ -2102,10 +2108,10 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
         <x:v>37</x:v>
@@ -2117,7 +2123,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>350000</x:v>
+        <x:v>8423195</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>21</x:v>
@@ -2131,13 +2137,13 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="1">
         <x:v>350000</x:v>
@@ -2148,33 +2154,33 @@
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>4697360</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>15</x:v>
@@ -2186,7 +2192,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>119644</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2200,19 +2206,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>285008</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
@@ -2226,13 +2232,13 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>21</x:v>
@@ -2240,22 +2246,22 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>628597</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>21</x:v>
@@ -2269,7 +2275,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
         <x:v>16</x:v>
@@ -2278,7 +2284,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>221403</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>21</x:v>
@@ -2292,16 +2298,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>250000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>21</x:v>
@@ -2321,10 +2327,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>21</x:v>
@@ -2338,13 +2344,13 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F67" s="1">
         <x:v>350000</x:v>
@@ -2361,18 +2367,41 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F68" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G68" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:7">
+      <x:c r="A69" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B69" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C69" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D69" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E69" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F68" s="1">
+      <x:c r="F69" s="1">
         <x:v>2250000</x:v>
       </x:c>
-      <x:c r="G68" s="1" t="s">
+      <x:c r="G69" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2392,7 +2421,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E54"/>
+  <x:dimension ref="A1:E55"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2456,7 +2485,7 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>26</x:v>
@@ -2465,7 +2494,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>111440</x:v>
+        <x:v>372060</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>21</x:v>
@@ -2507,16 +2536,16 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>54932</x:v>
+        <x:v>366028</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>21</x:v>
@@ -2533,7 +2562,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>106348</x:v>
+        <x:v>476254</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>21</x:v>
@@ -2541,16 +2570,16 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>54685</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>21</x:v>
@@ -2567,7 +2596,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>107388</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>21</x:v>
@@ -2575,16 +2604,16 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>107940</x:v>
+        <x:v>107388</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>21</x:v>
@@ -2592,16 +2621,16 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>558813</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>21</x:v>
@@ -2609,16 +2638,16 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>1673736</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>21</x:v>
@@ -2626,16 +2655,16 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>350000</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>21</x:v>
@@ -2643,16 +2672,16 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>430866</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>21</x:v>
@@ -2660,7 +2689,7 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>26</x:v>
@@ -2677,16 +2706,16 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>708827</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>21</x:v>
@@ -2694,24 +2723,24 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>56045</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>42</x:v>
@@ -2720,24 +2749,24 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>4210393</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>755146</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>21</x:v>
@@ -2745,16 +2774,16 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>285008</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>21</x:v>
@@ -2765,13 +2794,13 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>21</x:v>
@@ -2779,33 +2808,33 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>9985740</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>817066</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>12</x:v>
@@ -2813,16 +2842,16 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>2475786</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>12</x:v>
@@ -2830,33 +2859,33 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>557012</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>83860</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>21</x:v>
@@ -2864,16 +2893,16 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>513868</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>21</x:v>
@@ -2881,16 +2910,16 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>628597</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>21</x:v>
@@ -2898,7 +2927,7 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>16</x:v>
@@ -2907,7 +2936,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>221403</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>21</x:v>
@@ -2915,16 +2944,16 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>7170138</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>21</x:v>
@@ -2932,16 +2961,16 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>350000</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>21</x:v>
@@ -2949,16 +2978,16 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>21</x:v>
@@ -2966,16 +2995,16 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>3114863</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>21</x:v>
@@ -2983,16 +3012,16 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>91847</x:v>
+        <x:v>3114863</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>21</x:v>
@@ -3000,16 +3029,16 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>21</x:v>
@@ -3017,16 +3046,16 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>21</x:v>
@@ -3034,16 +3063,16 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>21</x:v>
@@ -3051,16 +3080,16 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>198570</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>21</x:v>
@@ -3068,16 +3097,16 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>275034</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>21</x:v>
@@ -3085,16 +3114,16 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>550000</x:v>
+        <x:v>275034</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>21</x:v>
@@ -3102,16 +3131,16 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>56118</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>21</x:v>
@@ -3119,16 +3148,16 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>2250000</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>21</x:v>
@@ -3136,16 +3165,16 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>21</x:v>
@@ -3153,16 +3182,16 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>461943</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>21</x:v>
@@ -3170,16 +3199,16 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>183312</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>21</x:v>
@@ -3187,24 +3216,24 @@
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D47" s="1">
-        <x:v>47162</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
         <x:v>45</x:v>
@@ -3213,24 +3242,24 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D48" s="1">
-        <x:v>6468074</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D49" s="1">
-        <x:v>426280</x:v>
+        <x:v>6468074</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>21</x:v>
@@ -3238,16 +3267,16 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D50" s="1">
-        <x:v>282526</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>21</x:v>
@@ -3255,16 +3284,16 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D51" s="1">
-        <x:v>616386</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>21</x:v>
@@ -3272,16 +3301,16 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D52" s="1">
-        <x:v>348433</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>21</x:v>
@@ -3289,24 +3318,24 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D53" s="1">
-        <x:v>20483</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
         <x:v>47</x:v>
@@ -3315,9 +3344,26 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D54" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:5">
+      <x:c r="A55" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B55" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C55" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D55" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E54" s="1" t="s">
+      <x:c r="E55" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -3337,7 +3383,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D50"/>
+  <x:dimension ref="A1:D51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3397,7 +3443,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>111440</x:v>
+        <x:v>372060</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
         <x:v>21</x:v>
@@ -3433,13 +3479,13 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>54932</x:v>
+        <x:v>366028</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>21</x:v>
@@ -3453,7 +3499,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>106348</x:v>
+        <x:v>476254</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>21</x:v>
@@ -3461,13 +3507,13 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>54685</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>21</x:v>
@@ -3481,7 +3527,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>107388</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>21</x:v>
@@ -3489,13 +3535,13 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>107940</x:v>
+        <x:v>107388</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
         <x:v>21</x:v>
@@ -3503,13 +3549,13 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>558813</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
         <x:v>21</x:v>
@@ -3517,13 +3563,13 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>1673736</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>21</x:v>
@@ -3531,13 +3577,13 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>350000</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>21</x:v>
@@ -3545,13 +3591,13 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>861732</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>21</x:v>
@@ -3559,13 +3605,13 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>708827</x:v>
+        <x:v>861732</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>21</x:v>
@@ -3573,16 +3619,16 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>56045</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
@@ -3593,21 +3639,21 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>4210393</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>755146</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>21</x:v>
@@ -3615,13 +3661,13 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>315191</x:v>
+        <x:v>755146</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>21</x:v>
@@ -3629,27 +3675,27 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>9985740</x:v>
+        <x:v>315191</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>817066</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3657,13 +3703,13 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>2475786</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>12</x:v>
@@ -3671,27 +3717,27 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>557012</x:v>
+        <x:v>2475786</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>83860</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>21</x:v>
@@ -3699,13 +3745,13 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>513868</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>21</x:v>
@@ -3713,13 +3759,13 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>850000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>21</x:v>
@@ -3727,13 +3773,13 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>7170138</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>21</x:v>
@@ -3741,13 +3787,13 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>600000</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>21</x:v>
@@ -3755,13 +3801,13 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>3114863</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
         <x:v>21</x:v>
@@ -3769,13 +3815,13 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>91847</x:v>
+        <x:v>3114863</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>21</x:v>
@@ -3783,13 +3829,13 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>161896</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>21</x:v>
@@ -3797,13 +3843,13 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>350000</x:v>
+        <x:v>161896</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>21</x:v>
@@ -3811,13 +3857,13 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
         <x:v>21</x:v>
@@ -3825,13 +3871,13 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>198570</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>21</x:v>
@@ -3839,13 +3885,13 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>275034</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
         <x:v>21</x:v>
@@ -3853,13 +3899,13 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>550000</x:v>
+        <x:v>275034</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>21</x:v>
@@ -3867,13 +3913,13 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>56118</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
         <x:v>21</x:v>
@@ -3881,13 +3927,13 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>2250000</x:v>
+        <x:v>56118</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>21</x:v>
@@ -3895,13 +3941,13 @@
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
         <x:v>21</x:v>
@@ -3909,13 +3955,13 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>461943</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
         <x:v>21</x:v>
@@ -3923,13 +3969,13 @@
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>183312</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>21</x:v>
@@ -3937,16 +3983,16 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>47162</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
@@ -3957,21 +4003,21 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>6468074</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C45" s="1">
-        <x:v>426280</x:v>
+        <x:v>6468074</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
         <x:v>21</x:v>
@@ -3979,13 +4025,13 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C46" s="1">
-        <x:v>282526</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
         <x:v>21</x:v>
@@ -3993,13 +4039,13 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C47" s="1">
-        <x:v>616386</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
         <x:v>21</x:v>
@@ -4007,13 +4053,13 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C48" s="1">
-        <x:v>348433</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
         <x:v>21</x:v>
@@ -4021,16 +4067,16 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C49" s="1">
-        <x:v>20483</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
@@ -4041,9 +4087,23 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C50" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:4">
+      <x:c r="A51" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C51" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D50" s="1" t="s">
+      <x:c r="D51" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -4110,7 +4170,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>763605</x:v>
+        <x:v>2124421</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>21</x:v>
@@ -4173,7 +4233,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>513868</x:v>
@@ -4195,7 +4255,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>600000</x:v>
@@ -4206,7 +4266,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>3114863</x:v>
@@ -4239,7 +4299,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>632975</x:v>
@@ -4253,7 +4313,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>198570</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>21</x:v>
@@ -4272,7 +4332,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>606118</x:v>
@@ -4378,7 +4438,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>763605</x:v>
+        <x:v>2124421</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -4407,7 +4467,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>513868</x:v>
@@ -4423,7 +4483,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>600000</x:v>
@@ -4431,7 +4491,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>3114863</x:v>
@@ -4455,7 +4515,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>632975</x:v>
@@ -4466,7 +4526,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>198570</x:v>
+        <x:v>262965</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
@@ -4479,7 +4539,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>606118</x:v>
@@ -4578,7 +4638,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>763605</x:v>
+        <x:v>2124421</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -4652,7 +4712,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>513868</x:v>
@@ -4685,7 +4745,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>600000</x:v>
@@ -4696,7 +4756,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>3114863</x:v>
@@ -4729,7 +4789,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>282975</x:v>
@@ -4740,7 +4800,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>350000</x:v>
@@ -4754,7 +4814,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>198570</x:v>
+        <x:v>262965</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -4773,7 +4833,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>56118</x:v>
@@ -4784,7 +4844,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>550000</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -340,6 +340,12 @@
   </x:si>
   <x:si>
     <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
   </x:si>
   <x:si>
     <x:t>COLLINS, MICHAEL A JR</x:t>
@@ -440,8 +446,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G69" totalsRowShown="0">
-  <x:autoFilter ref="A1:G69"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G70" totalsRowShown="0">
+  <x:autoFilter ref="A1:G70"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -456,8 +462,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E55" totalsRowShown="0">
-  <x:autoFilter ref="A1:E55"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E56" totalsRowShown="0">
+  <x:autoFilter ref="A1:E56"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -470,8 +476,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D51" totalsRowShown="0">
-  <x:autoFilter ref="A1:D51"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D52" totalsRowShown="0">
+  <x:autoFilter ref="A1:D52"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -483,8 +489,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C23" totalsRowShown="0">
-  <x:autoFilter ref="A1:C23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C24" totalsRowShown="0">
+  <x:autoFilter ref="A1:C24"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -495,8 +501,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B19" totalsRowShown="0">
-  <x:autoFilter ref="A1:B19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B20" totalsRowShown="0">
+  <x:autoFilter ref="A1:B20"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -506,8 +512,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C28" totalsRowShown="0">
-  <x:autoFilter ref="A1:C28"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C29" totalsRowShown="0">
+  <x:autoFilter ref="A1:C29"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -805,7 +811,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G69"/>
+  <x:dimension ref="A1:G70"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2114,16 +2120,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>8423195</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>21</x:v>
@@ -2131,10 +2137,10 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>37</x:v>
@@ -2146,7 +2152,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>350000</x:v>
+        <x:v>8423195</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
         <x:v>21</x:v>
@@ -2160,13 +2166,13 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="1">
         <x:v>350000</x:v>
@@ -2177,33 +2183,33 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>4697360</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>15</x:v>
@@ -2215,7 +2221,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>119644</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2229,19 +2235,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>285008</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
@@ -2255,13 +2261,13 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>30183</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>21</x:v>
@@ -2269,22 +2275,22 @@
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>628597</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>21</x:v>
@@ -2298,7 +2304,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
         <x:v>16</x:v>
@@ -2307,7 +2313,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>221403</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>21</x:v>
@@ -2321,16 +2327,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>250000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>21</x:v>
@@ -2350,10 +2356,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>21</x:v>
@@ -2367,13 +2373,13 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F68" s="1">
         <x:v>350000</x:v>
@@ -2390,18 +2396,41 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F69" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G69" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:7">
+      <x:c r="A70" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B70" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C70" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D70" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E70" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F69" s="1">
+      <x:c r="F70" s="1">
         <x:v>2250000</x:v>
       </x:c>
-      <x:c r="G69" s="1" t="s">
+      <x:c r="G70" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2421,7 +2450,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E55"/>
+  <x:dimension ref="A1:E56"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2672,7 +2701,7 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>16</x:v>
@@ -2791,10 +2820,10 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>11</x:v>
@@ -2808,10 +2837,10 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>11</x:v>
@@ -2944,7 +2973,7 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>16</x:v>
@@ -2978,13 +3007,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>350000</x:v>
@@ -2995,13 +3024,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>250000</x:v>
@@ -3063,7 +3092,7 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>16</x:v>
@@ -3165,16 +3194,16 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>2250000</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>21</x:v>
@@ -3182,16 +3211,16 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>21</x:v>
@@ -3199,16 +3228,16 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>461943</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>21</x:v>
@@ -3216,16 +3245,16 @@
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D47" s="1">
-        <x:v>183312</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>21</x:v>
@@ -3233,24 +3262,24 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D48" s="1">
-        <x:v>47162</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
         <x:v>45</x:v>
@@ -3259,24 +3288,24 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D49" s="1">
-        <x:v>6468074</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D50" s="1">
-        <x:v>426280</x:v>
+        <x:v>6468074</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>21</x:v>
@@ -3284,16 +3313,16 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D51" s="1">
-        <x:v>282526</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>21</x:v>
@@ -3301,16 +3330,16 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D52" s="1">
-        <x:v>616386</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>21</x:v>
@@ -3318,16 +3347,16 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D53" s="1">
-        <x:v>348433</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
         <x:v>21</x:v>
@@ -3335,24 +3364,24 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D54" s="1">
-        <x:v>20483</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
         <x:v>47</x:v>
@@ -3361,9 +3390,26 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D55" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="E55" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:5">
+      <x:c r="A56" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D56" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="E55" s="1" t="s">
+      <x:c r="E56" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -3383,7 +3429,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D51"/>
+  <x:dimension ref="A1:D52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3675,7 +3721,7 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>11</x:v>
@@ -3804,7 +3850,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>600000</x:v>
@@ -3944,10 +3990,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>2250000</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
         <x:v>21</x:v>
@@ -3955,13 +4001,13 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
         <x:v>21</x:v>
@@ -3969,13 +4015,13 @@
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>461943</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>21</x:v>
@@ -3983,13 +4029,13 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>183312</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
         <x:v>21</x:v>
@@ -3997,16 +4043,16 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>47162</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
@@ -4017,21 +4063,21 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C45" s="1">
-        <x:v>6468074</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C46" s="1">
-        <x:v>426280</x:v>
+        <x:v>6468074</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
         <x:v>21</x:v>
@@ -4039,13 +4085,13 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C47" s="1">
-        <x:v>282526</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
         <x:v>21</x:v>
@@ -4053,13 +4099,13 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C48" s="1">
-        <x:v>616386</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
         <x:v>21</x:v>
@@ -4067,13 +4113,13 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C49" s="1">
-        <x:v>348433</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
         <x:v>21</x:v>
@@ -4081,16 +4127,16 @@
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C50" s="1">
-        <x:v>20483</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
@@ -4101,9 +4147,23 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C51" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:4">
+      <x:c r="A52" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C52" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="D51" s="1" t="s">
+      <x:c r="D52" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -4123,7 +4183,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C23"/>
+  <x:dimension ref="A1:C24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4255,7 +4315,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>600000</x:v>
@@ -4343,13 +4403,13 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>47162</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -4357,21 +4417,21 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>12580270</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B22" s="1">
-        <x:v>20483</x:v>
+        <x:v>12580270</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -4379,9 +4439,20 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B23" s="1">
+        <x:v>20483</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B24" s="1">
         <x:v>1012792</x:v>
       </x:c>
-      <x:c r="C23" s="1" t="s">
+      <x:c r="C24" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -4401,7 +4472,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B19"/>
+  <x:dimension ref="A1:B20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4483,7 +4554,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>600000</x:v>
@@ -4547,17 +4618,25 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>12627432</x:v>
+        <x:v>411748</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B19" s="1">
+        <x:v>12627432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:2">
+      <x:c r="A20" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B19" s="1">
+      <x:c r="B20" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>
@@ -4577,7 +4656,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C28"/>
+  <x:dimension ref="A1:C29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4745,7 +4824,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>600000</x:v>
@@ -4855,32 +4934,32 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>3862196</x:v>
+        <x:v>411748</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>2250000</x:v>
+        <x:v>3862196</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>6515236</x:v>
+        <x:v>2250000</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -4888,9 +4967,20 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C28" s="1">
+        <x:v>6515236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C28" s="1">
+      <x:c r="C29" s="1">
         <x:v>1033275</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -1324,7 +1324,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>275034</x:v>
+        <x:v>318826</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>21</x:v>
@@ -1830,7 +1830,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>3114863</x:v>
+        <x:v>3174537</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>21</x:v>
@@ -2083,7 +2083,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>56118</x:v>
+        <x:v>112236</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>21</x:v>
@@ -3050,7 +3050,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>3114863</x:v>
+        <x:v>3174537</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>21</x:v>
@@ -3152,7 +3152,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>275034</x:v>
+        <x:v>318826</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>21</x:v>
@@ -3186,7 +3186,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>56118</x:v>
+        <x:v>112236</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>21</x:v>
@@ -3867,7 +3867,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>3114863</x:v>
+        <x:v>3174537</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>21</x:v>
@@ -3951,7 +3951,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>275034</x:v>
+        <x:v>318826</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>21</x:v>
@@ -3979,7 +3979,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>56118</x:v>
+        <x:v>112236</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>21</x:v>
@@ -4329,7 +4329,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>3114863</x:v>
+        <x:v>3174537</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>21</x:v>
@@ -4384,7 +4384,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>275034</x:v>
+        <x:v>318826</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>21</x:v>
@@ -4395,7 +4395,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>606118</x:v>
+        <x:v>662236</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>21</x:v>
@@ -4565,7 +4565,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>3114863</x:v>
+        <x:v>3174537</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
@@ -4605,7 +4605,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>275034</x:v>
+        <x:v>318826</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
@@ -4613,7 +4613,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>606118</x:v>
+        <x:v>662236</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -4838,7 +4838,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>3114863</x:v>
+        <x:v>3174537</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -4904,7 +4904,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>275034</x:v>
+        <x:v>318826</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -4915,7 +4915,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>56118</x:v>
+        <x:v>112236</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,6 +42,30 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
@@ -69,9 +93,6 @@
     <x:t>STRATTON, JULIANA</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00836221</x:t>
   </x:si>
   <x:si>
@@ -84,9 +105,6 @@
     <x:t>AR</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
     <x:t>MOORE, TIM</x:t>
   </x:si>
   <x:si>
@@ -117,9 +135,6 @@
     <x:t>08</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
     <x:t>GOBER, CHRIS</x:t>
   </x:si>
   <x:si>
@@ -189,12 +204,6 @@
     <x:t>GA</x:t>
   </x:si>
   <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>BARR, GARLAND ANDY</x:t>
   </x:si>
   <x:si>
@@ -300,9 +309,6 @@
     <x:t>03</x:t>
   </x:si>
   <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
     <x:t>BONCK, JON</x:t>
   </x:si>
   <x:si>
@@ -370,12 +376,6 @@
   </x:si>
   <x:si>
     <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -864,7 +864,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>817066</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -881,13 +881,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F3" s="1">
-        <x:v>1803694</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -895,102 +895,102 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>5168736</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
+      <x:c r="F5" s="1">
+        <x:v>1803694</x:v>
+      </x:c>
+      <x:c r="G5" s="1" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="F5" s="1">
-        <x:v>418058</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>80948</x:v>
+        <x:v>5168736</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>558813</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>28</x:v>
@@ -999,217 +999,217 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>1673736</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>771658</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="F10" s="1">
-        <x:v>91656</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>141263</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>5017853</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="D13" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>83860</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F14" s="1">
-        <x:v>515519</x:v>
+        <x:v>5017853</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>1564215</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>1012792</x:v>
+        <x:v>515519</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>20483</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1217,160 +1217,160 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
+      <x:c r="D18" s="1" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>91847</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>455146</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
+      <x:c r="C20" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>300000</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>7170138</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="F22" s="1">
-        <x:v>318826</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>430866</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>56045</x:v>
+        <x:v>318826</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>12</x:v>
@@ -1378,229 +1378,229 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>228075</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>34890</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>418060</x:v>
+        <x:v>228075</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>111598</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>109274</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
+      <x:c r="E30" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="F30" s="1">
-        <x:v>476254</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>106348</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>107940</x:v>
+        <x:v>476254</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>80948</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>47162</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1608,183 +1608,183 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>372060</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>366028</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>367531</x:v>
+        <x:v>372060</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D38" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>107388</x:v>
+        <x:v>366028</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D39" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>430866</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>708827</x:v>
+        <x:v>107388</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>4210393</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>672092</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1792,240 +1792,240 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>41493</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>3174537</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>282975</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>348433</x:v>
+        <x:v>3174537</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>771658</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>461943</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>91656</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>4903859</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>426280</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>141263</x:v>
+        <x:v>4903859</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>99</x:v>
@@ -2034,174 +2034,174 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>616386</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>513868</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>112236</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>550000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E57" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="D57" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E57" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
       <x:c r="F57" s="1">
-        <x:v>411748</x:v>
+        <x:v>112236</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>8423195</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>350000</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>350000</x:v>
+        <x:v>8423195</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
@@ -2212,16 +2212,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>4697360</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2229,22 +2229,22 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>119644</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2252,186 +2252,186 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>285008</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>30183</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>628597</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D66" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="D66" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>221403</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>250000</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>350000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D69" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E69" s="1" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D69" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E69" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="F69" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>2250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2480,937 +2480,937 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>13791048</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>372060</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>111598</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>366028</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>476254</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>367531</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>107388</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>430866</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>430866</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>708827</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>4210393</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>755146</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>285008</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>30183</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>513868</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>628597</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>221403</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>7170138</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>250000</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>3174537</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>282975</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>262965</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>318826</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>550000</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="B43" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>112236</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>411748</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>2250000</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>461943</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>6468074</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>426280</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>616386</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>348433</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3455,716 +3455,716 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>13791048</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>372060</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>111598</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>366028</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="B8" s="1" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>476254</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>367531</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>107388</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>861732</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>708827</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>4210393</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>755146</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>315191</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>513868</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>7170138</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>3174537</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>282975</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>262965</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>318826</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>550000</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>112236</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>411748</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>2250000</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>461943</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>6468074</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>426280</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>616386</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>348433</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4205,255 +4205,255 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>13791048</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2124421</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>2232549</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>6886098</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>13278592</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>956063</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>513868</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>8020138</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>3174537</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>632975</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>262965</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>318826</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>662236</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>411748</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>12580270</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4490,7 +4490,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>13791048</x:v>
@@ -4498,7 +4498,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
@@ -4506,7 +4506,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2124421</x:v>
@@ -4514,7 +4514,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>2232549</x:v>
@@ -4522,7 +4522,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>6942143</x:v>
@@ -4530,7 +4530,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>14234655</x:v>
@@ -4538,7 +4538,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>513868</x:v>
@@ -4546,7 +4546,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>8020138</x:v>
@@ -4554,7 +4554,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>600000</x:v>
@@ -4562,7 +4562,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>3174537</x:v>
@@ -4570,7 +4570,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>91847</x:v>
@@ -4578,7 +4578,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>161896</x:v>
@@ -4586,7 +4586,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>632975</x:v>
@@ -4594,7 +4594,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>262965</x:v>
@@ -4602,7 +4602,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>318826</x:v>
@@ -4610,7 +4610,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>662236</x:v>
@@ -4618,7 +4618,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>411748</x:v>
@@ -4626,7 +4626,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>12627432</x:v>
@@ -4634,7 +4634,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1033275</x:v>
@@ -4678,10 +4678,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>13441048</x:v>
@@ -4689,10 +4689,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>350000</x:v>
@@ -4700,10 +4700,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>836118</x:v>
@@ -4711,10 +4711,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>2124421</x:v>
@@ -4722,10 +4722,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>2232549</x:v>
@@ -4733,10 +4733,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2025705</x:v>
@@ -4744,10 +4744,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>650000</x:v>
@@ -4755,10 +4755,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>4266438</x:v>
@@ -4766,10 +4766,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>13158948</x:v>
@@ -4777,10 +4777,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1075707</x:v>
@@ -4788,10 +4788,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>513868</x:v>
@@ -4799,10 +4799,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>7170138</x:v>
@@ -4810,10 +4810,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>850000</x:v>
@@ -4821,10 +4821,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>600000</x:v>
@@ -4832,10 +4832,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>3174537</x:v>
@@ -4843,10 +4843,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>91847</x:v>
@@ -4854,10 +4854,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>161896</x:v>
@@ -4865,10 +4865,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>282975</x:v>
@@ -4876,10 +4876,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>350000</x:v>
@@ -4887,10 +4887,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>262965</x:v>
@@ -4898,10 +4898,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>318826</x:v>
@@ -4909,10 +4909,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>112236</x:v>
@@ -4920,10 +4920,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>550000</x:v>
@@ -4931,10 +4931,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>411748</x:v>
@@ -4942,10 +4942,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>3862196</x:v>
@@ -4953,10 +4953,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>2250000</x:v>
@@ -4964,10 +4964,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>6515236</x:v>
@@ -4975,10 +4975,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>1033275</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,340 +42,340 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATRONIS, JIMMY JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALKINSHAW, JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKARSKY, STELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00915181</x:t>
   </x:si>
   <x:si>
     <x:t>FELLOWSHIP PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TORRES, RITCHIE JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENENDEZ, ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIMON, LATEEFAH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WHITESIDES, GEORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIEU, TED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIN, DAVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCGUIRE, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRWIN, JACQUI V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIS, HILDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORREA, LOU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMITH, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELL, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
     <x:t>RICKETTS, PETE</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
     <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATRONIS, JIMMY JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALKINSHAW, JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKARSKY, STELLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00894428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROGERS, MICHAEL J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TORRES, RITCHIE JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENENDEZ, ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SIMON, LATEEFAH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOFGREN, ZOE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WHITESIDES, GEORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIEU, TED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIN, DAVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN, ALEXANDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCGUIRE, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRWIN, JACQUI V</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIS, HILDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CORREA, LOU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMITH, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEALER, ALEXANDRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELL, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROUNDS, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -864,7 +864,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>350000</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -881,13 +881,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>2250000</x:v>
+        <x:v>1803694</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -895,102 +895,102 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>817066</x:v>
+        <x:v>5168736</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>1803694</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>5168736</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="s">
+      <x:c r="D7" s="1" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>418058</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>28</x:v>
@@ -999,217 +999,217 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>80948</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
+      <x:c r="E9" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="F9" s="1">
-        <x:v>558813</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>1673736</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>771658</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="F12" s="1">
-        <x:v>91656</x:v>
+        <x:v>5017853</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>141263</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>5017853</x:v>
+        <x:v>515519</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
+      <x:c r="D15" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>83860</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="F16" s="1">
-        <x:v>515519</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>1564215</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1217,160 +1217,160 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>1012792</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>20483</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="F20" s="1">
-        <x:v>91847</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>455146</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>300000</x:v>
+        <x:v>318826</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>7170138</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>318826</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>12</x:v>
@@ -1378,229 +1378,229 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="F25" s="1">
-        <x:v>430866</x:v>
+        <x:v>228075</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>56045</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>228075</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>34890</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>418060</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>111598</x:v>
+        <x:v>476254</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>109274</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>476254</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>106348</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C34" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D34" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>107940</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1608,183 +1608,183 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>80948</x:v>
+        <x:v>372060</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>47162</x:v>
+        <x:v>366028</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>372060</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>366028</x:v>
+        <x:v>107388</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>367531</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>107388</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>430866</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>708827</x:v>
+        <x:v>672092</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1792,240 +1792,240 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>4210393</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>672092</x:v>
+        <x:v>3174537</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>41493</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>3174537</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>282975</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D48" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>348433</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>771658</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>461943</x:v>
+        <x:v>4903859</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>91656</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>4903859</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>99</x:v>
@@ -2034,174 +2034,174 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>426280</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>141263</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>616386</x:v>
+        <x:v>112236</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>513868</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>112236</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>550000</x:v>
+        <x:v>8423195</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>8423195</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
@@ -2212,16 +2212,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>350000</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2229,22 +2229,22 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>350000</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2252,186 +2252,186 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>4697360</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>119644</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>285008</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>30183</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>628597</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D68" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E68" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="D68" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E68" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="F68" s="1">
-        <x:v>221403</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2480,937 +2480,937 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>13791048</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>372060</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>111598</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>366028</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>476254</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>367531</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>107388</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>430866</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>430866</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>708827</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>4210393</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>755146</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>285008</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>30183</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
         <x:v>103</x:v>
-      </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>513868</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>628597</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>221403</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>7170138</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>250000</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>3174537</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>282975</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>262965</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>318826</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>550000</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>112236</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>411748</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>2250000</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>461943</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>6468074</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>426280</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>616386</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>348433</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3455,716 +3455,716 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>13791048</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>372060</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>111598</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>366028</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>476254</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>367531</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>107388</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>861732</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>708827</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>4210393</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>755146</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>315191</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>9985740</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>2475786</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>513868</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>850000</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>7170138</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>3174537</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>282975</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>262965</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>318826</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>550000</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>112236</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>411748</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>2250000</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>461943</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>6468074</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>426280</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>616386</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>348433</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4205,255 +4205,255 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>13791048</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2124421</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>2232549</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>6886098</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>13278592</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>956063</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>513868</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>8020138</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>3174537</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>632975</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>262965</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>318826</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>662236</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>411748</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>12580270</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4490,7 +4490,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>13791048</x:v>
@@ -4498,7 +4498,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>836118</x:v>
@@ -4506,7 +4506,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>2124421</x:v>
@@ -4514,7 +4514,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>2232549</x:v>
@@ -4522,7 +4522,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>6942143</x:v>
@@ -4530,7 +4530,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>14234655</x:v>
@@ -4538,7 +4538,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>513868</x:v>
@@ -4546,7 +4546,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>8020138</x:v>
@@ -4554,7 +4554,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>600000</x:v>
@@ -4562,7 +4562,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>3174537</x:v>
@@ -4570,7 +4570,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>91847</x:v>
@@ -4578,7 +4578,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>161896</x:v>
@@ -4586,7 +4586,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>632975</x:v>
@@ -4594,7 +4594,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>262965</x:v>
@@ -4602,7 +4602,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>318826</x:v>
@@ -4610,7 +4610,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>662236</x:v>
@@ -4618,7 +4618,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>411748</x:v>
@@ -4626,7 +4626,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>12627432</x:v>
@@ -4634,7 +4634,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1033275</x:v>
@@ -4678,10 +4678,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>13441048</x:v>
@@ -4689,10 +4689,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>350000</x:v>
@@ -4700,10 +4700,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>836118</x:v>
@@ -4711,10 +4711,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>2124421</x:v>
@@ -4722,10 +4722,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>2232549</x:v>
@@ -4733,10 +4733,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2025705</x:v>
@@ -4744,10 +4744,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>650000</x:v>
@@ -4755,10 +4755,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>4266438</x:v>
@@ -4766,10 +4766,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>13158948</x:v>
@@ -4777,10 +4777,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1075707</x:v>
@@ -4788,10 +4788,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>513868</x:v>
@@ -4799,10 +4799,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>7170138</x:v>
@@ -4810,10 +4810,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>850000</x:v>
@@ -4821,10 +4821,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>600000</x:v>
@@ -4832,10 +4832,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>3174537</x:v>
@@ -4843,10 +4843,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>91847</x:v>
@@ -4854,10 +4854,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>161896</x:v>
@@ -4865,10 +4865,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>282975</x:v>
@@ -4876,10 +4876,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>350000</x:v>
@@ -4887,10 +4887,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>262965</x:v>
@@ -4898,10 +4898,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>318826</x:v>
@@ -4909,10 +4909,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>112236</x:v>
@@ -4920,10 +4920,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>550000</x:v>
@@ -4931,10 +4931,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>411748</x:v>
@@ -4942,10 +4942,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>3862196</x:v>
@@ -4953,10 +4953,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>2250000</x:v>
@@ -4964,10 +4964,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>6515236</x:v>
@@ -4975,10 +4975,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>1033275</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -2083,7 +2083,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>112236</x:v>
+        <x:v>168354</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>21</x:v>
@@ -3186,7 +3186,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>112236</x:v>
+        <x:v>168354</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>21</x:v>
@@ -3979,7 +3979,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>112236</x:v>
+        <x:v>168354</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>21</x:v>
@@ -4395,7 +4395,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>662236</x:v>
+        <x:v>718354</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>21</x:v>
@@ -4613,7 +4613,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>662236</x:v>
+        <x:v>718354</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -4915,7 +4915,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>112236</x:v>
+        <x:v>168354</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,66 +42,288 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENENDEZ, ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIMON, LATEEFAH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WHITESIDES, GEORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIEU, TED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIN, DAVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCGUIRE, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRWIN, JACQUI V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIS, HILDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORREA, LOU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
     <x:t>FAIRSHAKE</x:t>
   </x:si>
   <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMITH, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELL, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
     <x:t>PETERS, ROBERT JAMES</x:t>
   </x:si>
   <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
     <x:t>PATRONIS, JIMMY JR.</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
     <x:t>FL</x:t>
   </x:si>
   <x:si>
@@ -111,54 +333,9 @@
     <x:t>06</x:t>
   </x:si>
   <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
     <x:t>BUDZINSKI, NIKKI</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
     <x:t>WALKINSHAW, JAMES</x:t>
   </x:si>
   <x:si>
@@ -186,21 +363,6 @@
     <x:t>FULLER, CLAY</x:t>
   </x:si>
   <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
     <x:t>TORRES, RITCHIE JOHN</x:t>
   </x:si>
   <x:si>
@@ -208,168 +370,6 @@
   </x:si>
   <x:si>
     <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENENDEZ, ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SIMON, LATEEFAH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOFGREN, ZOE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WHITESIDES, GEORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIEU, TED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIN, DAVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN, ALEXANDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCGUIRE, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRWIN, JACQUI V</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIS, HILDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CORREA, LOU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMITH, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEALER, ALEXANDRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELL, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROUNDS, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
   </x:si>
   <x:si>
     <x:t>RICKETTS, PETE</x:t>
@@ -864,7 +864,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>817066</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -872,45 +872,45 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>1803694</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>5168736</x:v>
+        <x:v>228075</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -918,298 +918,298 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>418058</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>80948</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+      <x:c r="E7" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F7" s="1">
-        <x:v>558813</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>1673736</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>771658</x:v>
+        <x:v>476254</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>91656</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>141263</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="F12" s="1">
-        <x:v>5017853</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C13" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F13" s="1">
-        <x:v>83860</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>515519</x:v>
+        <x:v>372060</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>1564215</x:v>
+        <x:v>366028</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>1012792</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>20483</x:v>
+        <x:v>107388</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1217,160 +1217,160 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>91847</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>455146</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>300000</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F21" s="1">
+        <x:v>672092</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="B21" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C21" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F21" s="1">
-        <x:v>7170138</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>318826</x:v>
+        <x:v>41493</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>430866</x:v>
+        <x:v>3234211</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>56045</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>12</x:v>
@@ -1378,229 +1378,229 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="F25" s="1">
-        <x:v>228075</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="F26" s="1">
-        <x:v>34890</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>418060</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>111598</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="F29" s="1">
-        <x:v>109274</x:v>
+        <x:v>4903859</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B30" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="F30" s="1">
-        <x:v>476254</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B31" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C31" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="F31" s="1">
-        <x:v>106348</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B32" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C32" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="F32" s="1">
-        <x:v>107940</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>80948</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>47162</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1608,183 +1608,183 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>372060</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>366028</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>367531</x:v>
+        <x:v>9673851</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D38" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>107388</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>430866</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>708827</x:v>
+        <x:v>4697360</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>4210393</x:v>
+        <x:v>119644</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>672092</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1792,217 +1792,217 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>41493</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>3174537</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>282975</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>348433</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>771658</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F48" s="1">
+        <x:v>817066</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="B48" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C48" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D48" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="E48" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F48" s="1">
-        <x:v>461943</x:v>
-      </x:c>
-      <x:c r="G48" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F49" s="1">
+        <x:v>1803694</x:v>
+      </x:c>
+      <x:c r="G49" s="1" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="B49" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C49" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D49" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F49" s="1">
-        <x:v>91656</x:v>
-      </x:c>
-      <x:c r="G49" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>4903859</x:v>
+        <x:v>5168736</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>426280</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>35</x:v>
@@ -2011,217 +2011,217 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>616386</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D54" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="E54" s="1" t="s">
-        <x:v>103</x:v>
-      </x:c>
       <x:c r="F54" s="1">
-        <x:v>513868</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>168354</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>550000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>411748</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>8423195</x:v>
+        <x:v>5017853</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>350000</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B60" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C60" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B60" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C60" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>350000</x:v>
+        <x:v>515519</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>4697360</x:v>
+        <x:v>1564215</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2229,22 +2229,22 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>119644</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2252,186 +2252,186 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>285008</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D64" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E64" s="1" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="D64" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E64" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F64" s="1">
-        <x:v>30183</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>628597</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>80</x:v>
       </x:c